--- a/Na-aba/home/data/RT KS양식.xlsx
+++ b/Na-aba/home/data/RT KS양식.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjch2\Desktop\보고서\Project PROVIDENCE\Request\PMI\Na-aba\home\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\-\OneDrive\바탕 화면\home\Na-aba\home\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE4EA1B-BD73-4CB4-88D2-E97D603EF44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="951" xr2:uid="{9ECEBE91-38AF-4599-BFDF-6D5CC01440CA}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="951"/>
   </bookViews>
   <sheets>
     <sheet name="갑100A" sheetId="1782" r:id="rId1"/>
@@ -1095,7 +1094,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="10">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2018,7 +2017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="361">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="31" applyBorder="1">
       <alignment vertical="center"/>
@@ -2605,6 +2604,327 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="31" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="6" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="8" fillId="0" borderId="46" xfId="30" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="13" fillId="0" borderId="31" xfId="30" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="13" fillId="0" borderId="38" xfId="30" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="30" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="30" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="30" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="30" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="30" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="22" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2632,9 +2952,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="22" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2659,9 +2976,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2689,327 +3003,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="22" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="22" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="22" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="30" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="30" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="30" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="8" fillId="0" borderId="46" xfId="30" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="13" fillId="0" borderId="31" xfId="30" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="13" fillId="0" borderId="38" xfId="30" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="30" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="30" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3019,6 +3018,24 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="29" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="29" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="29" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="29" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3073,15 +3090,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3091,50 +3099,53 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="29" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="29" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="29" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="33">
-    <cellStyle name="AeE­ [0]_INQUIRY ¿μ¾÷AßAø " xfId="1" xr:uid="{3061352C-7516-4DE1-AFC0-A1B29E711105}"/>
-    <cellStyle name="AeE­_INQUIRY ¿μ¾÷AßAø " xfId="2" xr:uid="{DE16C153-C687-456A-85A5-C8C679B27EC8}"/>
-    <cellStyle name="AÞ¸¶ [0]_INQUIRY ¿μ¾÷AßAø " xfId="3" xr:uid="{B5E10B54-4D55-4B23-8A92-96E5EBEC2F89}"/>
-    <cellStyle name="AÞ¸¶_INQUIRY ¿μ¾÷AßAø " xfId="4" xr:uid="{05519A78-27AA-4BCB-9316-4380509F9757}"/>
-    <cellStyle name="C￥AØ_¿μ¾÷CoE² " xfId="5" xr:uid="{95964D4E-0D62-4EB1-A7D4-C7B539D8037E}"/>
-    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="6" xr:uid="{DE144319-E848-44EF-A8BC-585105B8084B}"/>
-    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="7" xr:uid="{5381BFFC-F02B-4FE1-A1E3-A86DAF61D129}"/>
-    <cellStyle name="Comma0" xfId="8" xr:uid="{036982A4-43B7-41F7-A132-29C159AD4CF9}"/>
-    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="9" xr:uid="{F710A30F-C3BB-4FCB-B5D0-2E18D7EEA4DD}"/>
-    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="10" xr:uid="{3A93A1B0-0533-4C1D-A338-4935F1B727C8}"/>
-    <cellStyle name="Currency0" xfId="11" xr:uid="{811990FE-8AB8-44F4-A44B-E82D281158B4}"/>
-    <cellStyle name="Date" xfId="12" xr:uid="{9FABB5A9-07E5-4EC8-9A06-2EE46280C71D}"/>
-    <cellStyle name="Fixed" xfId="13" xr:uid="{5203EF62-25CD-40B8-B2F1-3775465109C1}"/>
-    <cellStyle name="Heading 1" xfId="14" xr:uid="{7D405A7B-B73E-4A7F-B645-C9F9FF4EA29B}"/>
-    <cellStyle name="Heading 2" xfId="15" xr:uid="{CBF44E66-CE5E-4C4F-8433-E3E14EE4DAA8}"/>
-    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="16" xr:uid="{05F8A452-49AA-4BDF-B841-34DA88854AD8}"/>
-    <cellStyle name="Total" xfId="17" xr:uid="{45B8ADD5-8B6B-4FA5-980C-1971070C4E5C}"/>
-    <cellStyle name="뷭?_BOOKSHIP" xfId="18" xr:uid="{815FD98D-C42D-4718-B0B0-5656A357DDEA}"/>
-    <cellStyle name="콤마 [0]_1202" xfId="19" xr:uid="{0C5D0AC3-A033-4226-A131-AD8BD896467E}"/>
-    <cellStyle name="콤마_1202" xfId="20" xr:uid="{4990173E-E963-429C-A610-5B09079A46EC}"/>
+    <cellStyle name="AeE­ [0]_INQUIRY ¿μ¾÷AßAø " xfId="1"/>
+    <cellStyle name="AeE­_INQUIRY ¿μ¾÷AßAø " xfId="2"/>
+    <cellStyle name="AÞ¸¶ [0]_INQUIRY ¿μ¾÷AßAø " xfId="3"/>
+    <cellStyle name="AÞ¸¶_INQUIRY ¿μ¾÷AßAø " xfId="4"/>
+    <cellStyle name="C￥AØ_¿μ¾÷CoE² " xfId="5"/>
+    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="6"/>
+    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="7"/>
+    <cellStyle name="Comma0" xfId="8"/>
+    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="9"/>
+    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="10"/>
+    <cellStyle name="Currency0" xfId="11"/>
+    <cellStyle name="Date" xfId="12"/>
+    <cellStyle name="Fixed" xfId="13"/>
+    <cellStyle name="Heading 1" xfId="14"/>
+    <cellStyle name="Heading 2" xfId="15"/>
+    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="16"/>
+    <cellStyle name="Total" xfId="17"/>
+    <cellStyle name="뷭?_BOOKSHIP" xfId="18"/>
+    <cellStyle name="콤마 [0]_1202" xfId="19"/>
+    <cellStyle name="콤마_1202" xfId="20"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 10" xfId="21" xr:uid="{855283DD-9CD2-4D16-A9EC-4AEED234454F}"/>
-    <cellStyle name="표준 2" xfId="22" xr:uid="{2C12960C-74AC-469F-8229-D4AB197D42D6}"/>
-    <cellStyle name="표준 3" xfId="23" xr:uid="{A305745F-6CC2-4B9F-B560-EF06ED89C796}"/>
-    <cellStyle name="표준 4" xfId="24" xr:uid="{80CDDEF6-F374-4E94-AB55-F5104B40E2FC}"/>
-    <cellStyle name="표준 5" xfId="25" xr:uid="{F4CB01FA-C3B7-41EB-A157-1ED29587CF8D}"/>
-    <cellStyle name="표준 6" xfId="26" xr:uid="{F7E4AAB3-F95D-4D06-9A31-691D3EDDAA9D}"/>
-    <cellStyle name="표준 7" xfId="27" xr:uid="{A345807D-7D7E-49E0-B09A-73A925DB9131}"/>
-    <cellStyle name="표준 8" xfId="28" xr:uid="{A5E212FB-DE55-4E32-BBF3-32C5CD892F3B}"/>
-    <cellStyle name="표준 9" xfId="29" xr:uid="{E6BBC66A-4C6F-4883-B531-3C286284E487}"/>
-    <cellStyle name="표준_002 RT" xfId="30" xr:uid="{B5B3DEC3-51E7-49B6-9DB6-53C502372D9A}"/>
-    <cellStyle name="표준_개정 성적서KS_036~039RT" xfId="31" xr:uid="{AAC59262-BA77-4B99-A682-E16EA1CEFCA3}"/>
-    <cellStyle name="표준_개정 성적서KS_064~067 RT" xfId="32" xr:uid="{B5FE0C4C-5965-473B-A986-64C058F73A73}"/>
+    <cellStyle name="표준 10" xfId="21"/>
+    <cellStyle name="표준 2" xfId="22"/>
+    <cellStyle name="표준 3" xfId="23"/>
+    <cellStyle name="표준 4" xfId="24"/>
+    <cellStyle name="표준 5" xfId="25"/>
+    <cellStyle name="표준 6" xfId="26"/>
+    <cellStyle name="표준 7" xfId="27"/>
+    <cellStyle name="표준 8" xfId="28"/>
+    <cellStyle name="표준 9" xfId="29"/>
+    <cellStyle name="표준_002 RT" xfId="30"/>
+    <cellStyle name="표준_개정 성적서KS_036~039RT" xfId="31"/>
+    <cellStyle name="표준_개정 성적서KS_064~067 RT" xfId="32"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3169,7 +3180,7 @@
         <xdr:cNvPr id="2" name="Text Box 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98FAC1F-D651-492D-E939-17587CBF9C0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F98FAC1F-D651-492D-E939-17587CBF9C0A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3245,7 +3256,7 @@
         <xdr:cNvPr id="3" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33108353-919B-AD37-8380-B598B2AC622C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{33108353-919B-AD37-8380-B598B2AC622C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3321,7 +3332,7 @@
         <xdr:cNvPr id="4" name="Text Box 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B09A7BCE-0182-22AD-800F-A6D64C804990}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B09A7BCE-0182-22AD-800F-A6D64C804990}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3404,7 +3415,7 @@
         <xdr:cNvPr id="5" name="Text Box 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC40579B-DD36-D58B-BF25-6475A330D45E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EC40579B-DD36-D58B-BF25-6475A330D45E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3487,7 +3498,7 @@
         <xdr:cNvPr id="6" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBF231F-67C1-7044-4C04-A985C4802126}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3EBF231F-67C1-7044-4C04-A985C4802126}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3563,7 +3574,7 @@
         <xdr:cNvPr id="7" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42E42894-DD26-B890-153E-FEFBC93C5BB0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{42E42894-DD26-B890-153E-FEFBC93C5BB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3639,7 +3650,7 @@
         <xdr:cNvPr id="3426053" name="Group 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EBFC3CA-1D9F-2B8F-FFEA-E3129C88045D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2EBFC3CA-1D9F-2B8F-FFEA-E3129C88045D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3649,8 +3660,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1112520" y="7094220"/>
-          <a:ext cx="4853940" cy="960120"/>
+          <a:off x="1240155" y="7210425"/>
+          <a:ext cx="5408295" cy="971550"/>
           <a:chOff x="126" y="704"/>
           <a:chExt cx="571" cy="102"/>
         </a:xfrm>
@@ -3660,7 +3671,7 @@
           <xdr:cNvPr id="3426302" name="Oval 8" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB2D715-B3BA-72D1-7663-481940195AD6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7DB2D715-B3BA-72D1-7663-481940195AD6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3696,7 +3707,7 @@
           <xdr:cNvPr id="3426303" name="Oval 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57C72CF8-8A22-1FD4-1C87-1D9B53477408}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{57C72CF8-8A22-1FD4-1C87-1D9B53477408}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3730,7 +3741,7 @@
           <xdr:cNvPr id="3426304" name="Freeform 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DECE7171-E42E-E6B6-7560-BAB3E453D084}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DECE7171-E42E-E6B6-7560-BAB3E453D084}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3817,7 +3828,7 @@
           <xdr:cNvPr id="12" name="Text Box 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50664E67-AC03-5680-08F1-67FED1FF9199}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{50664E67-AC03-5680-08F1-67FED1FF9199}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3899,7 +3910,7 @@
           <xdr:cNvPr id="3426306" name="Line 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07D8A4A6-7E19-57C3-D5EE-6778B716BF37}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07D8A4A6-7E19-57C3-D5EE-6778B716BF37}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3938,7 +3949,7 @@
           <xdr:cNvPr id="3426307" name="Line 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0693E5E6-724B-45C8-AA51-BD6E7F9288BD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0693E5E6-724B-45C8-AA51-BD6E7F9288BD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3978,7 +3989,7 @@
           <xdr:cNvPr id="3426308" name="Line 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF5752C-9583-23DE-97FC-8BCF64E31B31}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4DF5752C-9583-23DE-97FC-8BCF64E31B31}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4018,7 +4029,7 @@
           <xdr:cNvPr id="3426309" name="Freeform 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44EE272A-98B8-A1DD-595F-FE9FCB493EF9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{44EE272A-98B8-A1DD-595F-FE9FCB493EF9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4110,7 +4121,7 @@
           <xdr:cNvPr id="3426310" name="Freeform 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46EAA80D-4F1E-2C49-CF64-E53C758C844B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{46EAA80D-4F1E-2C49-CF64-E53C758C844B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4219,7 +4230,7 @@
           <xdr:cNvPr id="3426311" name="Rectangle 17" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB911486-1244-7A20-A27F-32973082E77D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB911486-1244-7A20-A27F-32973082E77D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4255,7 +4266,7 @@
           <xdr:cNvPr id="3426312" name="Rectangle 18" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1564D9F-73D7-4F14-31EF-84142B173058}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A1564D9F-73D7-4F14-31EF-84142B173058}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4291,7 +4302,7 @@
           <xdr:cNvPr id="3426313" name="Freeform 19">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAEA1E1-3FFC-25F7-D054-6E320EF527C6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8DAEA1E1-3FFC-25F7-D054-6E320EF527C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4449,7 +4460,7 @@
           <xdr:cNvPr id="21" name="Text Box 20">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C5190DE-F310-DD96-090C-6F83B34DD216}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C5190DE-F310-DD96-090C-6F83B34DD216}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4531,7 +4542,7 @@
           <xdr:cNvPr id="3426315" name="Line 21">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872B52D8-8449-B7DF-E30F-48DA080C380B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{872B52D8-8449-B7DF-E30F-48DA080C380B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4570,7 +4581,7 @@
           <xdr:cNvPr id="3426316" name="Line 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAA66FB-9C57-605C-A8FA-90F36E4A9101}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCAA66FB-9C57-605C-A8FA-90F36E4A9101}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4609,7 +4620,7 @@
           <xdr:cNvPr id="3426317" name="Line 23">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50D9CFD-42FE-886B-E983-EDBCEC5AE6D0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C50D9CFD-42FE-886B-E983-EDBCEC5AE6D0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4649,7 +4660,7 @@
           <xdr:cNvPr id="3426318" name="Line 24">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DBF658-A7FA-E45F-D99A-E81B7714669B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2DBF658-A7FA-E45F-D99A-E81B7714669B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4689,7 +4700,7 @@
           <xdr:cNvPr id="3426319" name="Freeform 25">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9464587C-B90F-D562-13CA-532EB2EC585F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9464587C-B90F-D562-13CA-532EB2EC585F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4776,7 +4787,7 @@
           <xdr:cNvPr id="3426320" name="Freeform 26" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4695B5DE-36AB-9E91-6472-92279588E80A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4695B5DE-36AB-9E91-6472-92279588E80A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4881,7 +4892,7 @@
           <xdr:cNvPr id="3426321" name="Oval 27" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2572122B-3C59-710B-AA97-632F09B5B6D8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2572122B-3C59-710B-AA97-632F09B5B6D8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4917,7 +4928,7 @@
           <xdr:cNvPr id="3426322" name="Oval 28">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09773257-DEAE-736F-F796-142B2C536BB3}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09773257-DEAE-736F-F796-142B2C536BB3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4951,7 +4962,7 @@
           <xdr:cNvPr id="3426323" name="Freeform 29">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A173643-2A40-1E90-C76C-BBAA1644008E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3A173643-2A40-1E90-C76C-BBAA1644008E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5038,7 +5049,7 @@
           <xdr:cNvPr id="31" name="Text Box 30">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6C877C-1FA0-1586-20B8-80C95CD2870D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2F6C877C-1FA0-1586-20B8-80C95CD2870D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5120,7 +5131,7 @@
           <xdr:cNvPr id="3426325" name="Line 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E59B9CD-9318-B259-4B58-45254C9389C7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E59B9CD-9318-B259-4B58-45254C9389C7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5159,7 +5170,7 @@
           <xdr:cNvPr id="3426326" name="Line 32">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF4915B2-ED67-B6DE-1061-3E1D9B6B95DA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EF4915B2-ED67-B6DE-1061-3E1D9B6B95DA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5199,7 +5210,7 @@
           <xdr:cNvPr id="3426327" name="Line 33">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68D33C33-5690-4953-C852-754679B37D0D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68D33C33-5690-4953-C852-754679B37D0D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5239,7 +5250,7 @@
           <xdr:cNvPr id="3426328" name="Freeform 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C218D996-5BA5-8B07-3910-DBD29E2C0182}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C218D996-5BA5-8B07-3910-DBD29E2C0182}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5331,7 +5342,7 @@
           <xdr:cNvPr id="3426329" name="Freeform 35">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FA2D215-2902-7EEE-27C6-2609BC661BB9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FA2D215-2902-7EEE-27C6-2609BC661BB9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5440,7 +5451,7 @@
           <xdr:cNvPr id="3426330" name="Rectangle 36" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F86858F-5AB7-D1D4-6F6A-77589C0BDB80}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1F86858F-5AB7-D1D4-6F6A-77589C0BDB80}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5476,7 +5487,7 @@
           <xdr:cNvPr id="3426331" name="Rectangle 37" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69970C06-A64D-3272-7649-CBC0387D73B0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{69970C06-A64D-3272-7649-CBC0387D73B0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5512,7 +5523,7 @@
           <xdr:cNvPr id="3426332" name="Freeform 38">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737F9507-8146-8D69-27D2-551E7F28B575}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{737F9507-8146-8D69-27D2-551E7F28B575}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5670,7 +5681,7 @@
           <xdr:cNvPr id="40" name="Text Box 39">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FEBCC9E-844D-A558-B182-18A74105FDF2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FEBCC9E-844D-A558-B182-18A74105FDF2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5752,7 +5763,7 @@
           <xdr:cNvPr id="3426334" name="Line 40">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{124D42B8-E2C5-0E68-85D9-A0A76AC4FC66}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{124D42B8-E2C5-0E68-85D9-A0A76AC4FC66}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5791,7 +5802,7 @@
           <xdr:cNvPr id="3426335" name="Line 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433B5DA4-B752-C4B3-6D79-5E3AFB999842}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{433B5DA4-B752-C4B3-6D79-5E3AFB999842}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5830,7 +5841,7 @@
           <xdr:cNvPr id="3426336" name="Freeform 42">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{774E1440-D564-9AC1-37FD-FAD4EB6DEB0D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{774E1440-D564-9AC1-37FD-FAD4EB6DEB0D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5917,7 +5928,7 @@
           <xdr:cNvPr id="3426337" name="Freeform 43" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE1DAC56-076E-C78B-F2E3-424BA00F692A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FE1DAC56-076E-C78B-F2E3-424BA00F692A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6040,7 +6051,7 @@
           <xdr:cNvPr id="3426338" name="Line 44">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B071D06C-A4F8-7274-3DFF-D3412A36EC91}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B071D06C-A4F8-7274-3DFF-D3412A36EC91}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6080,7 +6091,7 @@
           <xdr:cNvPr id="3426339" name="Line 45">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFB49859-D88B-619F-DD7C-FAEE67EA407A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CFB49859-D88B-619F-DD7C-FAEE67EA407A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6120,7 +6131,7 @@
           <xdr:cNvPr id="3426340" name="Freeform 46">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44647F3-C900-A7B0-F775-6F410E5D21CB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E44647F3-C900-A7B0-F775-6F410E5D21CB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6242,7 +6253,7 @@
           <xdr:cNvPr id="3426341" name="Freeform 47">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4A771CB-7DAC-31BF-480B-D133F696B61D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B4A771CB-7DAC-31BF-480B-D133F696B61D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6364,7 +6375,7 @@
           <xdr:cNvPr id="3426342" name="Oval 48" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FDC2419-5EDE-55A5-C717-EB0D58EE3D9A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FDC2419-5EDE-55A5-C717-EB0D58EE3D9A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6400,7 +6411,7 @@
           <xdr:cNvPr id="3426343" name="Oval 49">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F71CB4F-90C7-49F6-0C8D-2A717C497939}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5F71CB4F-90C7-49F6-0C8D-2A717C497939}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6434,7 +6445,7 @@
           <xdr:cNvPr id="3426344" name="Line 50">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AEC434-2635-248C-ACEF-8B92DA2B1111}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{98AEC434-2635-248C-ACEF-8B92DA2B1111}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6473,7 +6484,7 @@
           <xdr:cNvPr id="3426345" name="Line 51">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2D53B0-90D4-2988-F589-05C44EF2F018}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BF2D53B0-90D4-2988-F589-05C44EF2F018}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6513,7 +6524,7 @@
           <xdr:cNvPr id="3426346" name="Freeform 52">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{710B5F45-290D-B37E-2491-B7FD74E256E6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{710B5F45-290D-B37E-2491-B7FD74E256E6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6605,7 +6616,7 @@
           <xdr:cNvPr id="3426347" name="Freeform 53">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FB52224-71C0-58B4-D286-EED141FD4FB5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FB52224-71C0-58B4-D286-EED141FD4FB5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6714,7 +6725,7 @@
           <xdr:cNvPr id="3426348" name="Rectangle 54" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A2B03D3-ADAF-FB71-E515-3F249C12BD89}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7A2B03D3-ADAF-FB71-E515-3F249C12BD89}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6750,7 +6761,7 @@
           <xdr:cNvPr id="3426349" name="Line 55">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C716F34-8AC0-E246-90A8-77FF8D724164}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C716F34-8AC0-E246-90A8-77FF8D724164}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6790,7 +6801,7 @@
           <xdr:cNvPr id="3426350" name="Line 56">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7DD7220-82FE-66FB-98CF-BE6E627773F5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B7DD7220-82FE-66FB-98CF-BE6E627773F5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6830,7 +6841,7 @@
           <xdr:cNvPr id="3426351" name="Line 57">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C671D2B-9CF3-B0AE-49C0-8AE7A098936B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3C671D2B-9CF3-B0AE-49C0-8AE7A098936B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6869,7 +6880,7 @@
           <xdr:cNvPr id="3426352" name="Line 58">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8B856E1-F3A6-6044-16B6-EFEBA81D9D41}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B8B856E1-F3A6-6044-16B6-EFEBA81D9D41}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6908,7 +6919,7 @@
           <xdr:cNvPr id="3426353" name="Line 59">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6AFD834-2451-3E6E-19D9-25FE123ACC0A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A6AFD834-2451-3E6E-19D9-25FE123ACC0A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6948,7 +6959,7 @@
           <xdr:cNvPr id="3426354" name="Freeform 60" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D16C236-8CC6-9169-7FEC-441DAB0C4655}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5D16C236-8CC6-9169-7FEC-441DAB0C4655}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7030,7 +7041,7 @@
           <xdr:cNvPr id="3426355" name="Oval 61" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A63C2A9-AE9A-0925-D6E1-0320DF7989F1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4A63C2A9-AE9A-0925-D6E1-0320DF7989F1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7073,7 +7084,7 @@
           <xdr:cNvPr id="3426356" name="Freeform 62">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3CEDCF-48B8-6A88-7100-D60B8D845DA8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DE3CEDCF-48B8-6A88-7100-D60B8D845DA8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7153,7 +7164,7 @@
           <xdr:cNvPr id="3426357" name="Line 63">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBDD475D-5E5F-5FE2-B67A-4F70F2B0A8D7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EBDD475D-5E5F-5FE2-B67A-4F70F2B0A8D7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7192,7 +7203,7 @@
           <xdr:cNvPr id="3426358" name="Line 64">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7622C82A-704E-9E4A-4867-6D0E1235FFE7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7622C82A-704E-9E4A-4867-6D0E1235FFE7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7232,7 +7243,7 @@
           <xdr:cNvPr id="3426359" name="Line 65">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61087BAD-35AA-A724-802F-0B15B7221EC4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{61087BAD-35AA-A724-802F-0B15B7221EC4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7272,7 +7283,7 @@
           <xdr:cNvPr id="3426360" name="Oval 66" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DE614A0-5065-15AE-086E-3C07CE8B12AD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5DE614A0-5065-15AE-086E-3C07CE8B12AD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7308,7 +7319,7 @@
           <xdr:cNvPr id="3426361" name="Oval 67">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC882F86-215D-716E-310D-883A5FDA1E89}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AC882F86-215D-716E-310D-883A5FDA1E89}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7342,7 +7353,7 @@
           <xdr:cNvPr id="3426362" name="Line 68">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3CCB6BB-79A3-89C7-4FF2-0B15D9BCA850}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B3CCB6BB-79A3-89C7-4FF2-0B15D9BCA850}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7381,7 +7392,7 @@
           <xdr:cNvPr id="3426363" name="Line 69">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644AC0D5-7C23-CA66-B4EA-2387CD92B099}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{644AC0D5-7C23-CA66-B4EA-2387CD92B099}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7421,7 +7432,7 @@
           <xdr:cNvPr id="3426364" name="Freeform 70">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{043C11A5-D967-21F9-D426-88C6ECCB8835}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{043C11A5-D967-21F9-D426-88C6ECCB8835}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7513,7 +7524,7 @@
           <xdr:cNvPr id="3426365" name="Freeform 71">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D950DA3-EFC4-48EF-FD7F-189A54D1413F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1D950DA3-EFC4-48EF-FD7F-189A54D1413F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7622,7 +7633,7 @@
           <xdr:cNvPr id="3426366" name="Rectangle 72" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51234E0C-4F85-D8D6-4BAB-15D62EEEA602}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{51234E0C-4F85-D8D6-4BAB-15D62EEEA602}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7658,7 +7669,7 @@
           <xdr:cNvPr id="3426367" name="Line 73">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC4019F9-1102-F352-48CD-189A3FC0393C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EC4019F9-1102-F352-48CD-189A3FC0393C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7698,7 +7709,7 @@
           <xdr:cNvPr id="3426368" name="Line 74">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FC979E4-50F6-6D7A-2926-44649FAF462C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FC979E4-50F6-6D7A-2926-44649FAF462C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7738,7 +7749,7 @@
           <xdr:cNvPr id="3426369" name="Line 75">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0A1BF8B-5026-0FED-FA74-61A298124600}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E0A1BF8B-5026-0FED-FA74-61A298124600}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7777,7 +7788,7 @@
           <xdr:cNvPr id="3426370" name="Line 76">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC9CAA3-1FEF-C1A2-385F-7806B57BF1DF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EBC9CAA3-1FEF-C1A2-385F-7806B57BF1DF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7817,7 +7828,7 @@
           <xdr:cNvPr id="3426371" name="Freeform 77" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C0E6CD3-17D4-A128-7D61-BFE007FDCAE9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C0E6CD3-17D4-A128-7D61-BFE007FDCAE9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7899,7 +7910,7 @@
           <xdr:cNvPr id="3426372" name="Oval 78" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90829CD4-EB5E-B81B-0452-04EC1271C954}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{90829CD4-EB5E-B81B-0452-04EC1271C954}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7942,7 +7953,7 @@
           <xdr:cNvPr id="3426373" name="Freeform 79">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9A8B62-405D-1800-F4A8-94DCBC2DA8BC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D9A8B62-405D-1800-F4A8-94DCBC2DA8BC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8022,7 +8033,7 @@
           <xdr:cNvPr id="3426374" name="Line 80">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC2518C-1B81-F7C2-591C-3B61BF7F77AA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EEC2518C-1B81-F7C2-591C-3B61BF7F77AA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8061,7 +8072,7 @@
           <xdr:cNvPr id="3426375" name="Line 81">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDA586C-1B9D-D9FD-0169-AEEF933D9CCE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DBDA586C-1B9D-D9FD-0169-AEEF933D9CCE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8101,7 +8112,7 @@
           <xdr:cNvPr id="3426376" name="Line 82">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2A94FEE-2F75-6223-EF85-634B0A71DADD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B2A94FEE-2F75-6223-EF85-634B0A71DADD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8157,7 +8168,7 @@
         <xdr:cNvPr id="3426054" name="Group 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EE51EF4-DF1A-7DE5-A402-F9624DB6D3C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4EE51EF4-DF1A-7DE5-A402-F9624DB6D3C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8167,8 +8178,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1318260" y="5867400"/>
-          <a:ext cx="4648200" cy="1120140"/>
+          <a:off x="1461135" y="5972175"/>
+          <a:ext cx="5187315" cy="1131570"/>
           <a:chOff x="150" y="536"/>
           <a:chExt cx="540" cy="120"/>
         </a:xfrm>
@@ -8178,7 +8189,7 @@
           <xdr:cNvPr id="3426223" name="Rectangle 84" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46DA9E74-5DC3-DC5B-594E-E033691940F2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{46DA9E74-5DC3-DC5B-594E-E033691940F2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8214,7 +8225,7 @@
           <xdr:cNvPr id="3426224" name="Freeform 85">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{038DE85B-ACD4-A011-62B8-87F89CD8A9AB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{038DE85B-ACD4-A011-62B8-87F89CD8A9AB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8336,7 +8347,7 @@
           <xdr:cNvPr id="87" name="Text Box 86">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52ECB7DB-198D-BDC4-9E68-8E414F6EA2C4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{52ECB7DB-198D-BDC4-9E68-8E414F6EA2C4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8385,7 +8396,7 @@
           <xdr:cNvPr id="3426226" name="Line 87">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8252AC3-8671-9826-8925-C4B246C540D8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E8252AC3-8671-9826-8925-C4B246C540D8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8424,7 +8435,7 @@
           <xdr:cNvPr id="3426227" name="Line 88">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E17AA20-29D1-0BC7-FA2A-C872831A792E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5E17AA20-29D1-0BC7-FA2A-C872831A792E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8464,7 +8475,7 @@
           <xdr:cNvPr id="3426228" name="Line 89">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BE32EB0-732B-7310-B31B-82B933D6E057}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1BE32EB0-732B-7310-B31B-82B933D6E057}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8504,7 +8515,7 @@
           <xdr:cNvPr id="3426229" name="Line 90">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72BF71E1-4200-4F57-E8D7-BDA4E057E54B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{72BF71E1-4200-4F57-E8D7-BDA4E057E54B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8543,7 +8554,7 @@
           <xdr:cNvPr id="92" name="Text Box 91">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9CD1108-FB52-74D5-12A0-C04F7992D1C7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C9CD1108-FB52-74D5-12A0-C04F7992D1C7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8592,7 +8603,7 @@
           <xdr:cNvPr id="93" name="Text Box 92">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1DE41A9-32F5-6F9D-1ABE-32F99068BF85}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F1DE41A9-32F5-6F9D-1ABE-32F99068BF85}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8641,7 +8652,7 @@
           <xdr:cNvPr id="3426232" name="Oval 93" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6864B039-C9F6-DE9F-6172-F64F68759CEC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6864B039-C9F6-DE9F-6172-F64F68759CEC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8677,7 +8688,7 @@
           <xdr:cNvPr id="3426233" name="Oval 94">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2801247-BF8F-EDD4-2C50-0DAEFBC6078E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2801247-BF8F-EDD4-2C50-0DAEFBC6078E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8711,7 +8722,7 @@
           <xdr:cNvPr id="96" name="Text Box 95">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01E2D569-ECD2-5995-191A-8F6FB01250A6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{01E2D569-ECD2-5995-191A-8F6FB01250A6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8772,7 +8783,7 @@
           <xdr:cNvPr id="3426235" name="Line 96">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DB60D59-6F3A-6685-2D52-3799EB16040D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0DB60D59-6F3A-6685-2D52-3799EB16040D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8811,7 +8822,7 @@
           <xdr:cNvPr id="3426236" name="Line 97">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B612424-6BB9-8201-19F0-3C902518092D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4B612424-6BB9-8201-19F0-3C902518092D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8850,7 +8861,7 @@
           <xdr:cNvPr id="3426237" name="Line 98">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6395BB3-E5CC-7ECF-E095-A78FDB29A60D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C6395BB3-E5CC-7ECF-E095-A78FDB29A60D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8889,7 +8900,7 @@
           <xdr:cNvPr id="3426238" name="Line 99">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{790F8A3F-FF8F-06BB-C9A4-316245040E76}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{790F8A3F-FF8F-06BB-C9A4-316245040E76}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8928,7 +8939,7 @@
           <xdr:cNvPr id="3426239" name="Arc 100">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41D7A27F-C0D8-B8ED-A432-256A4DB48132}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{41D7A27F-C0D8-B8ED-A432-256A4DB48132}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9026,7 +9037,7 @@
           <xdr:cNvPr id="3426240" name="Arc 101">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E79F42B-1BED-4521-812B-EEF266EC90A1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2E79F42B-1BED-4521-812B-EEF266EC90A1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9124,7 +9135,7 @@
           <xdr:cNvPr id="3426241" name="Arc 102">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54F8C81-9478-3D21-9B59-CAF412ADD8D6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F54F8C81-9478-3D21-9B59-CAF412ADD8D6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9222,7 +9233,7 @@
           <xdr:cNvPr id="3426242" name="Arc 103">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87A12D66-1305-1365-423D-EF0C73087BC2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{87A12D66-1305-1365-423D-EF0C73087BC2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9320,7 +9331,7 @@
           <xdr:cNvPr id="3426243" name="Freeform 104">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA86188-1C16-A505-4E71-306F3792CBB2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EFA86188-1C16-A505-4E71-306F3792CBB2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9412,7 +9423,7 @@
           <xdr:cNvPr id="3426244" name="Freeform 105">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA988642-037F-ACFC-63A9-9ED14E419620}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DA988642-037F-ACFC-63A9-9ED14E419620}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9521,7 +9532,7 @@
           <xdr:cNvPr id="3426245" name="Rectangle 106" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA5D6BF-DAF1-881F-E2D6-69DA02384F2C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4BA5D6BF-DAF1-881F-E2D6-69DA02384F2C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9557,7 +9568,7 @@
           <xdr:cNvPr id="3426246" name="Rectangle 107" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D04E6B-F17F-EEDE-1276-1CE43C75CF40}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E1D04E6B-F17F-EEDE-1276-1CE43C75CF40}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9593,7 +9604,7 @@
           <xdr:cNvPr id="3426247" name="Line 108">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA7D1EB9-3A3D-A6B2-3157-B6B0D0717B87}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA7D1EB9-3A3D-A6B2-3157-B6B0D0717B87}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9632,7 +9643,7 @@
           <xdr:cNvPr id="3426248" name="Freeform 109">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCA62FFD-6FA3-B517-22EC-90FA76D41FE1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BCA62FFD-6FA3-B517-22EC-90FA76D41FE1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9719,7 +9730,7 @@
           <xdr:cNvPr id="3426249" name="Freeform 110" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA348F30-0FBF-5AB4-4953-B7D5DF46B6C6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA348F30-0FBF-5AB4-4953-B7D5DF46B6C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9824,7 +9835,7 @@
           <xdr:cNvPr id="3426250" name="Line 111">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B320389-4457-5DE4-7F2F-720CBB1AC17E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5B320389-4457-5DE4-7F2F-720CBB1AC17E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9864,7 +9875,7 @@
           <xdr:cNvPr id="3426251" name="Line 112">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27582639-D742-E655-FB57-09B0B2D29342}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27582639-D742-E655-FB57-09B0B2D29342}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9904,7 +9915,7 @@
           <xdr:cNvPr id="3426252" name="Freeform 113">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50D5212A-E377-ADF8-9C4B-744C36491BB6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{50D5212A-E377-ADF8-9C4B-744C36491BB6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10151,7 +10162,7 @@
           <xdr:cNvPr id="115" name="Text Box 114">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{303B1D54-E961-1A56-D4EE-70AC0D694145}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{303B1D54-E961-1A56-D4EE-70AC0D694145}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10212,7 +10223,7 @@
           <xdr:cNvPr id="3426254" name="Line 115">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B519D1CB-112B-937C-D406-7CAE32C61FBE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B519D1CB-112B-937C-D406-7CAE32C61FBE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10251,7 +10262,7 @@
           <xdr:cNvPr id="3426255" name="Line 116">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CCE304-C76A-F586-08C6-613FD1D607F9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{88CCE304-C76A-F586-08C6-613FD1D607F9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10291,7 +10302,7 @@
           <xdr:cNvPr id="3426256" name="Line 117">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E90F25B-F483-DF3A-40DC-8C4A6D00B07C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5E90F25B-F483-DF3A-40DC-8C4A6D00B07C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10331,7 +10342,7 @@
           <xdr:cNvPr id="3426257" name="Oval 118" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B85C85-F0EB-005D-2819-EC72579AA5C9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2B85C85-F0EB-005D-2819-EC72579AA5C9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10367,7 +10378,7 @@
           <xdr:cNvPr id="3426258" name="Oval 119">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D317AF-3380-FA25-1A4D-40403A2272AB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B1D317AF-3380-FA25-1A4D-40403A2272AB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10401,7 +10412,7 @@
           <xdr:cNvPr id="3426259" name="Freeform 120">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1EF327A-9D45-0B1A-3308-4B005F01729B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D1EF327A-9D45-0B1A-3308-4B005F01729B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10488,7 +10499,7 @@
           <xdr:cNvPr id="3426260" name="Line 121">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F00123A-B8C7-1EA1-2C3C-5503615BBB19}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5F00123A-B8C7-1EA1-2C3C-5503615BBB19}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10527,7 +10538,7 @@
           <xdr:cNvPr id="3426261" name="Line 122">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20635BB3-B634-F06A-7630-DDF038A3DDEB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{20635BB3-B634-F06A-7630-DDF038A3DDEB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10567,7 +10578,7 @@
           <xdr:cNvPr id="3426262" name="Line 123">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A8A054-5C75-4AF5-6887-81F5D2A3EF11}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{91A8A054-5C75-4AF5-6887-81F5D2A3EF11}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10607,7 +10618,7 @@
           <xdr:cNvPr id="125" name="Text Box 124">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E34E6B31-3F11-6D7C-186C-3A0D563B53CC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E34E6B31-3F11-6D7C-186C-3A0D563B53CC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10668,7 +10679,7 @@
           <xdr:cNvPr id="126" name="Text Box 125">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35324F7-5B95-CEAF-3E16-F6D575331BA2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D35324F7-5B95-CEAF-3E16-F6D575331BA2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10729,7 +10740,7 @@
           <xdr:cNvPr id="3426265" name="Freeform 126">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E800F296-CB02-E588-DD1D-98F2557E1C81}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E800F296-CB02-E588-DD1D-98F2557E1C81}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10821,7 +10832,7 @@
           <xdr:cNvPr id="3426266" name="Freeform 127">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3032F14C-6BD1-2E3E-E9D2-3FC9E4816A1F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3032F14C-6BD1-2E3E-E9D2-3FC9E4816A1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10930,7 +10941,7 @@
           <xdr:cNvPr id="3426267" name="Rectangle 128" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30CC88B7-E076-73F2-DA33-936D2D27D867}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{30CC88B7-E076-73F2-DA33-936D2D27D867}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10966,7 +10977,7 @@
           <xdr:cNvPr id="3426268" name="Rectangle 129" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEEBF1A-81C7-F1A3-1879-F27AB8C93646}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5CEEBF1A-81C7-F1A3-1879-F27AB8C93646}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11002,7 +11013,7 @@
           <xdr:cNvPr id="3426269" name="Freeform 130">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DDA93EF-66B7-5E36-EA64-4B6E8D63E2E0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8DDA93EF-66B7-5E36-EA64-4B6E8D63E2E0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11089,7 +11100,7 @@
           <xdr:cNvPr id="3426270" name="Freeform 131" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{173CE644-B2D6-6E6C-B0B1-A0E165E738ED}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{173CE644-B2D6-6E6C-B0B1-A0E165E738ED}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11194,7 +11205,7 @@
           <xdr:cNvPr id="3426271" name="Line 132">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBBFE3D5-F6AB-D07B-E7BE-6DBA9050F28C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DBBFE3D5-F6AB-D07B-E7BE-6DBA9050F28C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11234,7 +11245,7 @@
           <xdr:cNvPr id="3426272" name="Line 133">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B6072E8-7679-B4B4-C2B7-54AC9F151BEB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4B6072E8-7679-B4B4-C2B7-54AC9F151BEB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11274,7 +11285,7 @@
           <xdr:cNvPr id="3426273" name="Freeform 134">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BE60EB1-3CB2-B621-3733-40070652F20D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5BE60EB1-3CB2-B621-3733-40070652F20D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11521,7 +11532,7 @@
           <xdr:cNvPr id="136" name="Text Box 135">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0515C86D-CB2F-6788-3040-E98ECE5BDCC5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0515C86D-CB2F-6788-3040-E98ECE5BDCC5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11582,7 +11593,7 @@
           <xdr:cNvPr id="3426275" name="Freeform 136">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{757E0CB5-825D-4914-D2D7-F917BA41425E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{757E0CB5-825D-4914-D2D7-F917BA41425E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11704,7 +11715,7 @@
           <xdr:cNvPr id="3426276" name="Freeform 137">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1E585E-2894-6C8B-E498-9542EBCB8890}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3F1E585E-2894-6C8B-E498-9542EBCB8890}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11826,7 +11837,7 @@
           <xdr:cNvPr id="3426277" name="Line 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{613FEA6E-C272-A597-76A1-16FA0220EBF6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{613FEA6E-C272-A597-76A1-16FA0220EBF6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11865,7 +11876,7 @@
           <xdr:cNvPr id="3426278" name="Line 139">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916E7F06-7C05-04BC-EEDC-AE8BC76707D7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{916E7F06-7C05-04BC-EEDC-AE8BC76707D7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11905,7 +11916,7 @@
           <xdr:cNvPr id="3426279" name="Line 140">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61E23609-F7D5-8963-F580-2351D3C83B51}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{61E23609-F7D5-8963-F580-2351D3C83B51}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11945,7 +11956,7 @@
           <xdr:cNvPr id="3426280" name="Line 141">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12FF408C-BD85-ECB7-9915-D0DCBF137BBF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{12FF408C-BD85-ECB7-9915-D0DCBF137BBF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11984,7 +11995,7 @@
           <xdr:cNvPr id="3426281" name="Oval 142" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB1B4402-D5CC-E1E8-D10A-778AE87C7D24}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EB1B4402-D5CC-E1E8-D10A-778AE87C7D24}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12020,7 +12031,7 @@
           <xdr:cNvPr id="3426282" name="Oval 143">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F3F4C6A-C8C9-D374-3FB3-36D3A6975273}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4F3F4C6A-C8C9-D374-3FB3-36D3A6975273}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12054,7 +12065,7 @@
           <xdr:cNvPr id="3426283" name="Line 144">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D25896E-F5F4-80A3-151F-D21EFC33A7E4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9D25896E-F5F4-80A3-151F-D21EFC33A7E4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12093,7 +12104,7 @@
           <xdr:cNvPr id="3426284" name="Line 145">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{726083FD-3151-E2D8-1300-7337EBC41497}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{726083FD-3151-E2D8-1300-7337EBC41497}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12133,7 +12144,7 @@
           <xdr:cNvPr id="3426285" name="Freeform 146">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75230C73-ED7C-05AA-1823-63A74DDACECC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{75230C73-ED7C-05AA-1823-63A74DDACECC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12225,7 +12236,7 @@
           <xdr:cNvPr id="3426286" name="Freeform 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4950B46-5821-6A65-A5F1-64712537732F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A4950B46-5821-6A65-A5F1-64712537732F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12334,7 +12345,7 @@
           <xdr:cNvPr id="3426287" name="Rectangle 148" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC7FEDE1-0B57-1583-C2F6-25BA209B843D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FC7FEDE1-0B57-1583-C2F6-25BA209B843D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12370,7 +12381,7 @@
           <xdr:cNvPr id="3426288" name="Rectangle 149" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA9FCDF6-79B4-614D-36EE-3DD7307E4D12}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EA9FCDF6-79B4-614D-36EE-3DD7307E4D12}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12406,7 +12417,7 @@
           <xdr:cNvPr id="3426289" name="Freeform 150">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F524231-44F6-5DB6-D609-FEBBC3F1582A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7F524231-44F6-5DB6-D609-FEBBC3F1582A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12493,7 +12504,7 @@
           <xdr:cNvPr id="3426290" name="Freeform 151" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D4FB9B1-016C-8745-2D95-83C4B8EDE198}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D4FB9B1-016C-8745-2D95-83C4B8EDE198}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12598,7 +12609,7 @@
           <xdr:cNvPr id="3426291" name="Line 152">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{386A7781-D34D-D465-1A3D-EB1641146E5A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{386A7781-D34D-D465-1A3D-EB1641146E5A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12638,7 +12649,7 @@
           <xdr:cNvPr id="3426292" name="Line 153">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D5EBAEB-6484-8A00-89FE-66271E2DB7E2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D5EBAEB-6484-8A00-89FE-66271E2DB7E2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12678,7 +12689,7 @@
           <xdr:cNvPr id="3426293" name="Freeform 154">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96DA03F2-44DB-8656-7C69-BF63FE9C7FCC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{96DA03F2-44DB-8656-7C69-BF63FE9C7FCC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12925,7 +12936,7 @@
           <xdr:cNvPr id="3426294" name="Freeform 155">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DFA85E1-387E-0134-0518-D17AC42F7C60}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DFA85E1-387E-0134-0518-D17AC42F7C60}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13047,7 +13058,7 @@
           <xdr:cNvPr id="3426295" name="Line 156">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4142565B-7175-408E-2D38-21FD09DC3BC7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4142565B-7175-408E-2D38-21FD09DC3BC7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13086,7 +13097,7 @@
           <xdr:cNvPr id="3426296" name="Freeform 157">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCFE9EB7-7FB8-5E60-4BDC-6BA968FC8A7D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BCFE9EB7-7FB8-5E60-4BDC-6BA968FC8A7D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13173,7 +13184,7 @@
           <xdr:cNvPr id="3426297" name="Line 158">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E95A4C3-3988-3863-9E31-577559B373CC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E95A4C3-3988-3863-9E31-577559B373CC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13213,7 +13224,7 @@
           <xdr:cNvPr id="160" name="Text Box 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1225691D-88F9-EB7C-56AD-21C5C34F2601}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1225691D-88F9-EB7C-56AD-21C5C34F2601}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13274,7 +13285,7 @@
           <xdr:cNvPr id="3426299" name="Line 160">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3081FA7-1246-0AD4-C831-2AD5A26CEDCD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B3081FA7-1246-0AD4-C831-2AD5A26CEDCD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13313,7 +13324,7 @@
           <xdr:cNvPr id="3426300" name="Line 161">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C98BE2A5-9661-EFE8-4F07-946A693E013F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C98BE2A5-9661-EFE8-4F07-946A693E013F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13353,7 +13364,7 @@
           <xdr:cNvPr id="3426301" name="Line 162">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74752195-E220-955E-D73D-2D0DD58B300A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{74752195-E220-955E-D73D-2D0DD58B300A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13409,7 +13420,7 @@
         <xdr:cNvPr id="3426056" name="Line 164">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{298FB368-60B5-7A74-D0A6-28E7084D160D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{298FB368-60B5-7A74-D0A6-28E7084D160D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13463,7 +13474,7 @@
         <xdr:cNvPr id="3426057" name="Line 165">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FDFDBA6-80D9-6026-81CB-0369EF638049}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FDFDBA6-80D9-6026-81CB-0369EF638049}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13517,7 +13528,7 @@
         <xdr:cNvPr id="3426058" name="Line 206">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{454E0702-04AC-96C2-4A1E-25C77E8978A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{454E0702-04AC-96C2-4A1E-25C77E8978A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13571,7 +13582,7 @@
         <xdr:cNvPr id="3426059" name="Line 207">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E065500-0320-4368-7FC4-056DDEAE2BAC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2E065500-0320-4368-7FC4-056DDEAE2BAC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13625,7 +13636,7 @@
         <xdr:cNvPr id="169" name="Text Box 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A363919A-F1DE-636D-84E1-B6B5595380DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A363919A-F1DE-636D-84E1-B6B5595380DF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13701,7 +13712,7 @@
         <xdr:cNvPr id="170" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C071E74A-6EE5-C4CC-8C18-58EE6F589C31}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C071E74A-6EE5-C4CC-8C18-58EE6F589C31}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13777,7 +13788,7 @@
         <xdr:cNvPr id="173" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ABD7379-64FE-1FC5-CDED-99C3BA6AE5AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3ABD7379-64FE-1FC5-CDED-99C3BA6AE5AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13853,7 +13864,7 @@
         <xdr:cNvPr id="174" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042D797F-DB9F-F39F-FF6C-AE47842C3C68}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{042D797F-DB9F-F39F-FF6C-AE47842C3C68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13929,7 +13940,7 @@
         <xdr:cNvPr id="3426064" name="Group 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3D5C0E-B65A-1908-8334-E38DD303E343}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1A3D5C0E-B65A-1908-8334-E38DD303E343}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13939,8 +13950,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1112520" y="7094220"/>
-          <a:ext cx="4853940" cy="960120"/>
+          <a:off x="1240155" y="7210425"/>
+          <a:ext cx="5408295" cy="971550"/>
           <a:chOff x="126" y="704"/>
           <a:chExt cx="571" cy="102"/>
         </a:xfrm>
@@ -13950,7 +13961,7 @@
           <xdr:cNvPr id="3426148" name="Oval 8" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91EDA04-9AFA-FCB4-7487-49A750481F81}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D91EDA04-9AFA-FCB4-7487-49A750481F81}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13986,7 +13997,7 @@
           <xdr:cNvPr id="3426149" name="Oval 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD142D74-9A76-5CFB-BB4E-27B6632877FD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BD142D74-9A76-5CFB-BB4E-27B6632877FD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14020,7 +14031,7 @@
           <xdr:cNvPr id="3426150" name="Freeform 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B5BE5DB-9681-5FEB-3E4A-477BAEFE1692}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3B5BE5DB-9681-5FEB-3E4A-477BAEFE1692}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14106,7 +14117,7 @@
           <xdr:cNvPr id="179" name="Text Box 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4EBE38-ED01-8DC7-FB41-A9B377E75319}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C4EBE38-ED01-8DC7-FB41-A9B377E75319}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14185,7 +14196,7 @@
           <xdr:cNvPr id="3426152" name="Line 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5E7929-4EFC-A07E-70BF-0F0D81076487}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3A5E7929-4EFC-A07E-70BF-0F0D81076487}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14224,7 +14235,7 @@
           <xdr:cNvPr id="3426153" name="Line 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A79D3466-0FA5-617C-B9F2-10B0290AF247}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A79D3466-0FA5-617C-B9F2-10B0290AF247}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14264,7 +14275,7 @@
           <xdr:cNvPr id="3426154" name="Line 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B21DC6-19BB-9C07-8C55-6AC278C80E9F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{43B21DC6-19BB-9C07-8C55-6AC278C80E9F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14304,7 +14315,7 @@
           <xdr:cNvPr id="3426155" name="Freeform 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5146E7-CE65-A680-5BBC-EB98D92E7772}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BE5146E7-CE65-A680-5BBC-EB98D92E7772}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14395,7 +14406,7 @@
           <xdr:cNvPr id="3426156" name="Freeform 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D936D30-889F-19D6-2F9B-8177273360BF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7D936D30-889F-19D6-2F9B-8177273360BF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14503,7 +14514,7 @@
           <xdr:cNvPr id="3426157" name="Rectangle 17" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DCBF7BB-FD2A-BC8F-36A1-89E7E411ECCD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6DCBF7BB-FD2A-BC8F-36A1-89E7E411ECCD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14539,7 +14550,7 @@
           <xdr:cNvPr id="3426158" name="Rectangle 18" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCB9900D-FC6A-C20C-8A3C-EAE454216A57}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCB9900D-FC6A-C20C-8A3C-EAE454216A57}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14575,7 +14586,7 @@
           <xdr:cNvPr id="3426159" name="Freeform 19">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988001A1-1BE2-E3F2-CFC1-668EC9FDDE3E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{988001A1-1BE2-E3F2-CFC1-668EC9FDDE3E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14732,7 +14743,7 @@
           <xdr:cNvPr id="188" name="Text Box 20">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57DFAF6-2B59-2AC2-D3DF-A91DD23334B5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C57DFAF6-2B59-2AC2-D3DF-A91DD23334B5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14811,7 +14822,7 @@
           <xdr:cNvPr id="3426161" name="Line 21">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{499E48F0-C3F5-D320-767A-6DDF4AD796FA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{499E48F0-C3F5-D320-767A-6DDF4AD796FA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14850,7 +14861,7 @@
           <xdr:cNvPr id="3426162" name="Line 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31B03450-B821-BA83-DDD9-CA471563E476}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{31B03450-B821-BA83-DDD9-CA471563E476}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14889,7 +14900,7 @@
           <xdr:cNvPr id="3426163" name="Line 23">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7500CA25-B22E-516C-17AF-0E0B3A47F4D1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7500CA25-B22E-516C-17AF-0E0B3A47F4D1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14929,7 +14940,7 @@
           <xdr:cNvPr id="3426164" name="Line 24">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4F0D4A-91D3-2AB6-CB71-5980A345EC0B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4C4F0D4A-91D3-2AB6-CB71-5980A345EC0B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14969,7 +14980,7 @@
           <xdr:cNvPr id="3426165" name="Freeform 25">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3EFD27E-C82E-DCF3-B66A-50BF7E845BEC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A3EFD27E-C82E-DCF3-B66A-50BF7E845BEC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15055,7 +15066,7 @@
           <xdr:cNvPr id="3426166" name="Freeform 26" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B96CC863-465D-4569-C562-8494D826D9E8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B96CC863-465D-4569-C562-8494D826D9E8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15159,7 +15170,7 @@
           <xdr:cNvPr id="3426167" name="Oval 27" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A894F6E-41F4-1F4C-62AF-11FB7772FA35}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2A894F6E-41F4-1F4C-62AF-11FB7772FA35}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15195,7 +15206,7 @@
           <xdr:cNvPr id="3426168" name="Oval 28">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F45C8D-78CF-E907-CB4B-866B50A8D9F8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37F45C8D-78CF-E907-CB4B-866B50A8D9F8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15229,7 +15240,7 @@
           <xdr:cNvPr id="3426169" name="Freeform 29">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820E49E2-A42E-F74B-B8BB-8FFCC2B1FA1F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{820E49E2-A42E-F74B-B8BB-8FFCC2B1FA1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15315,7 +15326,7 @@
           <xdr:cNvPr id="198" name="Text Box 30">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B90D0E1-44A4-B12B-EB5C-6E16D82566ED}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3B90D0E1-44A4-B12B-EB5C-6E16D82566ED}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15394,7 +15405,7 @@
           <xdr:cNvPr id="3426171" name="Line 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552E979C-83AC-5636-A824-B6D2D7721188}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{552E979C-83AC-5636-A824-B6D2D7721188}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15433,7 +15444,7 @@
           <xdr:cNvPr id="3426172" name="Line 32">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B48FAFD4-AEA1-6C73-32B5-CEB20F041E23}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B48FAFD4-AEA1-6C73-32B5-CEB20F041E23}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15473,7 +15484,7 @@
           <xdr:cNvPr id="3426173" name="Line 33">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8050A2BB-1EE1-1EFF-49E3-075574C2FF72}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8050A2BB-1EE1-1EFF-49E3-075574C2FF72}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15513,7 +15524,7 @@
           <xdr:cNvPr id="3426174" name="Freeform 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA991A8D-FB0F-7361-25D3-B1A48A9B974B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DA991A8D-FB0F-7361-25D3-B1A48A9B974B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15604,7 +15615,7 @@
           <xdr:cNvPr id="3426175" name="Freeform 35">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634D408A-C49D-9A36-7E4A-8ABE205CCBAE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{634D408A-C49D-9A36-7E4A-8ABE205CCBAE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15712,7 +15723,7 @@
           <xdr:cNvPr id="3426176" name="Rectangle 36" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4BD6EAD-02BC-6816-4C4E-326260D20CC4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F4BD6EAD-02BC-6816-4C4E-326260D20CC4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15748,7 +15759,7 @@
           <xdr:cNvPr id="3426177" name="Rectangle 37" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CD9FB71-8DE1-7BC0-B29E-76E1103314E4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3CD9FB71-8DE1-7BC0-B29E-76E1103314E4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15784,7 +15795,7 @@
           <xdr:cNvPr id="3426178" name="Freeform 38">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC99814-8A74-CA8A-F037-1CC21532747E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FEC99814-8A74-CA8A-F037-1CC21532747E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15941,7 +15952,7 @@
           <xdr:cNvPr id="207" name="Text Box 39">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2E7B2F-32B8-45BE-EB96-0478783E3C62}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FF2E7B2F-32B8-45BE-EB96-0478783E3C62}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16020,7 +16031,7 @@
           <xdr:cNvPr id="3426180" name="Line 40">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E564B577-DC7B-72A7-B2F8-DB7C973EF291}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E564B577-DC7B-72A7-B2F8-DB7C973EF291}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16059,7 +16070,7 @@
           <xdr:cNvPr id="3426181" name="Line 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B4708D1-DB37-05E1-643F-28A77099B9DE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6B4708D1-DB37-05E1-643F-28A77099B9DE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16098,7 +16109,7 @@
           <xdr:cNvPr id="3426182" name="Freeform 42">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0559A0DF-1060-E40E-B19A-5A6C420F5D67}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0559A0DF-1060-E40E-B19A-5A6C420F5D67}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16184,7 +16195,7 @@
           <xdr:cNvPr id="3426183" name="Freeform 43" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3C0E6F-7415-983D-1BC0-C193AB96CDF0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DD3C0E6F-7415-983D-1BC0-C193AB96CDF0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16306,7 +16317,7 @@
           <xdr:cNvPr id="3426184" name="Line 44">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3F4C4CB-1766-0B7C-437E-B0D939554F7B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F3F4C4CB-1766-0B7C-437E-B0D939554F7B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16346,7 +16357,7 @@
           <xdr:cNvPr id="3426185" name="Line 45">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B33E89C3-E960-CA31-5DDE-2415A19972DC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B33E89C3-E960-CA31-5DDE-2415A19972DC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16386,7 +16397,7 @@
           <xdr:cNvPr id="3426186" name="Freeform 46">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1860B16-0F15-019A-9E07-0AF42C9E0C08}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F1860B16-0F15-019A-9E07-0AF42C9E0C08}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16507,7 +16518,7 @@
           <xdr:cNvPr id="3426187" name="Freeform 47">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{592860B5-2699-8E38-461C-247647098588}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{592860B5-2699-8E38-461C-247647098588}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16628,7 +16639,7 @@
           <xdr:cNvPr id="3426188" name="Oval 48" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7A06C5E-02EC-B394-6F1D-C4D1DFE6923E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C7A06C5E-02EC-B394-6F1D-C4D1DFE6923E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16664,7 +16675,7 @@
           <xdr:cNvPr id="3426189" name="Oval 49">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80BC19A1-A2CF-AD2B-0444-894ABC258EDC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{80BC19A1-A2CF-AD2B-0444-894ABC258EDC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16698,7 +16709,7 @@
           <xdr:cNvPr id="3426190" name="Line 50">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10882EC4-581F-E88B-38BE-FA600845ABBD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{10882EC4-581F-E88B-38BE-FA600845ABBD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16737,7 +16748,7 @@
           <xdr:cNvPr id="3426191" name="Line 51">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{339EC3E4-A176-F1A4-E29F-BA56E57ABDA0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{339EC3E4-A176-F1A4-E29F-BA56E57ABDA0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16777,7 +16788,7 @@
           <xdr:cNvPr id="3426192" name="Freeform 52">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC904DD7-C682-E58A-D051-30D382C932ED}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EC904DD7-C682-E58A-D051-30D382C932ED}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16868,7 +16879,7 @@
           <xdr:cNvPr id="3426193" name="Freeform 53">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2A25EAC-D696-01ED-4346-9087D773B9FD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2A25EAC-D696-01ED-4346-9087D773B9FD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16976,7 +16987,7 @@
           <xdr:cNvPr id="3426194" name="Rectangle 54" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F14B252-9101-390E-49BC-ADC0947FB40B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2F14B252-9101-390E-49BC-ADC0947FB40B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17012,7 +17023,7 @@
           <xdr:cNvPr id="3426195" name="Line 55">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8996386E-7EB6-37D4-5578-51480BC33642}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8996386E-7EB6-37D4-5578-51480BC33642}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17052,7 +17063,7 @@
           <xdr:cNvPr id="3426196" name="Line 56">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{300A8D23-4513-FAD2-0FCE-D6E6379549CF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{300A8D23-4513-FAD2-0FCE-D6E6379549CF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17092,7 +17103,7 @@
           <xdr:cNvPr id="3426197" name="Line 57">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5C2C53-41EE-EE56-0303-0218B3C25BC2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1A5C2C53-41EE-EE56-0303-0218B3C25BC2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17131,7 +17142,7 @@
           <xdr:cNvPr id="3426198" name="Line 58">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFA70F51-47CB-F84B-7259-B815641DB569}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DFA70F51-47CB-F84B-7259-B815641DB569}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17170,7 +17181,7 @@
           <xdr:cNvPr id="3426199" name="Line 59">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A504A8E-CB45-69EB-8B11-F97CBF3E20E0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A504A8E-CB45-69EB-8B11-F97CBF3E20E0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17210,7 +17221,7 @@
           <xdr:cNvPr id="3426200" name="Freeform 60" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABE9C3C7-4F02-46FF-294E-C9BD4D4D6C28}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ABE9C3C7-4F02-46FF-294E-C9BD4D4D6C28}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17291,7 +17302,7 @@
           <xdr:cNvPr id="3426201" name="Oval 61" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8677084-9414-322A-86DA-D8056E1DB481}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F8677084-9414-322A-86DA-D8056E1DB481}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17334,7 +17345,7 @@
           <xdr:cNvPr id="3426202" name="Freeform 62">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C8CEB54-5A1C-C8A5-4871-6C3BD85235C9}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C8CEB54-5A1C-C8A5-4871-6C3BD85235C9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17413,7 +17424,7 @@
           <xdr:cNvPr id="3426203" name="Line 63">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2D575F2-8B18-4E32-7CB0-06F55B9AF961}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2D575F2-8B18-4E32-7CB0-06F55B9AF961}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17452,7 +17463,7 @@
           <xdr:cNvPr id="3426204" name="Line 64">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D34BE1F-5462-0D3F-E019-A29CED2D69CB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9D34BE1F-5462-0D3F-E019-A29CED2D69CB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17492,7 +17503,7 @@
           <xdr:cNvPr id="3426205" name="Line 65">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF3D8E12-F817-23A1-4B40-8E42EE9CA273}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FF3D8E12-F817-23A1-4B40-8E42EE9CA273}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17532,7 +17543,7 @@
           <xdr:cNvPr id="3426206" name="Oval 66" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D783B4-CBC0-7462-9F92-12617D2F6C00}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D783B4-CBC0-7462-9F92-12617D2F6C00}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17568,7 +17579,7 @@
           <xdr:cNvPr id="3426207" name="Oval 67">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B7F7F6E-2898-3B4B-0070-14F0522F8D36}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0B7F7F6E-2898-3B4B-0070-14F0522F8D36}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17602,7 +17613,7 @@
           <xdr:cNvPr id="3426208" name="Line 68">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A0FE706-1FE1-811F-EEE9-259CE9A1957A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4A0FE706-1FE1-811F-EEE9-259CE9A1957A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17641,7 +17652,7 @@
           <xdr:cNvPr id="3426209" name="Line 69">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71459369-8327-DF22-B87B-52187EBD146D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{71459369-8327-DF22-B87B-52187EBD146D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17681,7 +17692,7 @@
           <xdr:cNvPr id="3426210" name="Freeform 70">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF7F07F3-816B-47C4-187F-E5DD65030C67}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FF7F07F3-816B-47C4-187F-E5DD65030C67}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17772,7 +17783,7 @@
           <xdr:cNvPr id="3426211" name="Freeform 71">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E8B2A10-1896-09EF-3B5C-83E9580D53D7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E8B2A10-1896-09EF-3B5C-83E9580D53D7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17880,7 +17891,7 @@
           <xdr:cNvPr id="3426212" name="Rectangle 72" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBF30957-20D8-E176-8CC4-131F51136BDE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CBF30957-20D8-E176-8CC4-131F51136BDE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17916,7 +17927,7 @@
           <xdr:cNvPr id="3426213" name="Line 73">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DE060E-4059-C3C2-8105-9B1389B2CDA5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{82DE060E-4059-C3C2-8105-9B1389B2CDA5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17956,7 +17967,7 @@
           <xdr:cNvPr id="3426214" name="Line 74">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B444B81E-6878-4C96-A8D7-64715F1D9B64}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B444B81E-6878-4C96-A8D7-64715F1D9B64}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17996,7 +18007,7 @@
           <xdr:cNvPr id="3426215" name="Line 75">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F9AB64B-AF9A-AEC4-4E57-9430909D642E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6F9AB64B-AF9A-AEC4-4E57-9430909D642E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18035,7 +18046,7 @@
           <xdr:cNvPr id="3426216" name="Line 76">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F93C76-0E44-E9F9-2245-68DED5AC6E1B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27F93C76-0E44-E9F9-2245-68DED5AC6E1B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18075,7 +18086,7 @@
           <xdr:cNvPr id="3426217" name="Freeform 77" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E4CECF-AF58-6EFA-E680-DF1D596B706B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F6E4CECF-AF58-6EFA-E680-DF1D596B706B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18156,7 +18167,7 @@
           <xdr:cNvPr id="3426218" name="Oval 78" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E729013D-7100-3A84-0BB2-77B7C0E3EBBC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E729013D-7100-3A84-0BB2-77B7C0E3EBBC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18199,7 +18210,7 @@
           <xdr:cNvPr id="3426219" name="Freeform 79">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDEECB7-4403-8FB9-D388-20C3AC032D4E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7BDEECB7-4403-8FB9-D388-20C3AC032D4E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18278,7 +18289,7 @@
           <xdr:cNvPr id="3426220" name="Line 80">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDE77B8D-8142-E5B2-74BA-85BC6A425D68}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FDE77B8D-8142-E5B2-74BA-85BC6A425D68}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18317,7 +18328,7 @@
           <xdr:cNvPr id="3426221" name="Line 81">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2493C94-E508-22E5-222A-BAA9F556FAA4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B2493C94-E508-22E5-222A-BAA9F556FAA4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18357,7 +18368,7 @@
           <xdr:cNvPr id="3426222" name="Line 82">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF11FAA-1F44-9B14-DEE7-582334C50D87}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DF11FAA-1F44-9B14-DEE7-582334C50D87}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18413,7 +18424,7 @@
         <xdr:cNvPr id="3426065" name="Group 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{876EDBA7-CB63-3146-2069-5DFB00917133}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{876EDBA7-CB63-3146-2069-5DFB00917133}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18423,8 +18434,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1318260" y="5867400"/>
-          <a:ext cx="4648200" cy="1120140"/>
+          <a:off x="1461135" y="5972175"/>
+          <a:ext cx="5187315" cy="1131570"/>
           <a:chOff x="150" y="536"/>
           <a:chExt cx="540" cy="120"/>
         </a:xfrm>
@@ -18434,7 +18445,7 @@
           <xdr:cNvPr id="3426069" name="Rectangle 84" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A73DB8B-B7D3-0F26-AC56-58505E932806}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8A73DB8B-B7D3-0F26-AC56-58505E932806}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18470,7 +18481,7 @@
           <xdr:cNvPr id="3426070" name="Freeform 85">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22A24246-BE5C-34F1-448A-A1B87549D0F2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{22A24246-BE5C-34F1-448A-A1B87549D0F2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18591,7 +18602,7 @@
           <xdr:cNvPr id="254" name="Text Box 86">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{059527C1-B45A-707C-8EE5-F4205DC5361B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{059527C1-B45A-707C-8EE5-F4205DC5361B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18640,7 +18651,7 @@
           <xdr:cNvPr id="3426072" name="Line 87">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C5247D-7CCF-9CE5-79CA-B0D66FBBD884}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2C5247D-7CCF-9CE5-79CA-B0D66FBBD884}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18679,7 +18690,7 @@
           <xdr:cNvPr id="3426073" name="Line 88">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF15BCF-FFA1-B751-B073-B978F25F7457}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DF15BCF-FFA1-B751-B073-B978F25F7457}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18719,7 +18730,7 @@
           <xdr:cNvPr id="3426074" name="Line 89">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D87E2B0C-E1E8-8042-B0BC-A3DC98A76D25}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D87E2B0C-E1E8-8042-B0BC-A3DC98A76D25}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18759,7 +18770,7 @@
           <xdr:cNvPr id="3426075" name="Line 90">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CDD4ACE-D1BD-9318-A4DE-24D31608EC8D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CDD4ACE-D1BD-9318-A4DE-24D31608EC8D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18798,7 +18809,7 @@
           <xdr:cNvPr id="259" name="Text Box 91">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6FE8C91-A745-137E-3C6F-7B0C5D58003F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E6FE8C91-A745-137E-3C6F-7B0C5D58003F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18847,7 +18858,7 @@
           <xdr:cNvPr id="260" name="Text Box 92">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3A0D67A-0C2D-25E9-A45B-3548A6FBEF2A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F3A0D67A-0C2D-25E9-A45B-3548A6FBEF2A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18896,7 +18907,7 @@
           <xdr:cNvPr id="3426078" name="Oval 93" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8D2BF0-80A3-4101-EF33-1CC70AD0E2D0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DF8D2BF0-80A3-4101-EF33-1CC70AD0E2D0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18932,7 +18943,7 @@
           <xdr:cNvPr id="3426079" name="Oval 94">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51273C5B-51B6-D41D-D5F3-D0C56F4428BB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{51273C5B-51B6-D41D-D5F3-D0C56F4428BB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18966,7 +18977,7 @@
           <xdr:cNvPr id="263" name="Text Box 95">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C181CF8-3F03-E011-C5BC-A155E767C534}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C181CF8-3F03-E011-C5BC-A155E767C534}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19033,7 +19044,7 @@
           <xdr:cNvPr id="3426081" name="Line 96">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFC68C92-1009-8315-DC8A-E87B2D15DF6E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BFC68C92-1009-8315-DC8A-E87B2D15DF6E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19072,7 +19083,7 @@
           <xdr:cNvPr id="3426082" name="Line 97">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65918EFA-1B81-32D7-3379-1F35FA49B029}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{65918EFA-1B81-32D7-3379-1F35FA49B029}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19111,7 +19122,7 @@
           <xdr:cNvPr id="3426083" name="Line 98">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5034D995-9EA8-F456-3F64-CDD98E08045B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5034D995-9EA8-F456-3F64-CDD98E08045B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19150,7 +19161,7 @@
           <xdr:cNvPr id="3426084" name="Line 99">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7879408F-738E-EE3D-ACDA-17E38FB4FBF1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7879408F-738E-EE3D-ACDA-17E38FB4FBF1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19189,7 +19200,7 @@
           <xdr:cNvPr id="3426085" name="Arc 100">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1998B37-8C11-CAE3-4078-F1C41C670963}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B1998B37-8C11-CAE3-4078-F1C41C670963}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19287,7 +19298,7 @@
           <xdr:cNvPr id="3426086" name="Arc 101">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4441C2C-193E-0B53-C84C-8F5F47467F6B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F4441C2C-193E-0B53-C84C-8F5F47467F6B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19385,7 +19396,7 @@
           <xdr:cNvPr id="3426087" name="Arc 102">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40494613-FBE6-65CC-6142-2A0FB9E2CA13}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{40494613-FBE6-65CC-6142-2A0FB9E2CA13}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19483,7 +19494,7 @@
           <xdr:cNvPr id="3426088" name="Arc 103">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B511D19-F1BD-F252-350E-0EC112881806}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B511D19-F1BD-F252-350E-0EC112881806}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19581,7 +19592,7 @@
           <xdr:cNvPr id="3426089" name="Freeform 104">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08EC917E-1A55-DF5E-4865-3107E4F685AC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{08EC917E-1A55-DF5E-4865-3107E4F685AC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19672,7 +19683,7 @@
           <xdr:cNvPr id="3426090" name="Freeform 105">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{306D10FE-4DF9-2321-A7EE-6E85ADF94D7C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{306D10FE-4DF9-2321-A7EE-6E85ADF94D7C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19780,7 +19791,7 @@
           <xdr:cNvPr id="3426091" name="Rectangle 106" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F9AE31-1BA0-8E51-7C7C-479636464185}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D2F9AE31-1BA0-8E51-7C7C-479636464185}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19816,7 +19827,7 @@
           <xdr:cNvPr id="3426092" name="Rectangle 107" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B5D84A-EC95-881E-B451-AA18082C1A58}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D1B5D84A-EC95-881E-B451-AA18082C1A58}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19852,7 +19863,7 @@
           <xdr:cNvPr id="3426093" name="Line 108">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B788542-D4CF-150B-72D2-1E4B72713C58}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4B788542-D4CF-150B-72D2-1E4B72713C58}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19891,7 +19902,7 @@
           <xdr:cNvPr id="3426094" name="Freeform 109">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535DD355-B86B-5FF9-0987-482AC9712AB5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{535DD355-B86B-5FF9-0987-482AC9712AB5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19977,7 +19988,7 @@
           <xdr:cNvPr id="3426095" name="Freeform 110" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A410C5FA-9345-1EE6-BC3F-FC13FB69809E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A410C5FA-9345-1EE6-BC3F-FC13FB69809E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20081,7 +20092,7 @@
           <xdr:cNvPr id="3426096" name="Line 111">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B324D3-9C33-016D-1670-AFF8AE5DB30D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{47B324D3-9C33-016D-1670-AFF8AE5DB30D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20121,7 +20132,7 @@
           <xdr:cNvPr id="3426097" name="Line 112">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD825C9E-7B34-061A-339D-E4DF60619D90}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CD825C9E-7B34-061A-339D-E4DF60619D90}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20161,7 +20172,7 @@
           <xdr:cNvPr id="3426098" name="Freeform 113">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D18D2DFF-0091-4479-D300-AF4140499F36}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D18D2DFF-0091-4479-D300-AF4140499F36}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20407,7 +20418,7 @@
           <xdr:cNvPr id="282" name="Text Box 114">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C421DD3-CA25-0095-15CB-A5642321F95A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C421DD3-CA25-0095-15CB-A5642321F95A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20474,7 +20485,7 @@
           <xdr:cNvPr id="3426100" name="Line 115">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2614C6F7-2B78-87C8-18F4-C24F5FED4984}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2614C6F7-2B78-87C8-18F4-C24F5FED4984}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20513,7 +20524,7 @@
           <xdr:cNvPr id="3426101" name="Line 116">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A23C59-9221-787C-AF19-5DF7F58BCDFE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35A23C59-9221-787C-AF19-5DF7F58BCDFE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20553,7 +20564,7 @@
           <xdr:cNvPr id="3426102" name="Line 117">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{627DB02D-00AC-3F70-9E6C-99DB663C92BB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{627DB02D-00AC-3F70-9E6C-99DB663C92BB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20593,7 +20604,7 @@
           <xdr:cNvPr id="3426103" name="Oval 118" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E489024-016D-55DB-175B-03630F816FAD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E489024-016D-55DB-175B-03630F816FAD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20629,7 +20640,7 @@
           <xdr:cNvPr id="3426104" name="Oval 119">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B63D80-9E0C-9637-73E1-6D3755148692}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D1B63D80-9E0C-9637-73E1-6D3755148692}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20663,7 +20674,7 @@
           <xdr:cNvPr id="3426105" name="Freeform 120">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C60DDD-ED85-9623-9F55-BED48EA32313}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D5C60DDD-ED85-9623-9F55-BED48EA32313}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20749,7 +20760,7 @@
           <xdr:cNvPr id="3426106" name="Line 121">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46CFF6F4-E2E4-A5D6-96D5-17FE14307DDE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{46CFF6F4-E2E4-A5D6-96D5-17FE14307DDE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20788,7 +20799,7 @@
           <xdr:cNvPr id="3426107" name="Line 122">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B34EEE1-3E4C-4DB1-6F27-3239E35A7FFE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7B34EEE1-3E4C-4DB1-6F27-3239E35A7FFE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20828,7 +20839,7 @@
           <xdr:cNvPr id="3426108" name="Line 123">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D134361-BD1D-66A9-9FAA-AD0983DA0F94}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6D134361-BD1D-66A9-9FAA-AD0983DA0F94}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20868,7 +20879,7 @@
           <xdr:cNvPr id="292" name="Text Box 124">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFD738E2-345B-5389-7A73-44DCDFA949DA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AFD738E2-345B-5389-7A73-44DCDFA949DA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20929,7 +20940,7 @@
           <xdr:cNvPr id="293" name="Text Box 125">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A2069A3-627D-124B-6719-054783EE0EFC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9A2069A3-627D-124B-6719-054783EE0EFC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20996,7 +21007,7 @@
           <xdr:cNvPr id="3426111" name="Freeform 126">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC7B2CAD-27DD-EFB9-4DBB-3E19B5FC7F10}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BC7B2CAD-27DD-EFB9-4DBB-3E19B5FC7F10}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21087,7 +21098,7 @@
           <xdr:cNvPr id="3426112" name="Freeform 127">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31354BD8-EC6C-843B-5F9A-85DF6EB6BC31}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{31354BD8-EC6C-843B-5F9A-85DF6EB6BC31}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21195,7 +21206,7 @@
           <xdr:cNvPr id="3426113" name="Rectangle 128" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEFA94DC-6CEA-039D-42B3-430B4DE49D98}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FEFA94DC-6CEA-039D-42B3-430B4DE49D98}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21231,7 +21242,7 @@
           <xdr:cNvPr id="3426114" name="Rectangle 129" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5405F755-1983-A412-6D7B-8EA610FBE64E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5405F755-1983-A412-6D7B-8EA610FBE64E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21267,7 +21278,7 @@
           <xdr:cNvPr id="3426115" name="Freeform 130">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39AB44B5-7329-FE1D-2136-74649672D3B6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{39AB44B5-7329-FE1D-2136-74649672D3B6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21353,7 +21364,7 @@
           <xdr:cNvPr id="3426116" name="Freeform 131" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{960E3166-B228-7D30-BEBC-FF8B60F51DD8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{960E3166-B228-7D30-BEBC-FF8B60F51DD8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21457,7 +21468,7 @@
           <xdr:cNvPr id="3426117" name="Line 132">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21151EFD-1A21-209A-2178-ED611F1F87F6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{21151EFD-1A21-209A-2178-ED611F1F87F6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21497,7 +21508,7 @@
           <xdr:cNvPr id="3426118" name="Line 133">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF13E9-330D-16DB-E14C-474F8C330F2A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00AF13E9-330D-16DB-E14C-474F8C330F2A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21537,7 +21548,7 @@
           <xdr:cNvPr id="3426119" name="Freeform 134">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5538123E-B653-ABDF-6B10-8FC9C47521A2}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5538123E-B653-ABDF-6B10-8FC9C47521A2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21783,7 +21794,7 @@
           <xdr:cNvPr id="303" name="Text Box 135">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401D0606-9C96-5634-B5C5-EF830454E849}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{401D0606-9C96-5634-B5C5-EF830454E849}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21850,7 +21861,7 @@
           <xdr:cNvPr id="3426121" name="Freeform 136">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FF04289-CAC4-57A5-C81B-7A54EE1A34A4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8FF04289-CAC4-57A5-C81B-7A54EE1A34A4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21971,7 +21982,7 @@
           <xdr:cNvPr id="3426122" name="Freeform 137">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0B7100-43CC-6262-BA59-1CFFED50FADA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8F0B7100-43CC-6262-BA59-1CFFED50FADA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22092,7 +22103,7 @@
           <xdr:cNvPr id="3426123" name="Line 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB1F00B3-3D2A-F225-C553-75AE883FF51E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FB1F00B3-3D2A-F225-C553-75AE883FF51E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22131,7 +22142,7 @@
           <xdr:cNvPr id="3426124" name="Line 139">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FF28ACD-D9C6-A9F7-BD03-C3E47E077FA3}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4FF28ACD-D9C6-A9F7-BD03-C3E47E077FA3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22171,7 +22182,7 @@
           <xdr:cNvPr id="3426125" name="Line 140">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207CA2E1-86D4-3AFE-7EFC-2E3932AA6276}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{207CA2E1-86D4-3AFE-7EFC-2E3932AA6276}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22211,7 +22222,7 @@
           <xdr:cNvPr id="3426126" name="Line 141">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1537142-2B38-83F7-E97A-D34931C91631}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D1537142-2B38-83F7-E97A-D34931C91631}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22250,7 +22261,7 @@
           <xdr:cNvPr id="3426127" name="Oval 142" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DF405C-BAFF-55D5-62EF-637AE2F8584B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E0DF405C-BAFF-55D5-62EF-637AE2F8584B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22286,7 +22297,7 @@
           <xdr:cNvPr id="3426128" name="Oval 143">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDC49F74-1FCF-DECD-EEAE-440A0BA255AE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DDC49F74-1FCF-DECD-EEAE-440A0BA255AE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22320,7 +22331,7 @@
           <xdr:cNvPr id="3426129" name="Line 144">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E968BC8A-BE85-0C1E-04A7-246D9C535FD6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E968BC8A-BE85-0C1E-04A7-246D9C535FD6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22359,7 +22370,7 @@
           <xdr:cNvPr id="3426130" name="Line 145">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED207D2E-5615-FBBC-7913-7FEF56FA5147}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED207D2E-5615-FBBC-7913-7FEF56FA5147}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22399,7 +22410,7 @@
           <xdr:cNvPr id="3426131" name="Freeform 146">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDD6E5C-FC0F-C567-9769-4ADF3AE3609C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1BDD6E5C-FC0F-C567-9769-4ADF3AE3609C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22490,7 +22501,7 @@
           <xdr:cNvPr id="3426132" name="Freeform 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D3BD76-7C46-1906-8DF8-7739B9D657DC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F7D3BD76-7C46-1906-8DF8-7739B9D657DC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22598,7 +22609,7 @@
           <xdr:cNvPr id="3426133" name="Rectangle 148" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3CCB519-AA81-63DB-5444-AFA33448C52B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B3CCB519-AA81-63DB-5444-AFA33448C52B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22634,7 +22645,7 @@
           <xdr:cNvPr id="3426134" name="Rectangle 149" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D23CB8C-5653-B4EB-E646-778DBAF247A3}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D23CB8C-5653-B4EB-E646-778DBAF247A3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22670,7 +22681,7 @@
           <xdr:cNvPr id="3426135" name="Freeform 150">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{069F2632-5E3B-7BAA-5D5F-BDF970BAC81D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{069F2632-5E3B-7BAA-5D5F-BDF970BAC81D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22756,7 +22767,7 @@
           <xdr:cNvPr id="3426136" name="Freeform 151" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D8428C-897C-2734-E221-0CF6E1B08C80}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{10D8428C-897C-2734-E221-0CF6E1B08C80}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22860,7 +22871,7 @@
           <xdr:cNvPr id="3426137" name="Line 152">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0285CFF0-4FA4-B965-F6D2-F7063E28BF71}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0285CFF0-4FA4-B965-F6D2-F7063E28BF71}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22900,7 +22911,7 @@
           <xdr:cNvPr id="3426138" name="Line 153">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D62A3B-A8ED-AECE-5D9F-8FB03769E7E7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{78D62A3B-A8ED-AECE-5D9F-8FB03769E7E7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22940,7 +22951,7 @@
           <xdr:cNvPr id="3426139" name="Freeform 154">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16365616-9894-8064-2B07-35BBFAB6922F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{16365616-9894-8064-2B07-35BBFAB6922F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23186,7 +23197,7 @@
           <xdr:cNvPr id="3426140" name="Freeform 155">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23D4359-C1C2-A571-A977-0DB6779C552B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C23D4359-C1C2-A571-A977-0DB6779C552B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23307,7 +23318,7 @@
           <xdr:cNvPr id="3426141" name="Line 156">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1480A8F4-CB5E-3CC6-0DD7-D6EBE3AC49AF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1480A8F4-CB5E-3CC6-0DD7-D6EBE3AC49AF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23346,7 +23357,7 @@
           <xdr:cNvPr id="3426142" name="Freeform 157">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C42FCD57-36C8-EDBE-C16D-E69E3EC5732A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C42FCD57-36C8-EDBE-C16D-E69E3EC5732A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23432,7 +23443,7 @@
           <xdr:cNvPr id="3426143" name="Line 158">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51F9A7FA-7DF9-97A6-51DF-570D0F3D6C45}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{51F9A7FA-7DF9-97A6-51DF-570D0F3D6C45}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23472,7 +23483,7 @@
           <xdr:cNvPr id="327" name="Text Box 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90002F1-50FE-4EB8-4B2B-22658A06706C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A90002F1-50FE-4EB8-4B2B-22658A06706C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23533,7 +23544,7 @@
           <xdr:cNvPr id="3426145" name="Line 160">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B71913B-4F67-2599-63F9-8F75B4DD0A10}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4B71913B-4F67-2599-63F9-8F75B4DD0A10}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23572,7 +23583,7 @@
           <xdr:cNvPr id="3426146" name="Line 161">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79513DC5-7EC0-15F0-E660-0E6D43F2A140}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{79513DC5-7EC0-15F0-E660-0E6D43F2A140}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23612,7 +23623,7 @@
           <xdr:cNvPr id="3426147" name="Line 162">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C44CC300-4B47-396E-09AD-AA33F7319503}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C44CC300-4B47-396E-09AD-AA33F7319503}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23668,7 +23679,7 @@
         <xdr:cNvPr id="3426066" name="Picture 444">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BCF11A-2599-36A1-E12E-DCCBAE7F2E9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00BCF11A-2599-36A1-E12E-DCCBAE7F2E9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23753,7 +23764,7 @@
         <xdr:cNvPr id="3426067" name="_x298645232" descr="EMB000059a8045b">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E06BB8-CF7F-4ACA-0F9E-9B78AFF46CDF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{58E06BB8-CF7F-4ACA-0F9E-9B78AFF46CDF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23815,6 +23826,50 @@
             </a14:hiddenLine>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1000124</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>123212</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123824" y="733424"/>
+          <a:ext cx="923925" cy="580413"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -24169,73 +24224,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAAF969-2101-449E-BFA6-59EDC18AD5EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P48"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="27.75" customHeight="1"/>
+  <dimension ref="A1:P352"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="27.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="0.59765625" style="122" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="124" customWidth="1"/>
-    <col min="3" max="3" width="1.796875" style="122" customWidth="1"/>
-    <col min="4" max="4" width="6.19921875" style="123" customWidth="1"/>
-    <col min="5" max="5" width="1.796875" style="122" customWidth="1"/>
-    <col min="6" max="6" width="5.796875" style="123" customWidth="1"/>
-    <col min="7" max="7" width="1.796875" style="122" customWidth="1"/>
-    <col min="8" max="8" width="8.8984375" style="123"/>
+    <col min="1" max="1" width="0.5546875" style="122" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="124" customWidth="1"/>
+    <col min="3" max="3" width="1.77734375" style="122" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="123" customWidth="1"/>
+    <col min="5" max="5" width="1.77734375" style="122" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" style="123" customWidth="1"/>
+    <col min="7" max="7" width="1.77734375" style="122" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="123"/>
     <col min="9" max="9" width="1" style="123" customWidth="1"/>
-    <col min="10" max="10" width="0.69921875" style="125" customWidth="1"/>
-    <col min="11" max="11" width="12.69921875" style="124" customWidth="1"/>
-    <col min="12" max="12" width="8.09765625" style="123" customWidth="1"/>
-    <col min="13" max="13" width="1.796875" style="122" customWidth="1"/>
-    <col min="14" max="14" width="7.69921875" style="123" customWidth="1"/>
-    <col min="15" max="15" width="1.796875" style="122" customWidth="1"/>
-    <col min="16" max="16" width="9.59765625" style="123" customWidth="1"/>
-    <col min="17" max="17" width="5.796875" style="122" customWidth="1"/>
-    <col min="18" max="18" width="5.19921875" style="122" customWidth="1"/>
-    <col min="19" max="19" width="8.8984375" style="122"/>
-    <col min="20" max="20" width="4.69921875" style="122" customWidth="1"/>
-    <col min="21" max="16384" width="8.8984375" style="122"/>
+    <col min="10" max="10" width="0.6640625" style="125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="124" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" style="123" customWidth="1"/>
+    <col min="13" max="13" width="1.77734375" style="122" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" style="123" customWidth="1"/>
+    <col min="15" max="15" width="1.77734375" style="122" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" style="123" customWidth="1"/>
+    <col min="17" max="17" width="5.77734375" style="122" customWidth="1"/>
+    <col min="18" max="18" width="5.21875" style="122" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="122"/>
+    <col min="20" max="20" width="4.6640625" style="122" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="122"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="310" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
     </row>
     <row r="2" spans="1:16" ht="18.75" customHeight="1">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="310" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="204"/>
+      <c r="B2" s="311"/>
+      <c r="C2" s="311"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="311"/>
+      <c r="J2" s="311"/>
+      <c r="K2" s="311"/>
+      <c r="L2" s="311"/>
+      <c r="M2" s="311"/>
+      <c r="N2" s="311"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
     </row>
     <row r="3" spans="1:16" ht="12" customHeight="1">
       <c r="A3" s="163"/>
@@ -24251,154 +24306,154 @@
       <c r="K3" s="161"/>
       <c r="L3" s="161"/>
       <c r="M3" s="161"/>
-      <c r="N3" s="213" t="s">
+      <c r="N3" s="319" t="s">
         <v>220</v>
       </c>
-      <c r="O3" s="214"/>
-      <c r="P3" s="214"/>
+      <c r="O3" s="297"/>
+      <c r="P3" s="297"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1">
       <c r="A4" s="160"/>
       <c r="B4" s="159"/>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="320" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="258" t="s">
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
+      <c r="I4" s="321"/>
+      <c r="J4" s="321"/>
+      <c r="K4" s="322"/>
+      <c r="L4" s="266" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="259"/>
-      <c r="N4" s="260" t="s">
+      <c r="M4" s="267"/>
+      <c r="N4" s="268" t="s">
         <v>211</v>
       </c>
-      <c r="O4" s="261"/>
-      <c r="P4" s="262"/>
+      <c r="O4" s="269"/>
+      <c r="P4" s="270"/>
     </row>
     <row r="5" spans="1:16" ht="12.75" customHeight="1">
       <c r="A5" s="160"/>
       <c r="B5" s="159"/>
-      <c r="C5" s="218" t="s">
+      <c r="C5" s="323" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
-      <c r="F5" s="218"/>
-      <c r="G5" s="218"/>
-      <c r="H5" s="218"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="218"/>
-      <c r="K5" s="219"/>
-      <c r="L5" s="226" t="s">
+      <c r="D5" s="323"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
+      <c r="H5" s="323"/>
+      <c r="I5" s="323"/>
+      <c r="J5" s="323"/>
+      <c r="K5" s="324"/>
+      <c r="L5" s="329" t="s">
         <v>77</v>
       </c>
-      <c r="M5" s="227"/>
-      <c r="N5" s="263"/>
-      <c r="O5" s="264"/>
-      <c r="P5" s="265"/>
+      <c r="M5" s="330"/>
+      <c r="N5" s="271"/>
+      <c r="O5" s="272"/>
+      <c r="P5" s="273"/>
     </row>
     <row r="6" spans="1:16" ht="12.75" customHeight="1">
       <c r="A6" s="160"/>
       <c r="B6" s="159"/>
-      <c r="C6" s="220" t="s">
+      <c r="C6" s="325" t="s">
         <v>210</v>
       </c>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="220"/>
-      <c r="G6" s="220"/>
-      <c r="H6" s="220"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="220"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="201" t="s">
+      <c r="D6" s="325"/>
+      <c r="E6" s="325"/>
+      <c r="F6" s="325"/>
+      <c r="G6" s="325"/>
+      <c r="H6" s="325"/>
+      <c r="I6" s="325"/>
+      <c r="J6" s="325"/>
+      <c r="K6" s="326"/>
+      <c r="L6" s="308" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="202"/>
-      <c r="N6" s="252" t="s">
+      <c r="M6" s="309"/>
+      <c r="N6" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="O6" s="253"/>
-      <c r="P6" s="254"/>
+      <c r="O6" s="261"/>
+      <c r="P6" s="262"/>
     </row>
     <row r="7" spans="1:16" ht="12.75" customHeight="1">
       <c r="A7" s="158"/>
       <c r="B7" s="157"/>
-      <c r="C7" s="199" t="s">
+      <c r="C7" s="306" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="199"/>
-      <c r="E7" s="199"/>
-      <c r="F7" s="199"/>
-      <c r="G7" s="199"/>
-      <c r="H7" s="199"/>
-      <c r="I7" s="199"/>
-      <c r="J7" s="199"/>
-      <c r="K7" s="200"/>
-      <c r="L7" s="250" t="s">
+      <c r="D7" s="306"/>
+      <c r="E7" s="306"/>
+      <c r="F7" s="306"/>
+      <c r="G7" s="306"/>
+      <c r="H7" s="306"/>
+      <c r="I7" s="306"/>
+      <c r="J7" s="306"/>
+      <c r="K7" s="307"/>
+      <c r="L7" s="258" t="s">
         <v>79</v>
       </c>
-      <c r="M7" s="251"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="256"/>
-      <c r="P7" s="257"/>
+      <c r="M7" s="259"/>
+      <c r="N7" s="263"/>
+      <c r="O7" s="264"/>
+      <c r="P7" s="265"/>
     </row>
     <row r="8" spans="1:16" s="145" customFormat="1" ht="24" customHeight="1">
       <c r="A8" s="156"/>
       <c r="B8" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="266" t="s">
+      <c r="C8" s="274" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="267"/>
-      <c r="E8" s="267"/>
-      <c r="F8" s="267"/>
-      <c r="G8" s="267"/>
-      <c r="H8" s="267"/>
-      <c r="I8" s="268"/>
+      <c r="D8" s="275"/>
+      <c r="E8" s="275"/>
+      <c r="F8" s="275"/>
+      <c r="G8" s="275"/>
+      <c r="H8" s="275"/>
+      <c r="I8" s="276"/>
       <c r="J8" s="51"/>
       <c r="K8" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="L8" s="269" t="s">
+      <c r="L8" s="277" t="s">
         <v>234</v>
       </c>
-      <c r="M8" s="270"/>
-      <c r="N8" s="270"/>
-      <c r="O8" s="270"/>
-      <c r="P8" s="271"/>
+      <c r="M8" s="278"/>
+      <c r="N8" s="278"/>
+      <c r="O8" s="278"/>
+      <c r="P8" s="279"/>
     </row>
     <row r="9" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A9" s="146"/>
       <c r="B9" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="232" t="s">
+      <c r="C9" s="207" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="303"/>
-      <c r="E9" s="303"/>
-      <c r="F9" s="303"/>
-      <c r="G9" s="303"/>
-      <c r="H9" s="303"/>
-      <c r="I9" s="304"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="209"/>
       <c r="J9" s="53"/>
       <c r="K9" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="292" t="s">
+      <c r="L9" s="196" t="s">
         <v>222</v>
       </c>
-      <c r="M9" s="293"/>
-      <c r="N9" s="293"/>
-      <c r="O9" s="293"/>
+      <c r="M9" s="197"/>
+      <c r="N9" s="197"/>
+      <c r="O9" s="197"/>
       <c r="P9" s="54" t="s">
         <v>83</v>
       </c>
@@ -24408,21 +24463,21 @@
       <c r="B10" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="305"/>
-      <c r="D10" s="306"/>
-      <c r="E10" s="306"/>
-      <c r="F10" s="306"/>
-      <c r="G10" s="306"/>
-      <c r="H10" s="306"/>
-      <c r="I10" s="307"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="211"/>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
+      <c r="G10" s="211"/>
+      <c r="H10" s="211"/>
+      <c r="I10" s="212"/>
       <c r="J10" s="56"/>
       <c r="K10" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="294"/>
-      <c r="M10" s="295"/>
-      <c r="N10" s="295"/>
-      <c r="O10" s="295"/>
+      <c r="L10" s="198"/>
+      <c r="M10" s="199"/>
+      <c r="N10" s="199"/>
+      <c r="O10" s="199"/>
       <c r="P10" s="57" t="s">
         <v>190</v>
       </c>
@@ -24455,13 +24510,13 @@
       <c r="K11" s="182" t="s">
         <v>228</v>
       </c>
-      <c r="L11" s="196" t="s">
+      <c r="L11" s="303" t="s">
         <v>229</v>
       </c>
-      <c r="M11" s="197"/>
-      <c r="N11" s="197"/>
-      <c r="O11" s="197"/>
-      <c r="P11" s="198"/>
+      <c r="M11" s="304"/>
+      <c r="N11" s="304"/>
+      <c r="O11" s="304"/>
+      <c r="P11" s="305"/>
     </row>
     <row r="12" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A12" s="155"/>
@@ -24485,13 +24540,13 @@
       <c r="K12" s="183" t="s">
         <v>230</v>
       </c>
-      <c r="L12" s="277" t="s">
+      <c r="L12" s="235" t="s">
         <v>231</v>
       </c>
-      <c r="M12" s="278"/>
-      <c r="N12" s="278"/>
-      <c r="O12" s="278"/>
-      <c r="P12" s="279"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="237"/>
     </row>
     <row r="13" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A13" s="154"/>
@@ -24524,10 +24579,10 @@
       <c r="L13" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="M13" s="318" t="s">
+      <c r="M13" s="225" t="s">
         <v>204</v>
       </c>
-      <c r="N13" s="318"/>
+      <c r="N13" s="225"/>
       <c r="O13" s="52" t="s">
         <v>0</v>
       </c>
@@ -24560,10 +24615,10 @@
       <c r="L14" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="M14" s="319">
+      <c r="M14" s="226">
         <v>4.9000000000000004</v>
       </c>
-      <c r="N14" s="319"/>
+      <c r="N14" s="226"/>
       <c r="O14" s="62" t="s">
         <v>108</v>
       </c>
@@ -24579,18 +24634,18 @@
       <c r="C15" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="308" t="s">
+      <c r="D15" s="213" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="316"/>
-      <c r="F15" s="316"/>
+      <c r="E15" s="222"/>
+      <c r="F15" s="222"/>
       <c r="G15" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="H15" s="308" t="s">
+      <c r="H15" s="213" t="s">
         <v>112</v>
       </c>
-      <c r="I15" s="309"/>
+      <c r="I15" s="214"/>
       <c r="J15" s="53"/>
       <c r="K15" s="52" t="s">
         <v>113</v>
@@ -24598,10 +24653,10 @@
       <c r="L15" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="M15" s="296">
+      <c r="M15" s="200">
         <v>1.2</v>
       </c>
-      <c r="N15" s="297"/>
+      <c r="N15" s="201"/>
       <c r="O15" s="52" t="s">
         <v>0</v>
       </c>
@@ -24617,18 +24672,18 @@
       <c r="C16" s="114" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="290" t="s">
+      <c r="D16" s="215" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="285"/>
-      <c r="F16" s="285"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
       <c r="G16" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="H16" s="290" t="s">
+      <c r="H16" s="215" t="s">
         <v>117</v>
       </c>
-      <c r="I16" s="310"/>
+      <c r="I16" s="216"/>
       <c r="J16" s="49"/>
       <c r="K16" s="62" t="s">
         <v>118</v>
@@ -24636,8 +24691,8 @@
       <c r="L16" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="M16" s="272"/>
-      <c r="N16" s="317"/>
+      <c r="M16" s="223"/>
+      <c r="N16" s="224"/>
       <c r="O16" s="62" t="s">
         <v>108</v>
       </c>
@@ -24669,13 +24724,13 @@
       <c r="K17" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="L17" s="236" t="s">
+      <c r="L17" s="248" t="s">
         <v>205</v>
       </c>
-      <c r="M17" s="233"/>
-      <c r="N17" s="233"/>
-      <c r="O17" s="233"/>
-      <c r="P17" s="237"/>
+      <c r="M17" s="227"/>
+      <c r="N17" s="227"/>
+      <c r="O17" s="227"/>
+      <c r="P17" s="284"/>
     </row>
     <row r="18" spans="1:16" s="145" customFormat="1" ht="12.75" customHeight="1">
       <c r="A18" s="146"/>
@@ -24701,20 +24756,20 @@
       <c r="K18" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="L18" s="284" t="s">
+      <c r="L18" s="242" t="s">
         <v>125</v>
       </c>
-      <c r="M18" s="285"/>
-      <c r="N18" s="285"/>
-      <c r="O18" s="285"/>
-      <c r="P18" s="286"/>
+      <c r="M18" s="243"/>
+      <c r="N18" s="243"/>
+      <c r="O18" s="243"/>
+      <c r="P18" s="244"/>
     </row>
     <row r="19" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A19" s="150"/>
       <c r="B19" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="311" t="s">
+      <c r="C19" s="217" t="s">
         <v>127</v>
       </c>
       <c r="D19" s="113" t="s">
@@ -24754,7 +24809,7 @@
       <c r="B20" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="312"/>
+      <c r="C20" s="218"/>
       <c r="D20" s="112"/>
       <c r="E20" s="64"/>
       <c r="F20" s="112"/>
@@ -24769,11 +24824,11 @@
       <c r="K20" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="L20" s="274" t="s">
+      <c r="L20" s="302" t="s">
         <v>204</v>
       </c>
-      <c r="M20" s="235"/>
-      <c r="N20" s="235"/>
+      <c r="M20" s="229"/>
+      <c r="N20" s="229"/>
       <c r="O20" s="62" t="s">
         <v>95</v>
       </c>
@@ -24796,20 +24851,20 @@
       <c r="F21" s="109" t="s">
         <v>209</v>
       </c>
-      <c r="G21" s="291" t="s">
+      <c r="G21" s="249" t="s">
         <v>215</v>
       </c>
-      <c r="H21" s="291"/>
-      <c r="I21" s="280"/>
+      <c r="H21" s="249"/>
+      <c r="I21" s="238"/>
       <c r="J21" s="59"/>
       <c r="K21" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="L21" s="232" t="s">
+      <c r="L21" s="207" t="s">
         <v>204</v>
       </c>
-      <c r="M21" s="233"/>
-      <c r="N21" s="233"/>
+      <c r="M21" s="227"/>
+      <c r="N21" s="227"/>
       <c r="O21" s="52" t="s">
         <v>0</v>
       </c>
@@ -24830,18 +24885,18 @@
       <c r="F22" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="G22" s="329" t="s">
+      <c r="G22" s="256" t="s">
         <v>232</v>
       </c>
-      <c r="H22" s="330"/>
-      <c r="I22" s="281"/>
+      <c r="H22" s="257"/>
+      <c r="I22" s="239"/>
       <c r="J22" s="64"/>
       <c r="K22" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="L22" s="234"/>
-      <c r="M22" s="235"/>
-      <c r="N22" s="235"/>
+      <c r="L22" s="228"/>
+      <c r="M22" s="229"/>
+      <c r="N22" s="229"/>
       <c r="O22" s="62" t="s">
         <v>95</v>
       </c>
@@ -24858,10 +24913,10 @@
       <c r="D23" s="86" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="321">
+      <c r="E23" s="231">
         <v>119.4</v>
       </c>
-      <c r="F23" s="322"/>
+      <c r="F23" s="232"/>
       <c r="G23" s="52" t="s">
         <v>0</v>
       </c>
@@ -24873,11 +24928,11 @@
       <c r="K23" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="L23" s="232" t="s">
+      <c r="L23" s="207" t="s">
         <v>199</v>
       </c>
-      <c r="M23" s="233"/>
-      <c r="N23" s="233"/>
+      <c r="M23" s="227"/>
+      <c r="N23" s="227"/>
       <c r="O23" s="52" t="s">
         <v>95</v>
       </c>
@@ -24894,11 +24949,11 @@
       <c r="D24" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="323">
+      <c r="E24" s="250">
         <f>M14+M15</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="F24" s="324"/>
+      <c r="F24" s="251"/>
       <c r="G24" s="55" t="s">
         <v>108</v>
       </c>
@@ -24910,9 +24965,9 @@
       <c r="K24" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="L24" s="234"/>
-      <c r="M24" s="235"/>
-      <c r="N24" s="235"/>
+      <c r="L24" s="228"/>
+      <c r="M24" s="229"/>
+      <c r="N24" s="229"/>
       <c r="O24" s="52" t="s">
         <v>108</v>
       </c>
@@ -24926,11 +24981,11 @@
         <v>149</v>
       </c>
       <c r="C25" s="90"/>
-      <c r="D25" s="325" t="s">
+      <c r="D25" s="252" t="s">
         <v>200</v>
       </c>
-      <c r="E25" s="326"/>
-      <c r="F25" s="326"/>
+      <c r="E25" s="253"/>
+      <c r="F25" s="253"/>
       <c r="G25" s="52" t="s">
         <v>108</v>
       </c>
@@ -24945,12 +25000,12 @@
       <c r="L25" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="M25" s="296" t="s">
+      <c r="M25" s="200" t="s">
         <v>152</v>
       </c>
-      <c r="N25" s="296"/>
-      <c r="O25" s="296"/>
-      <c r="P25" s="320"/>
+      <c r="N25" s="200"/>
+      <c r="O25" s="200"/>
+      <c r="P25" s="230"/>
     </row>
     <row r="26" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A26" s="148"/>
@@ -24981,24 +25036,24 @@
       <c r="L26" s="85" t="s">
         <v>156</v>
       </c>
-      <c r="M26" s="272" t="s">
+      <c r="M26" s="223" t="s">
         <v>157</v>
       </c>
-      <c r="N26" s="272"/>
-      <c r="O26" s="272"/>
-      <c r="P26" s="273"/>
+      <c r="N26" s="223"/>
+      <c r="O26" s="223"/>
+      <c r="P26" s="301"/>
     </row>
     <row r="27" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A27" s="150"/>
       <c r="B27" s="92" t="s">
         <v>158</v>
       </c>
-      <c r="C27" s="236"/>
-      <c r="D27" s="327" t="s">
+      <c r="C27" s="248"/>
+      <c r="D27" s="254" t="s">
         <v>159</v>
       </c>
-      <c r="E27" s="282"/>
-      <c r="F27" s="282" t="s">
+      <c r="E27" s="240"/>
+      <c r="F27" s="240" t="s">
         <v>160</v>
       </c>
       <c r="G27" s="52" t="s">
@@ -25033,10 +25088,10 @@
       <c r="B28" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="C28" s="284"/>
-      <c r="D28" s="328"/>
-      <c r="E28" s="283"/>
-      <c r="F28" s="283"/>
+      <c r="C28" s="242"/>
+      <c r="D28" s="255"/>
+      <c r="E28" s="241"/>
+      <c r="F28" s="241"/>
       <c r="G28" s="62" t="s">
         <v>0</v>
       </c>
@@ -25063,38 +25118,38 @@
       <c r="B29" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="298" t="s">
+      <c r="C29" s="202" t="s">
         <v>225</v>
       </c>
-      <c r="D29" s="299"/>
-      <c r="E29" s="300"/>
-      <c r="F29" s="300"/>
-      <c r="G29" s="300"/>
-      <c r="H29" s="301"/>
-      <c r="I29" s="302"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="204"/>
+      <c r="F29" s="204"/>
+      <c r="G29" s="204"/>
+      <c r="H29" s="205"/>
+      <c r="I29" s="206"/>
       <c r="J29" s="95"/>
       <c r="K29" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="L29" s="313">
+      <c r="L29" s="219">
         <v>0.2</v>
       </c>
-      <c r="M29" s="314"/>
-      <c r="N29" s="314"/>
-      <c r="O29" s="314"/>
-      <c r="P29" s="315"/>
+      <c r="M29" s="220"/>
+      <c r="N29" s="220"/>
+      <c r="O29" s="220"/>
+      <c r="P29" s="221"/>
     </row>
     <row r="30" spans="1:16" s="147" customFormat="1" ht="19.5" customHeight="1">
       <c r="A30" s="150"/>
       <c r="B30" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="228" t="s">
+      <c r="C30" s="280" t="s">
         <v>226</v>
       </c>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
+      <c r="D30" s="281"/>
+      <c r="E30" s="281"/>
+      <c r="F30" s="281"/>
       <c r="G30" s="52" t="s">
         <v>95</v>
       </c>
@@ -25106,12 +25161,12 @@
       <c r="K30" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="L30" s="232" t="s">
+      <c r="L30" s="207" t="s">
         <v>216</v>
       </c>
-      <c r="M30" s="233"/>
-      <c r="N30" s="233"/>
-      <c r="O30" s="233"/>
+      <c r="M30" s="227"/>
+      <c r="N30" s="227"/>
+      <c r="O30" s="227"/>
       <c r="P30" s="97" t="s">
         <v>201</v>
       </c>
@@ -25121,10 +25176,10 @@
       <c r="B31" s="98" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="230"/>
-      <c r="D31" s="231"/>
-      <c r="E31" s="231"/>
-      <c r="F31" s="231"/>
+      <c r="C31" s="282"/>
+      <c r="D31" s="283"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="283"/>
       <c r="G31" s="117" t="s">
         <v>193</v>
       </c>
@@ -25136,17 +25191,17 @@
       <c r="K31" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="L31" s="287" t="s">
+      <c r="L31" s="245" t="s">
         <v>202</v>
       </c>
-      <c r="M31" s="288"/>
-      <c r="N31" s="288"/>
-      <c r="O31" s="288"/>
-      <c r="P31" s="289"/>
+      <c r="M31" s="246"/>
+      <c r="N31" s="246"/>
+      <c r="O31" s="246"/>
+      <c r="P31" s="247"/>
     </row>
     <row r="32" spans="1:16" s="147" customFormat="1" ht="6.75" customHeight="1">
       <c r="A32" s="148"/>
-      <c r="B32" s="275" t="s">
+      <c r="B32" s="233" t="s">
         <v>177</v>
       </c>
       <c r="C32" s="48"/>
@@ -25166,7 +25221,7 @@
     </row>
     <row r="33" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A33" s="148"/>
-      <c r="B33" s="276"/>
+      <c r="B33" s="234"/>
       <c r="C33" s="55" t="s">
         <v>0</v>
       </c>
@@ -25361,103 +25416,103 @@
     <row r="43" spans="1:16" ht="13.5" customHeight="1">
       <c r="A43" s="144"/>
       <c r="B43" s="143"/>
-      <c r="C43" s="206"/>
-      <c r="D43" s="206"/>
-      <c r="E43" s="206"/>
-      <c r="F43" s="222"/>
-      <c r="G43" s="223"/>
+      <c r="C43" s="312"/>
+      <c r="D43" s="312"/>
+      <c r="E43" s="312"/>
+      <c r="F43" s="327"/>
+      <c r="G43" s="328"/>
       <c r="H43" s="142"/>
       <c r="I43" s="141"/>
       <c r="J43" s="140"/>
-      <c r="K43" s="207" t="s">
+      <c r="K43" s="313" t="s">
         <v>180</v>
       </c>
-      <c r="L43" s="208"/>
-      <c r="M43" s="208"/>
-      <c r="N43" s="208"/>
-      <c r="O43" s="208"/>
-      <c r="P43" s="209"/>
+      <c r="L43" s="314"/>
+      <c r="M43" s="314"/>
+      <c r="N43" s="314"/>
+      <c r="O43" s="314"/>
+      <c r="P43" s="315"/>
     </row>
     <row r="44" spans="1:16" ht="15.75" customHeight="1">
       <c r="A44" s="136"/>
       <c r="B44" s="122" t="s">
         <v>178</v>
       </c>
-      <c r="C44" s="205"/>
-      <c r="D44" s="205"/>
-      <c r="E44" s="205"/>
-      <c r="F44" s="224" t="s">
+      <c r="C44" s="286"/>
+      <c r="D44" s="286"/>
+      <c r="E44" s="286"/>
+      <c r="F44" s="290" t="s">
         <v>179</v>
       </c>
-      <c r="G44" s="225"/>
+      <c r="G44" s="291"/>
       <c r="H44" s="135"/>
-      <c r="K44" s="210">
+      <c r="K44" s="316">
         <v>45611</v>
       </c>
-      <c r="L44" s="211"/>
-      <c r="M44" s="211"/>
-      <c r="N44" s="211"/>
-      <c r="O44" s="211"/>
-      <c r="P44" s="212"/>
+      <c r="L44" s="317"/>
+      <c r="M44" s="317"/>
+      <c r="N44" s="317"/>
+      <c r="O44" s="317"/>
+      <c r="P44" s="318"/>
     </row>
     <row r="45" spans="1:16" ht="12.75" customHeight="1">
       <c r="A45" s="136"/>
       <c r="B45" s="122" t="s">
         <v>208</v>
       </c>
-      <c r="C45" s="245" t="s">
+      <c r="C45" s="295" t="s">
         <v>203</v>
       </c>
-      <c r="D45" s="245"/>
-      <c r="E45" s="245"/>
-      <c r="F45" s="224" t="s">
+      <c r="D45" s="295"/>
+      <c r="E45" s="295"/>
+      <c r="F45" s="290" t="s">
         <v>181</v>
       </c>
-      <c r="G45" s="225"/>
+      <c r="G45" s="291"/>
       <c r="H45" s="135" t="s">
         <v>212</v>
       </c>
       <c r="I45" s="138"/>
       <c r="J45" s="139"/>
-      <c r="K45" s="242" t="s">
+      <c r="K45" s="292" t="s">
         <v>182</v>
       </c>
-      <c r="L45" s="243"/>
-      <c r="M45" s="243"/>
-      <c r="N45" s="243"/>
-      <c r="O45" s="243"/>
-      <c r="P45" s="244"/>
+      <c r="L45" s="293"/>
+      <c r="M45" s="293"/>
+      <c r="N45" s="293"/>
+      <c r="O45" s="293"/>
+      <c r="P45" s="294"/>
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1">
       <c r="A46" s="136"/>
       <c r="B46" s="122"/>
-      <c r="C46" s="205"/>
-      <c r="D46" s="205"/>
-      <c r="E46" s="205"/>
-      <c r="F46" s="224"/>
-      <c r="G46" s="225"/>
+      <c r="C46" s="286"/>
+      <c r="D46" s="286"/>
+      <c r="E46" s="286"/>
+      <c r="F46" s="290"/>
+      <c r="G46" s="291"/>
       <c r="H46" s="135"/>
       <c r="I46" s="138"/>
       <c r="J46" s="137"/>
-      <c r="K46" s="239"/>
-      <c r="L46" s="240"/>
-      <c r="M46" s="240"/>
-      <c r="N46" s="240"/>
-      <c r="O46" s="240"/>
-      <c r="P46" s="241"/>
+      <c r="K46" s="287"/>
+      <c r="L46" s="288"/>
+      <c r="M46" s="288"/>
+      <c r="N46" s="288"/>
+      <c r="O46" s="288"/>
+      <c r="P46" s="289"/>
     </row>
     <row r="47" spans="1:16" ht="13.5" customHeight="1">
       <c r="A47" s="136"/>
       <c r="B47" s="122" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="205"/>
-      <c r="D47" s="205"/>
-      <c r="E47" s="205"/>
-      <c r="F47" s="224" t="s">
+      <c r="C47" s="286"/>
+      <c r="D47" s="286"/>
+      <c r="E47" s="286"/>
+      <c r="F47" s="290" t="s">
         <v>179</v>
       </c>
-      <c r="G47" s="225"/>
+      <c r="G47" s="291"/>
       <c r="H47" s="135"/>
       <c r="K47" s="134" t="s">
         <v>184</v>
@@ -25479,29 +25534,4034 @@
       <c r="B48" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="C48" s="238" t="s">
+      <c r="C48" s="285" t="s">
         <v>236</v>
       </c>
-      <c r="D48" s="238"/>
-      <c r="E48" s="238"/>
-      <c r="F48" s="248" t="s">
+      <c r="D48" s="285"/>
+      <c r="E48" s="285"/>
+      <c r="F48" s="299" t="s">
         <v>181</v>
       </c>
-      <c r="G48" s="249"/>
+      <c r="G48" s="300"/>
       <c r="H48" s="128" t="s">
         <v>206</v>
       </c>
       <c r="I48" s="127"/>
       <c r="J48" s="126"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="214"/>
-      <c r="M48" s="214"/>
-      <c r="N48" s="214"/>
-      <c r="O48" s="214"/>
-      <c r="P48" s="247"/>
+      <c r="K48" s="296"/>
+      <c r="L48" s="297"/>
+      <c r="M48" s="297"/>
+      <c r="N48" s="297"/>
+      <c r="O48" s="297"/>
+      <c r="P48" s="298"/>
+    </row>
+    <row r="49" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B49" s="361"/>
+      <c r="C49" s="143"/>
+      <c r="D49" s="141"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="141"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="141"/>
+      <c r="I49" s="141"/>
+      <c r="J49" s="141"/>
+      <c r="K49" s="361"/>
+      <c r="L49" s="141"/>
+    </row>
+    <row r="50" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B50" s="362"/>
+      <c r="C50" s="363"/>
+      <c r="D50" s="364"/>
+      <c r="E50" s="363"/>
+      <c r="F50" s="364"/>
+      <c r="G50" s="363"/>
+      <c r="H50" s="364"/>
+      <c r="I50" s="364"/>
+      <c r="J50" s="364"/>
+      <c r="K50" s="362"/>
+      <c r="L50" s="364"/>
+    </row>
+    <row r="51" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B51" s="362"/>
+      <c r="C51" s="363"/>
+      <c r="D51" s="364"/>
+      <c r="E51" s="363"/>
+      <c r="F51" s="364"/>
+      <c r="G51" s="363"/>
+      <c r="H51" s="364"/>
+      <c r="I51" s="364"/>
+      <c r="J51" s="364"/>
+      <c r="K51" s="362"/>
+      <c r="L51" s="364"/>
+    </row>
+    <row r="52" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B52" s="362"/>
+      <c r="C52" s="363"/>
+      <c r="D52" s="364"/>
+      <c r="E52" s="363"/>
+      <c r="F52" s="364"/>
+      <c r="G52" s="363"/>
+      <c r="H52" s="364"/>
+      <c r="I52" s="364"/>
+      <c r="J52" s="364"/>
+      <c r="K52" s="362"/>
+      <c r="L52" s="364"/>
+    </row>
+    <row r="53" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B53" s="362"/>
+      <c r="C53" s="363"/>
+      <c r="D53" s="364"/>
+      <c r="E53" s="363"/>
+      <c r="F53" s="364"/>
+      <c r="G53" s="363"/>
+      <c r="H53" s="364"/>
+      <c r="I53" s="364"/>
+      <c r="J53" s="364"/>
+      <c r="K53" s="362"/>
+      <c r="L53" s="364"/>
+    </row>
+    <row r="54" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B54" s="362"/>
+      <c r="C54" s="363"/>
+      <c r="D54" s="364"/>
+      <c r="E54" s="363"/>
+      <c r="F54" s="364"/>
+      <c r="G54" s="363"/>
+      <c r="H54" s="364"/>
+      <c r="I54" s="364"/>
+      <c r="J54" s="364"/>
+      <c r="K54" s="362"/>
+      <c r="L54" s="364"/>
+    </row>
+    <row r="55" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B55" s="362"/>
+      <c r="C55" s="363"/>
+      <c r="D55" s="364"/>
+      <c r="E55" s="363"/>
+      <c r="F55" s="364"/>
+      <c r="G55" s="363"/>
+      <c r="H55" s="364"/>
+      <c r="I55" s="364"/>
+      <c r="J55" s="364"/>
+      <c r="K55" s="362"/>
+      <c r="L55" s="364"/>
+    </row>
+    <row r="56" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B56" s="362"/>
+      <c r="C56" s="363"/>
+      <c r="D56" s="364"/>
+      <c r="E56" s="363"/>
+      <c r="F56" s="364"/>
+      <c r="G56" s="363"/>
+      <c r="H56" s="364"/>
+      <c r="I56" s="364"/>
+      <c r="J56" s="364"/>
+      <c r="K56" s="362"/>
+      <c r="L56" s="364"/>
+    </row>
+    <row r="57" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B57" s="362"/>
+      <c r="C57" s="363"/>
+      <c r="D57" s="364"/>
+      <c r="E57" s="363"/>
+      <c r="F57" s="364"/>
+      <c r="G57" s="363"/>
+      <c r="H57" s="364"/>
+      <c r="I57" s="364"/>
+      <c r="J57" s="364"/>
+      <c r="K57" s="362"/>
+      <c r="L57" s="364"/>
+    </row>
+    <row r="58" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B58" s="362"/>
+      <c r="C58" s="363"/>
+      <c r="D58" s="364"/>
+      <c r="E58" s="363"/>
+      <c r="F58" s="364"/>
+      <c r="G58" s="363"/>
+      <c r="H58" s="364"/>
+      <c r="I58" s="364"/>
+      <c r="J58" s="364"/>
+      <c r="K58" s="362"/>
+      <c r="L58" s="364"/>
+    </row>
+    <row r="59" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B59" s="362"/>
+      <c r="C59" s="363"/>
+      <c r="D59" s="364"/>
+      <c r="E59" s="363"/>
+      <c r="F59" s="364"/>
+      <c r="G59" s="363"/>
+      <c r="H59" s="364"/>
+      <c r="I59" s="364"/>
+      <c r="J59" s="364"/>
+      <c r="K59" s="362"/>
+      <c r="L59" s="364"/>
+    </row>
+    <row r="60" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B60" s="362"/>
+      <c r="C60" s="363"/>
+      <c r="D60" s="364"/>
+      <c r="E60" s="363"/>
+      <c r="F60" s="364"/>
+      <c r="G60" s="363"/>
+      <c r="H60" s="364"/>
+      <c r="I60" s="364"/>
+      <c r="J60" s="364"/>
+      <c r="K60" s="362"/>
+      <c r="L60" s="364"/>
+    </row>
+    <row r="61" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B61" s="362"/>
+      <c r="C61" s="363"/>
+      <c r="D61" s="364"/>
+      <c r="E61" s="363"/>
+      <c r="F61" s="364"/>
+      <c r="G61" s="363"/>
+      <c r="H61" s="364"/>
+      <c r="I61" s="364"/>
+      <c r="J61" s="364"/>
+      <c r="K61" s="362"/>
+      <c r="L61" s="364"/>
+    </row>
+    <row r="62" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B62" s="362"/>
+      <c r="C62" s="363"/>
+      <c r="D62" s="364"/>
+      <c r="E62" s="363"/>
+      <c r="F62" s="364"/>
+      <c r="G62" s="363"/>
+      <c r="H62" s="364"/>
+      <c r="I62" s="364"/>
+      <c r="J62" s="364"/>
+      <c r="K62" s="362"/>
+      <c r="L62" s="364"/>
+    </row>
+    <row r="63" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B63" s="362"/>
+      <c r="C63" s="363"/>
+      <c r="D63" s="364"/>
+      <c r="E63" s="363"/>
+      <c r="F63" s="364"/>
+      <c r="G63" s="363"/>
+      <c r="H63" s="364"/>
+      <c r="I63" s="364"/>
+      <c r="J63" s="364"/>
+      <c r="K63" s="362"/>
+      <c r="L63" s="364"/>
+    </row>
+    <row r="64" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B64" s="362"/>
+      <c r="C64" s="363"/>
+      <c r="D64" s="364"/>
+      <c r="E64" s="363"/>
+      <c r="F64" s="364"/>
+      <c r="G64" s="363"/>
+      <c r="H64" s="364"/>
+      <c r="I64" s="364"/>
+      <c r="J64" s="364"/>
+      <c r="K64" s="362"/>
+      <c r="L64" s="364"/>
+    </row>
+    <row r="65" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B65" s="362"/>
+      <c r="C65" s="363"/>
+      <c r="D65" s="364"/>
+      <c r="E65" s="363"/>
+      <c r="F65" s="364"/>
+      <c r="G65" s="363"/>
+      <c r="H65" s="364"/>
+      <c r="I65" s="364"/>
+      <c r="J65" s="364"/>
+      <c r="K65" s="362"/>
+      <c r="L65" s="364"/>
+    </row>
+    <row r="66" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B66" s="362"/>
+      <c r="C66" s="363"/>
+      <c r="D66" s="364"/>
+      <c r="E66" s="363"/>
+      <c r="F66" s="364"/>
+      <c r="G66" s="363"/>
+      <c r="H66" s="364"/>
+      <c r="I66" s="364"/>
+      <c r="J66" s="364"/>
+      <c r="K66" s="362"/>
+      <c r="L66" s="364"/>
+    </row>
+    <row r="67" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B67" s="362"/>
+      <c r="C67" s="363"/>
+      <c r="D67" s="364"/>
+      <c r="E67" s="363"/>
+      <c r="F67" s="364"/>
+      <c r="G67" s="363"/>
+      <c r="H67" s="364"/>
+      <c r="I67" s="364"/>
+      <c r="J67" s="364"/>
+      <c r="K67" s="362"/>
+      <c r="L67" s="364"/>
+    </row>
+    <row r="68" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B68" s="362"/>
+      <c r="C68" s="363"/>
+      <c r="D68" s="364"/>
+      <c r="E68" s="363"/>
+      <c r="F68" s="364"/>
+      <c r="G68" s="363"/>
+      <c r="H68" s="364"/>
+      <c r="I68" s="364"/>
+      <c r="J68" s="364"/>
+      <c r="K68" s="362"/>
+      <c r="L68" s="364"/>
+    </row>
+    <row r="69" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B69" s="362"/>
+      <c r="C69" s="363"/>
+      <c r="D69" s="364"/>
+      <c r="E69" s="363"/>
+      <c r="F69" s="364"/>
+      <c r="G69" s="363"/>
+      <c r="H69" s="364"/>
+      <c r="I69" s="364"/>
+      <c r="J69" s="364"/>
+      <c r="K69" s="362"/>
+      <c r="L69" s="364"/>
+    </row>
+    <row r="70" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B70" s="362"/>
+      <c r="C70" s="363"/>
+      <c r="D70" s="364"/>
+      <c r="E70" s="363"/>
+      <c r="F70" s="364"/>
+      <c r="G70" s="363"/>
+      <c r="H70" s="364"/>
+      <c r="I70" s="364"/>
+      <c r="J70" s="364"/>
+      <c r="K70" s="362"/>
+      <c r="L70" s="364"/>
+    </row>
+    <row r="71" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B71" s="362"/>
+      <c r="C71" s="363"/>
+      <c r="D71" s="364"/>
+      <c r="E71" s="363"/>
+      <c r="F71" s="364"/>
+      <c r="G71" s="363"/>
+      <c r="H71" s="364"/>
+      <c r="I71" s="364"/>
+      <c r="J71" s="364"/>
+      <c r="K71" s="362"/>
+      <c r="L71" s="364"/>
+    </row>
+    <row r="72" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B72" s="362"/>
+      <c r="C72" s="363"/>
+      <c r="D72" s="364"/>
+      <c r="E72" s="363"/>
+      <c r="F72" s="364"/>
+      <c r="G72" s="363"/>
+      <c r="H72" s="364"/>
+      <c r="I72" s="364"/>
+      <c r="J72" s="364"/>
+      <c r="K72" s="362"/>
+      <c r="L72" s="364"/>
+    </row>
+    <row r="73" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B73" s="362"/>
+      <c r="C73" s="363"/>
+      <c r="D73" s="364"/>
+      <c r="E73" s="363"/>
+      <c r="F73" s="364"/>
+      <c r="G73" s="363"/>
+      <c r="H73" s="364"/>
+      <c r="I73" s="364"/>
+      <c r="J73" s="364"/>
+      <c r="K73" s="362"/>
+      <c r="L73" s="364"/>
+    </row>
+    <row r="74" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B74" s="362"/>
+      <c r="C74" s="363"/>
+      <c r="D74" s="364"/>
+      <c r="E74" s="363"/>
+      <c r="F74" s="364"/>
+      <c r="G74" s="363"/>
+      <c r="H74" s="364"/>
+      <c r="I74" s="364"/>
+      <c r="J74" s="364"/>
+      <c r="K74" s="362"/>
+      <c r="L74" s="364"/>
+    </row>
+    <row r="75" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B75" s="362"/>
+      <c r="C75" s="363"/>
+      <c r="D75" s="364"/>
+      <c r="E75" s="363"/>
+      <c r="F75" s="364"/>
+      <c r="G75" s="363"/>
+      <c r="H75" s="364"/>
+      <c r="I75" s="364"/>
+      <c r="J75" s="364"/>
+      <c r="K75" s="362"/>
+      <c r="L75" s="364"/>
+    </row>
+    <row r="76" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B76" s="362"/>
+      <c r="C76" s="363"/>
+      <c r="D76" s="364"/>
+      <c r="E76" s="363"/>
+      <c r="F76" s="364"/>
+      <c r="G76" s="363"/>
+      <c r="H76" s="364"/>
+      <c r="I76" s="364"/>
+      <c r="J76" s="364"/>
+      <c r="K76" s="362"/>
+      <c r="L76" s="364"/>
+    </row>
+    <row r="77" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B77" s="362"/>
+      <c r="C77" s="363"/>
+      <c r="D77" s="364"/>
+      <c r="E77" s="363"/>
+      <c r="F77" s="364"/>
+      <c r="G77" s="363"/>
+      <c r="H77" s="364"/>
+      <c r="I77" s="364"/>
+      <c r="J77" s="364"/>
+      <c r="K77" s="362"/>
+      <c r="L77" s="364"/>
+    </row>
+    <row r="78" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B78" s="362"/>
+      <c r="C78" s="363"/>
+      <c r="D78" s="364"/>
+      <c r="E78" s="363"/>
+      <c r="F78" s="364"/>
+      <c r="G78" s="363"/>
+      <c r="H78" s="364"/>
+      <c r="I78" s="364"/>
+      <c r="J78" s="364"/>
+      <c r="K78" s="362"/>
+      <c r="L78" s="364"/>
+    </row>
+    <row r="79" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B79" s="362"/>
+      <c r="C79" s="363"/>
+      <c r="D79" s="364"/>
+      <c r="E79" s="363"/>
+      <c r="F79" s="364"/>
+      <c r="G79" s="363"/>
+      <c r="H79" s="364"/>
+      <c r="I79" s="364"/>
+      <c r="J79" s="364"/>
+      <c r="K79" s="362"/>
+      <c r="L79" s="364"/>
+    </row>
+    <row r="80" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B80" s="362"/>
+      <c r="C80" s="363"/>
+      <c r="D80" s="364"/>
+      <c r="E80" s="363"/>
+      <c r="F80" s="364"/>
+      <c r="G80" s="363"/>
+      <c r="H80" s="364"/>
+      <c r="I80" s="364"/>
+      <c r="J80" s="364"/>
+      <c r="K80" s="362"/>
+      <c r="L80" s="364"/>
+    </row>
+    <row r="81" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B81" s="362"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="364"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="364"/>
+      <c r="G81" s="363"/>
+      <c r="H81" s="364"/>
+      <c r="I81" s="364"/>
+      <c r="J81" s="364"/>
+      <c r="K81" s="362"/>
+      <c r="L81" s="364"/>
+    </row>
+    <row r="82" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B82" s="362"/>
+      <c r="C82" s="363"/>
+      <c r="D82" s="364"/>
+      <c r="E82" s="363"/>
+      <c r="F82" s="364"/>
+      <c r="G82" s="363"/>
+      <c r="H82" s="364"/>
+      <c r="I82" s="364"/>
+      <c r="J82" s="364"/>
+      <c r="K82" s="362"/>
+      <c r="L82" s="364"/>
+    </row>
+    <row r="83" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B83" s="362"/>
+      <c r="C83" s="363"/>
+      <c r="D83" s="364"/>
+      <c r="E83" s="363"/>
+      <c r="F83" s="364"/>
+      <c r="G83" s="363"/>
+      <c r="H83" s="364"/>
+      <c r="I83" s="364"/>
+      <c r="J83" s="364"/>
+      <c r="K83" s="362"/>
+      <c r="L83" s="364"/>
+    </row>
+    <row r="84" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B84" s="362"/>
+      <c r="C84" s="363"/>
+      <c r="D84" s="364"/>
+      <c r="E84" s="363"/>
+      <c r="F84" s="364"/>
+      <c r="G84" s="363"/>
+      <c r="H84" s="364"/>
+      <c r="I84" s="364"/>
+      <c r="J84" s="364"/>
+      <c r="K84" s="362"/>
+      <c r="L84" s="364"/>
+    </row>
+    <row r="85" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B85" s="362"/>
+      <c r="C85" s="363"/>
+      <c r="D85" s="364"/>
+      <c r="E85" s="363"/>
+      <c r="F85" s="364"/>
+      <c r="G85" s="363"/>
+      <c r="H85" s="364"/>
+      <c r="I85" s="364"/>
+      <c r="J85" s="364"/>
+      <c r="K85" s="362"/>
+      <c r="L85" s="364"/>
+    </row>
+    <row r="86" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B86" s="362"/>
+      <c r="C86" s="363"/>
+      <c r="D86" s="364"/>
+      <c r="E86" s="363"/>
+      <c r="F86" s="364"/>
+      <c r="G86" s="363"/>
+      <c r="H86" s="364"/>
+      <c r="I86" s="364"/>
+      <c r="J86" s="364"/>
+      <c r="K86" s="362"/>
+      <c r="L86" s="364"/>
+    </row>
+    <row r="87" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B87" s="362"/>
+      <c r="C87" s="363"/>
+      <c r="D87" s="364"/>
+      <c r="E87" s="363"/>
+      <c r="F87" s="364"/>
+      <c r="G87" s="363"/>
+      <c r="H87" s="364"/>
+      <c r="I87" s="364"/>
+      <c r="J87" s="364"/>
+      <c r="K87" s="362"/>
+      <c r="L87" s="364"/>
+    </row>
+    <row r="88" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B88" s="362"/>
+      <c r="C88" s="363"/>
+      <c r="D88" s="364"/>
+      <c r="E88" s="363"/>
+      <c r="F88" s="364"/>
+      <c r="G88" s="363"/>
+      <c r="H88" s="364"/>
+      <c r="I88" s="364"/>
+      <c r="J88" s="364"/>
+      <c r="K88" s="362"/>
+      <c r="L88" s="364"/>
+    </row>
+    <row r="89" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B89" s="362"/>
+      <c r="C89" s="363"/>
+      <c r="D89" s="364"/>
+      <c r="E89" s="363"/>
+      <c r="F89" s="364"/>
+      <c r="G89" s="363"/>
+      <c r="H89" s="364"/>
+      <c r="I89" s="364"/>
+      <c r="J89" s="364"/>
+      <c r="K89" s="362"/>
+      <c r="L89" s="364"/>
+    </row>
+    <row r="90" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B90" s="362"/>
+      <c r="C90" s="363"/>
+      <c r="D90" s="364"/>
+      <c r="E90" s="363"/>
+      <c r="F90" s="364"/>
+      <c r="G90" s="363"/>
+      <c r="H90" s="364"/>
+      <c r="I90" s="364"/>
+      <c r="J90" s="364"/>
+      <c r="K90" s="362"/>
+      <c r="L90" s="364"/>
+    </row>
+    <row r="91" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B91" s="362"/>
+      <c r="C91" s="363"/>
+      <c r="D91" s="364"/>
+      <c r="E91" s="363"/>
+      <c r="F91" s="364"/>
+      <c r="G91" s="363"/>
+      <c r="H91" s="364"/>
+      <c r="I91" s="364"/>
+      <c r="J91" s="364"/>
+      <c r="K91" s="362"/>
+      <c r="L91" s="364"/>
+    </row>
+    <row r="92" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B92" s="362"/>
+      <c r="C92" s="363"/>
+      <c r="D92" s="364"/>
+      <c r="E92" s="363"/>
+      <c r="F92" s="364"/>
+      <c r="G92" s="363"/>
+      <c r="H92" s="364"/>
+      <c r="I92" s="364"/>
+      <c r="J92" s="364"/>
+      <c r="K92" s="362"/>
+      <c r="L92" s="364"/>
+    </row>
+    <row r="93" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B93" s="362"/>
+      <c r="C93" s="363"/>
+      <c r="D93" s="364"/>
+      <c r="E93" s="363"/>
+      <c r="F93" s="364"/>
+      <c r="G93" s="363"/>
+      <c r="H93" s="364"/>
+      <c r="I93" s="364"/>
+      <c r="J93" s="364"/>
+      <c r="K93" s="362"/>
+      <c r="L93" s="364"/>
+    </row>
+    <row r="94" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B94" s="362"/>
+      <c r="C94" s="363"/>
+      <c r="D94" s="364"/>
+      <c r="E94" s="363"/>
+      <c r="F94" s="364"/>
+      <c r="G94" s="363"/>
+      <c r="H94" s="364"/>
+      <c r="I94" s="364"/>
+      <c r="J94" s="364"/>
+      <c r="K94" s="362"/>
+      <c r="L94" s="364"/>
+    </row>
+    <row r="95" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B95" s="362"/>
+      <c r="C95" s="363"/>
+      <c r="D95" s="364"/>
+      <c r="E95" s="363"/>
+      <c r="F95" s="364"/>
+      <c r="G95" s="363"/>
+      <c r="H95" s="364"/>
+      <c r="I95" s="364"/>
+      <c r="J95" s="364"/>
+      <c r="K95" s="362"/>
+      <c r="L95" s="364"/>
+    </row>
+    <row r="96" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B96" s="362"/>
+      <c r="C96" s="363"/>
+      <c r="D96" s="364"/>
+      <c r="E96" s="363"/>
+      <c r="F96" s="364"/>
+      <c r="G96" s="363"/>
+      <c r="H96" s="364"/>
+      <c r="I96" s="364"/>
+      <c r="J96" s="364"/>
+      <c r="K96" s="362"/>
+      <c r="L96" s="364"/>
+    </row>
+    <row r="97" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B97" s="362"/>
+      <c r="C97" s="363"/>
+      <c r="D97" s="364"/>
+      <c r="E97" s="363"/>
+      <c r="F97" s="364"/>
+      <c r="G97" s="363"/>
+      <c r="H97" s="364"/>
+      <c r="I97" s="364"/>
+      <c r="J97" s="364"/>
+      <c r="K97" s="362"/>
+      <c r="L97" s="364"/>
+    </row>
+    <row r="98" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B98" s="362"/>
+      <c r="C98" s="363"/>
+      <c r="D98" s="364"/>
+      <c r="E98" s="363"/>
+      <c r="F98" s="364"/>
+      <c r="G98" s="363"/>
+      <c r="H98" s="364"/>
+      <c r="I98" s="364"/>
+      <c r="J98" s="364"/>
+      <c r="K98" s="362"/>
+      <c r="L98" s="364"/>
+    </row>
+    <row r="99" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B99" s="362"/>
+      <c r="C99" s="363"/>
+      <c r="D99" s="364"/>
+      <c r="E99" s="363"/>
+      <c r="F99" s="364"/>
+      <c r="G99" s="363"/>
+      <c r="H99" s="364"/>
+      <c r="I99" s="364"/>
+      <c r="J99" s="364"/>
+      <c r="K99" s="362"/>
+      <c r="L99" s="364"/>
+    </row>
+    <row r="100" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B100" s="362"/>
+      <c r="C100" s="363"/>
+      <c r="D100" s="364"/>
+      <c r="E100" s="363"/>
+      <c r="F100" s="364"/>
+      <c r="G100" s="363"/>
+      <c r="H100" s="364"/>
+      <c r="I100" s="364"/>
+      <c r="J100" s="364"/>
+      <c r="K100" s="362"/>
+      <c r="L100" s="364"/>
+    </row>
+    <row r="101" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B101" s="362"/>
+      <c r="C101" s="363"/>
+      <c r="D101" s="364"/>
+      <c r="E101" s="363"/>
+      <c r="F101" s="364"/>
+      <c r="G101" s="363"/>
+      <c r="H101" s="364"/>
+      <c r="I101" s="364"/>
+      <c r="J101" s="364"/>
+      <c r="K101" s="362"/>
+      <c r="L101" s="364"/>
+    </row>
+    <row r="102" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B102" s="362"/>
+      <c r="C102" s="363"/>
+      <c r="D102" s="364"/>
+      <c r="E102" s="363"/>
+      <c r="F102" s="364"/>
+      <c r="G102" s="363"/>
+      <c r="H102" s="364"/>
+      <c r="I102" s="364"/>
+      <c r="J102" s="364"/>
+      <c r="K102" s="362"/>
+      <c r="L102" s="364"/>
+    </row>
+    <row r="103" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B103" s="362"/>
+      <c r="C103" s="363"/>
+      <c r="D103" s="364"/>
+      <c r="E103" s="363"/>
+      <c r="F103" s="364"/>
+      <c r="G103" s="363"/>
+      <c r="H103" s="364"/>
+      <c r="I103" s="364"/>
+      <c r="J103" s="364"/>
+      <c r="K103" s="362"/>
+      <c r="L103" s="364"/>
+    </row>
+    <row r="104" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B104" s="362"/>
+      <c r="C104" s="363"/>
+      <c r="D104" s="364"/>
+      <c r="E104" s="363"/>
+      <c r="F104" s="364"/>
+      <c r="G104" s="363"/>
+      <c r="H104" s="364"/>
+      <c r="I104" s="364"/>
+      <c r="J104" s="364"/>
+      <c r="K104" s="362"/>
+      <c r="L104" s="364"/>
+    </row>
+    <row r="105" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B105" s="362"/>
+      <c r="C105" s="363"/>
+      <c r="D105" s="364"/>
+      <c r="E105" s="363"/>
+      <c r="F105" s="364"/>
+      <c r="G105" s="363"/>
+      <c r="H105" s="364"/>
+      <c r="I105" s="364"/>
+      <c r="J105" s="364"/>
+      <c r="K105" s="362"/>
+      <c r="L105" s="364"/>
+    </row>
+    <row r="106" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B106" s="362"/>
+      <c r="C106" s="363"/>
+      <c r="D106" s="364"/>
+      <c r="E106" s="363"/>
+      <c r="F106" s="364"/>
+      <c r="G106" s="363"/>
+      <c r="H106" s="364"/>
+      <c r="I106" s="364"/>
+      <c r="J106" s="364"/>
+      <c r="K106" s="362"/>
+      <c r="L106" s="364"/>
+    </row>
+    <row r="107" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B107" s="362"/>
+      <c r="C107" s="363"/>
+      <c r="D107" s="364"/>
+      <c r="E107" s="363"/>
+      <c r="F107" s="364"/>
+      <c r="G107" s="363"/>
+      <c r="H107" s="364"/>
+      <c r="I107" s="364"/>
+      <c r="J107" s="364"/>
+      <c r="K107" s="362"/>
+      <c r="L107" s="364"/>
+    </row>
+    <row r="108" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B108" s="362"/>
+      <c r="C108" s="363"/>
+      <c r="D108" s="364"/>
+      <c r="E108" s="363"/>
+      <c r="F108" s="364"/>
+      <c r="G108" s="363"/>
+      <c r="H108" s="364"/>
+      <c r="I108" s="364"/>
+      <c r="J108" s="364"/>
+      <c r="K108" s="362"/>
+      <c r="L108" s="364"/>
+    </row>
+    <row r="109" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B109" s="362"/>
+      <c r="C109" s="363"/>
+      <c r="D109" s="364"/>
+      <c r="E109" s="363"/>
+      <c r="F109" s="364"/>
+      <c r="G109" s="363"/>
+      <c r="H109" s="364"/>
+      <c r="I109" s="364"/>
+      <c r="J109" s="364"/>
+      <c r="K109" s="362"/>
+      <c r="L109" s="364"/>
+    </row>
+    <row r="110" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B110" s="362"/>
+      <c r="C110" s="363"/>
+      <c r="D110" s="364"/>
+      <c r="E110" s="363"/>
+      <c r="F110" s="364"/>
+      <c r="G110" s="363"/>
+      <c r="H110" s="364"/>
+      <c r="I110" s="364"/>
+      <c r="J110" s="364"/>
+      <c r="K110" s="362"/>
+      <c r="L110" s="364"/>
+    </row>
+    <row r="111" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B111" s="362"/>
+      <c r="C111" s="363"/>
+      <c r="D111" s="364"/>
+      <c r="E111" s="363"/>
+      <c r="F111" s="364"/>
+      <c r="G111" s="363"/>
+      <c r="H111" s="364"/>
+      <c r="I111" s="364"/>
+      <c r="J111" s="364"/>
+      <c r="K111" s="362"/>
+      <c r="L111" s="364"/>
+    </row>
+    <row r="112" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B112" s="362"/>
+      <c r="C112" s="363"/>
+      <c r="D112" s="364"/>
+      <c r="E112" s="363"/>
+      <c r="F112" s="364"/>
+      <c r="G112" s="363"/>
+      <c r="H112" s="364"/>
+      <c r="I112" s="364"/>
+      <c r="J112" s="364"/>
+      <c r="K112" s="362"/>
+      <c r="L112" s="364"/>
+    </row>
+    <row r="113" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B113" s="362"/>
+      <c r="C113" s="363"/>
+      <c r="D113" s="364"/>
+      <c r="E113" s="363"/>
+      <c r="F113" s="364"/>
+      <c r="G113" s="363"/>
+      <c r="H113" s="364"/>
+      <c r="I113" s="364"/>
+      <c r="J113" s="364"/>
+      <c r="K113" s="362"/>
+      <c r="L113" s="364"/>
+    </row>
+    <row r="114" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B114" s="362"/>
+      <c r="C114" s="363"/>
+      <c r="D114" s="364"/>
+      <c r="E114" s="363"/>
+      <c r="F114" s="364"/>
+      <c r="G114" s="363"/>
+      <c r="H114" s="364"/>
+      <c r="I114" s="364"/>
+      <c r="J114" s="364"/>
+      <c r="K114" s="362"/>
+      <c r="L114" s="364"/>
+    </row>
+    <row r="115" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B115" s="362"/>
+      <c r="C115" s="363"/>
+      <c r="D115" s="364"/>
+      <c r="E115" s="363"/>
+      <c r="F115" s="364"/>
+      <c r="G115" s="363"/>
+      <c r="H115" s="364"/>
+      <c r="I115" s="364"/>
+      <c r="J115" s="364"/>
+      <c r="K115" s="362"/>
+      <c r="L115" s="364"/>
+    </row>
+    <row r="116" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B116" s="362"/>
+      <c r="C116" s="363"/>
+      <c r="D116" s="364"/>
+      <c r="E116" s="363"/>
+      <c r="F116" s="364"/>
+      <c r="G116" s="363"/>
+      <c r="H116" s="364"/>
+      <c r="I116" s="364"/>
+      <c r="J116" s="364"/>
+      <c r="K116" s="362"/>
+      <c r="L116" s="364"/>
+    </row>
+    <row r="117" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B117" s="362"/>
+      <c r="C117" s="363"/>
+      <c r="D117" s="364"/>
+      <c r="E117" s="363"/>
+      <c r="F117" s="364"/>
+      <c r="G117" s="363"/>
+      <c r="H117" s="364"/>
+      <c r="I117" s="364"/>
+      <c r="J117" s="364"/>
+      <c r="K117" s="362"/>
+      <c r="L117" s="364"/>
+    </row>
+    <row r="118" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B118" s="362"/>
+      <c r="C118" s="363"/>
+      <c r="D118" s="364"/>
+      <c r="E118" s="363"/>
+      <c r="F118" s="364"/>
+      <c r="G118" s="363"/>
+      <c r="H118" s="364"/>
+      <c r="I118" s="364"/>
+      <c r="J118" s="364"/>
+      <c r="K118" s="362"/>
+      <c r="L118" s="364"/>
+    </row>
+    <row r="119" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B119" s="362"/>
+      <c r="C119" s="363"/>
+      <c r="D119" s="364"/>
+      <c r="E119" s="363"/>
+      <c r="F119" s="364"/>
+      <c r="G119" s="363"/>
+      <c r="H119" s="364"/>
+      <c r="I119" s="364"/>
+      <c r="J119" s="364"/>
+      <c r="K119" s="362"/>
+      <c r="L119" s="364"/>
+    </row>
+    <row r="120" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B120" s="362"/>
+      <c r="C120" s="363"/>
+      <c r="D120" s="364"/>
+      <c r="E120" s="363"/>
+      <c r="F120" s="364"/>
+      <c r="G120" s="363"/>
+      <c r="H120" s="364"/>
+      <c r="I120" s="364"/>
+      <c r="J120" s="364"/>
+      <c r="K120" s="362"/>
+      <c r="L120" s="364"/>
+    </row>
+    <row r="121" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B121" s="362"/>
+      <c r="C121" s="363"/>
+      <c r="D121" s="364"/>
+      <c r="E121" s="363"/>
+      <c r="F121" s="364"/>
+      <c r="G121" s="363"/>
+      <c r="H121" s="364"/>
+      <c r="I121" s="364"/>
+      <c r="J121" s="364"/>
+      <c r="K121" s="362"/>
+      <c r="L121" s="364"/>
+    </row>
+    <row r="122" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B122" s="362"/>
+      <c r="C122" s="363"/>
+      <c r="D122" s="364"/>
+      <c r="E122" s="363"/>
+      <c r="F122" s="364"/>
+      <c r="G122" s="363"/>
+      <c r="H122" s="364"/>
+      <c r="I122" s="364"/>
+      <c r="J122" s="364"/>
+      <c r="K122" s="362"/>
+      <c r="L122" s="364"/>
+    </row>
+    <row r="123" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B123" s="362"/>
+      <c r="C123" s="363"/>
+      <c r="D123" s="364"/>
+      <c r="E123" s="363"/>
+      <c r="F123" s="364"/>
+      <c r="G123" s="363"/>
+      <c r="H123" s="364"/>
+      <c r="I123" s="364"/>
+      <c r="J123" s="364"/>
+      <c r="K123" s="362"/>
+      <c r="L123" s="364"/>
+    </row>
+    <row r="124" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B124" s="362"/>
+      <c r="C124" s="363"/>
+      <c r="D124" s="364"/>
+      <c r="E124" s="363"/>
+      <c r="F124" s="364"/>
+      <c r="G124" s="363"/>
+      <c r="H124" s="364"/>
+      <c r="I124" s="364"/>
+      <c r="J124" s="364"/>
+      <c r="K124" s="362"/>
+      <c r="L124" s="364"/>
+    </row>
+    <row r="125" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B125" s="362"/>
+      <c r="C125" s="363"/>
+      <c r="D125" s="364"/>
+      <c r="E125" s="363"/>
+      <c r="F125" s="364"/>
+      <c r="G125" s="363"/>
+      <c r="H125" s="364"/>
+      <c r="I125" s="364"/>
+      <c r="J125" s="364"/>
+      <c r="K125" s="362"/>
+      <c r="L125" s="364"/>
+    </row>
+    <row r="126" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B126" s="362"/>
+      <c r="C126" s="363"/>
+      <c r="D126" s="364"/>
+      <c r="E126" s="363"/>
+      <c r="F126" s="364"/>
+      <c r="G126" s="363"/>
+      <c r="H126" s="364"/>
+      <c r="I126" s="364"/>
+      <c r="J126" s="364"/>
+      <c r="K126" s="362"/>
+      <c r="L126" s="364"/>
+    </row>
+    <row r="127" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B127" s="362"/>
+      <c r="C127" s="363"/>
+      <c r="D127" s="364"/>
+      <c r="E127" s="363"/>
+      <c r="F127" s="364"/>
+      <c r="G127" s="363"/>
+      <c r="H127" s="364"/>
+      <c r="I127" s="364"/>
+      <c r="J127" s="364"/>
+      <c r="K127" s="362"/>
+      <c r="L127" s="364"/>
+    </row>
+    <row r="128" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B128" s="362"/>
+      <c r="C128" s="363"/>
+      <c r="D128" s="364"/>
+      <c r="E128" s="363"/>
+      <c r="F128" s="364"/>
+      <c r="G128" s="363"/>
+      <c r="H128" s="364"/>
+      <c r="I128" s="364"/>
+      <c r="J128" s="364"/>
+      <c r="K128" s="362"/>
+      <c r="L128" s="364"/>
+    </row>
+    <row r="129" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B129" s="362"/>
+      <c r="C129" s="363"/>
+      <c r="D129" s="364"/>
+      <c r="E129" s="363"/>
+      <c r="F129" s="364"/>
+      <c r="G129" s="363"/>
+      <c r="H129" s="364"/>
+      <c r="I129" s="364"/>
+      <c r="J129" s="364"/>
+      <c r="K129" s="362"/>
+      <c r="L129" s="364"/>
+    </row>
+    <row r="130" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B130" s="362"/>
+      <c r="C130" s="363"/>
+      <c r="D130" s="364"/>
+      <c r="E130" s="363"/>
+      <c r="F130" s="364"/>
+      <c r="G130" s="363"/>
+      <c r="H130" s="364"/>
+      <c r="I130" s="364"/>
+      <c r="J130" s="364"/>
+      <c r="K130" s="362"/>
+      <c r="L130" s="364"/>
+    </row>
+    <row r="131" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B131" s="362"/>
+      <c r="C131" s="363"/>
+      <c r="D131" s="364"/>
+      <c r="E131" s="363"/>
+      <c r="F131" s="364"/>
+      <c r="G131" s="363"/>
+      <c r="H131" s="364"/>
+      <c r="I131" s="364"/>
+      <c r="J131" s="364"/>
+      <c r="K131" s="362"/>
+      <c r="L131" s="364"/>
+    </row>
+    <row r="132" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B132" s="362"/>
+      <c r="C132" s="363"/>
+      <c r="D132" s="364"/>
+      <c r="E132" s="363"/>
+      <c r="F132" s="364"/>
+      <c r="G132" s="363"/>
+      <c r="H132" s="364"/>
+      <c r="I132" s="364"/>
+      <c r="J132" s="364"/>
+      <c r="K132" s="362"/>
+      <c r="L132" s="364"/>
+    </row>
+    <row r="133" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B133" s="362"/>
+      <c r="C133" s="363"/>
+      <c r="D133" s="364"/>
+      <c r="E133" s="363"/>
+      <c r="F133" s="364"/>
+      <c r="G133" s="363"/>
+      <c r="H133" s="364"/>
+      <c r="I133" s="364"/>
+      <c r="J133" s="364"/>
+      <c r="K133" s="362"/>
+      <c r="L133" s="364"/>
+    </row>
+    <row r="134" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="364"/>
+      <c r="G134" s="363"/>
+      <c r="H134" s="364"/>
+      <c r="I134" s="364"/>
+      <c r="J134" s="364"/>
+      <c r="K134" s="362"/>
+      <c r="L134" s="364"/>
+    </row>
+    <row r="135" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B135" s="362"/>
+      <c r="C135" s="363"/>
+      <c r="D135" s="364"/>
+      <c r="E135" s="363"/>
+      <c r="F135" s="364"/>
+      <c r="G135" s="363"/>
+      <c r="H135" s="364"/>
+      <c r="I135" s="364"/>
+      <c r="J135" s="364"/>
+      <c r="K135" s="362"/>
+      <c r="L135" s="364"/>
+    </row>
+    <row r="136" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B136" s="362"/>
+      <c r="C136" s="363"/>
+      <c r="D136" s="364"/>
+      <c r="E136" s="363"/>
+      <c r="F136" s="364"/>
+      <c r="G136" s="363"/>
+      <c r="H136" s="364"/>
+      <c r="I136" s="364"/>
+      <c r="J136" s="364"/>
+      <c r="K136" s="362"/>
+      <c r="L136" s="364"/>
+    </row>
+    <row r="137" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B137" s="362"/>
+      <c r="C137" s="363"/>
+      <c r="D137" s="364"/>
+      <c r="E137" s="363"/>
+      <c r="F137" s="364"/>
+      <c r="G137" s="363"/>
+      <c r="H137" s="364"/>
+      <c r="I137" s="364"/>
+      <c r="J137" s="364"/>
+      <c r="K137" s="362"/>
+      <c r="L137" s="364"/>
+    </row>
+    <row r="138" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B138" s="362"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="364"/>
+      <c r="G138" s="363"/>
+      <c r="H138" s="364"/>
+      <c r="I138" s="364"/>
+      <c r="J138" s="364"/>
+      <c r="K138" s="362"/>
+      <c r="L138" s="364"/>
+    </row>
+    <row r="139" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B139" s="362"/>
+      <c r="C139" s="363"/>
+      <c r="D139" s="364"/>
+      <c r="E139" s="363"/>
+      <c r="F139" s="364"/>
+      <c r="G139" s="363"/>
+      <c r="H139" s="364"/>
+      <c r="I139" s="364"/>
+      <c r="J139" s="364"/>
+      <c r="K139" s="362"/>
+      <c r="L139" s="364"/>
+    </row>
+    <row r="140" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B140" s="362"/>
+      <c r="C140" s="363"/>
+      <c r="D140" s="364"/>
+      <c r="E140" s="363"/>
+      <c r="F140" s="364"/>
+      <c r="G140" s="363"/>
+      <c r="H140" s="364"/>
+      <c r="I140" s="364"/>
+      <c r="J140" s="364"/>
+      <c r="K140" s="362"/>
+      <c r="L140" s="364"/>
+    </row>
+    <row r="141" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B141" s="362"/>
+      <c r="C141" s="363"/>
+      <c r="D141" s="364"/>
+      <c r="E141" s="363"/>
+      <c r="F141" s="364"/>
+      <c r="G141" s="363"/>
+      <c r="H141" s="364"/>
+      <c r="I141" s="364"/>
+      <c r="J141" s="364"/>
+      <c r="K141" s="362"/>
+      <c r="L141" s="364"/>
+    </row>
+    <row r="142" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B142" s="362"/>
+      <c r="C142" s="363"/>
+      <c r="D142" s="364"/>
+      <c r="E142" s="363"/>
+      <c r="F142" s="364"/>
+      <c r="G142" s="363"/>
+      <c r="H142" s="364"/>
+      <c r="I142" s="364"/>
+      <c r="J142" s="364"/>
+      <c r="K142" s="362"/>
+      <c r="L142" s="364"/>
+    </row>
+    <row r="143" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B143" s="362"/>
+      <c r="C143" s="363"/>
+      <c r="D143" s="364"/>
+      <c r="E143" s="363"/>
+      <c r="F143" s="364"/>
+      <c r="G143" s="363"/>
+      <c r="H143" s="364"/>
+      <c r="I143" s="364"/>
+      <c r="J143" s="364"/>
+      <c r="K143" s="362"/>
+      <c r="L143" s="364"/>
+    </row>
+    <row r="144" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B144" s="362"/>
+      <c r="C144" s="363"/>
+      <c r="D144" s="364"/>
+      <c r="E144" s="363"/>
+      <c r="F144" s="364"/>
+      <c r="G144" s="363"/>
+      <c r="H144" s="364"/>
+      <c r="I144" s="364"/>
+      <c r="J144" s="364"/>
+      <c r="K144" s="362"/>
+      <c r="L144" s="364"/>
+    </row>
+    <row r="145" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B145" s="362"/>
+      <c r="C145" s="363"/>
+      <c r="D145" s="364"/>
+      <c r="E145" s="363"/>
+      <c r="F145" s="364"/>
+      <c r="G145" s="363"/>
+      <c r="H145" s="364"/>
+      <c r="I145" s="364"/>
+      <c r="J145" s="364"/>
+      <c r="K145" s="362"/>
+      <c r="L145" s="364"/>
+    </row>
+    <row r="146" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B146" s="362"/>
+      <c r="C146" s="363"/>
+      <c r="D146" s="364"/>
+      <c r="E146" s="363"/>
+      <c r="F146" s="364"/>
+      <c r="G146" s="363"/>
+      <c r="H146" s="364"/>
+      <c r="I146" s="364"/>
+      <c r="J146" s="364"/>
+      <c r="K146" s="362"/>
+      <c r="L146" s="364"/>
+    </row>
+    <row r="147" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B147" s="362"/>
+      <c r="C147" s="363"/>
+      <c r="D147" s="364"/>
+      <c r="E147" s="363"/>
+      <c r="F147" s="364"/>
+      <c r="G147" s="363"/>
+      <c r="H147" s="364"/>
+      <c r="I147" s="364"/>
+      <c r="J147" s="364"/>
+      <c r="K147" s="362"/>
+      <c r="L147" s="364"/>
+    </row>
+    <row r="148" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B148" s="362"/>
+      <c r="C148" s="363"/>
+      <c r="D148" s="364"/>
+      <c r="E148" s="363"/>
+      <c r="F148" s="364"/>
+      <c r="G148" s="363"/>
+      <c r="H148" s="364"/>
+      <c r="I148" s="364"/>
+      <c r="J148" s="364"/>
+      <c r="K148" s="362"/>
+      <c r="L148" s="364"/>
+    </row>
+    <row r="149" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B149" s="362"/>
+      <c r="C149" s="363"/>
+      <c r="D149" s="364"/>
+      <c r="E149" s="363"/>
+      <c r="F149" s="364"/>
+      <c r="G149" s="363"/>
+      <c r="H149" s="364"/>
+      <c r="I149" s="364"/>
+      <c r="J149" s="364"/>
+      <c r="K149" s="362"/>
+      <c r="L149" s="364"/>
+    </row>
+    <row r="150" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B150" s="362"/>
+      <c r="C150" s="363"/>
+      <c r="D150" s="364"/>
+      <c r="E150" s="363"/>
+      <c r="F150" s="364"/>
+      <c r="G150" s="363"/>
+      <c r="H150" s="364"/>
+      <c r="I150" s="364"/>
+      <c r="J150" s="364"/>
+      <c r="K150" s="362"/>
+      <c r="L150" s="364"/>
+    </row>
+    <row r="151" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B151" s="362"/>
+      <c r="C151" s="363"/>
+      <c r="D151" s="364"/>
+      <c r="E151" s="363"/>
+      <c r="F151" s="364"/>
+      <c r="G151" s="363"/>
+      <c r="H151" s="364"/>
+      <c r="I151" s="364"/>
+      <c r="J151" s="364"/>
+      <c r="K151" s="362"/>
+      <c r="L151" s="364"/>
+    </row>
+    <row r="152" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B152" s="362"/>
+      <c r="C152" s="363"/>
+      <c r="D152" s="364"/>
+      <c r="E152" s="363"/>
+      <c r="F152" s="364"/>
+      <c r="G152" s="363"/>
+      <c r="H152" s="364"/>
+      <c r="I152" s="364"/>
+      <c r="J152" s="364"/>
+      <c r="K152" s="362"/>
+      <c r="L152" s="364"/>
+    </row>
+    <row r="153" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B153" s="362"/>
+      <c r="C153" s="363"/>
+      <c r="D153" s="364"/>
+      <c r="E153" s="363"/>
+      <c r="F153" s="364"/>
+      <c r="G153" s="363"/>
+      <c r="H153" s="364"/>
+      <c r="I153" s="364"/>
+      <c r="J153" s="364"/>
+      <c r="K153" s="362"/>
+      <c r="L153" s="364"/>
+    </row>
+    <row r="154" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B154" s="362"/>
+      <c r="C154" s="363"/>
+      <c r="D154" s="364"/>
+      <c r="E154" s="363"/>
+      <c r="F154" s="364"/>
+      <c r="G154" s="363"/>
+      <c r="H154" s="364"/>
+      <c r="I154" s="364"/>
+      <c r="J154" s="364"/>
+      <c r="K154" s="362"/>
+      <c r="L154" s="364"/>
+    </row>
+    <row r="155" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B155" s="362"/>
+      <c r="C155" s="363"/>
+      <c r="D155" s="364"/>
+      <c r="E155" s="363"/>
+      <c r="F155" s="364"/>
+      <c r="G155" s="363"/>
+      <c r="H155" s="364"/>
+      <c r="I155" s="364"/>
+      <c r="J155" s="364"/>
+      <c r="K155" s="362"/>
+      <c r="L155" s="364"/>
+    </row>
+    <row r="156" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B156" s="362"/>
+      <c r="C156" s="363"/>
+      <c r="D156" s="364"/>
+      <c r="E156" s="363"/>
+      <c r="F156" s="364"/>
+      <c r="G156" s="363"/>
+      <c r="H156" s="364"/>
+      <c r="I156" s="364"/>
+      <c r="J156" s="364"/>
+      <c r="K156" s="362"/>
+      <c r="L156" s="364"/>
+    </row>
+    <row r="157" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B157" s="362"/>
+      <c r="C157" s="363"/>
+      <c r="D157" s="364"/>
+      <c r="E157" s="363"/>
+      <c r="F157" s="364"/>
+      <c r="G157" s="363"/>
+      <c r="H157" s="364"/>
+      <c r="I157" s="364"/>
+      <c r="J157" s="364"/>
+      <c r="K157" s="362"/>
+      <c r="L157" s="364"/>
+    </row>
+    <row r="158" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B158" s="362"/>
+      <c r="C158" s="363"/>
+      <c r="D158" s="364"/>
+      <c r="E158" s="363"/>
+      <c r="F158" s="364"/>
+      <c r="G158" s="363"/>
+      <c r="H158" s="364"/>
+      <c r="I158" s="364"/>
+      <c r="J158" s="364"/>
+      <c r="K158" s="362"/>
+      <c r="L158" s="364"/>
+    </row>
+    <row r="159" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B159" s="362"/>
+      <c r="C159" s="363"/>
+      <c r="D159" s="364"/>
+      <c r="E159" s="363"/>
+      <c r="F159" s="364"/>
+      <c r="G159" s="363"/>
+      <c r="H159" s="364"/>
+      <c r="I159" s="364"/>
+      <c r="J159" s="364"/>
+      <c r="K159" s="362"/>
+      <c r="L159" s="364"/>
+    </row>
+    <row r="160" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B160" s="362"/>
+      <c r="C160" s="363"/>
+      <c r="D160" s="364"/>
+      <c r="E160" s="363"/>
+      <c r="F160" s="364"/>
+      <c r="G160" s="363"/>
+      <c r="H160" s="364"/>
+      <c r="I160" s="364"/>
+      <c r="J160" s="364"/>
+      <c r="K160" s="362"/>
+      <c r="L160" s="364"/>
+    </row>
+    <row r="161" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B161" s="362"/>
+      <c r="C161" s="363"/>
+      <c r="D161" s="364"/>
+      <c r="E161" s="363"/>
+      <c r="F161" s="364"/>
+      <c r="G161" s="363"/>
+      <c r="H161" s="364"/>
+      <c r="I161" s="364"/>
+      <c r="J161" s="364"/>
+      <c r="K161" s="362"/>
+      <c r="L161" s="364"/>
+    </row>
+    <row r="162" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B162" s="362"/>
+      <c r="C162" s="363"/>
+      <c r="D162" s="364"/>
+      <c r="E162" s="363"/>
+      <c r="F162" s="364"/>
+      <c r="G162" s="363"/>
+      <c r="H162" s="364"/>
+      <c r="I162" s="364"/>
+      <c r="J162" s="364"/>
+      <c r="K162" s="362"/>
+      <c r="L162" s="364"/>
+    </row>
+    <row r="163" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B163" s="362"/>
+      <c r="C163" s="363"/>
+      <c r="D163" s="364"/>
+      <c r="E163" s="363"/>
+      <c r="F163" s="364"/>
+      <c r="G163" s="363"/>
+      <c r="H163" s="364"/>
+      <c r="I163" s="364"/>
+      <c r="J163" s="364"/>
+      <c r="K163" s="362"/>
+      <c r="L163" s="364"/>
+    </row>
+    <row r="164" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B164" s="362"/>
+      <c r="C164" s="363"/>
+      <c r="D164" s="364"/>
+      <c r="E164" s="363"/>
+      <c r="F164" s="364"/>
+      <c r="G164" s="363"/>
+      <c r="H164" s="364"/>
+      <c r="I164" s="364"/>
+      <c r="J164" s="364"/>
+      <c r="K164" s="362"/>
+      <c r="L164" s="364"/>
+    </row>
+    <row r="165" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B165" s="362"/>
+      <c r="C165" s="363"/>
+      <c r="D165" s="364"/>
+      <c r="E165" s="363"/>
+      <c r="F165" s="364"/>
+      <c r="G165" s="363"/>
+      <c r="H165" s="364"/>
+      <c r="I165" s="364"/>
+      <c r="J165" s="364"/>
+      <c r="K165" s="362"/>
+      <c r="L165" s="364"/>
+    </row>
+    <row r="166" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B166" s="362"/>
+      <c r="C166" s="363"/>
+      <c r="D166" s="364"/>
+      <c r="E166" s="363"/>
+      <c r="F166" s="364"/>
+      <c r="G166" s="363"/>
+      <c r="H166" s="364"/>
+      <c r="I166" s="364"/>
+      <c r="J166" s="364"/>
+      <c r="K166" s="362"/>
+      <c r="L166" s="364"/>
+    </row>
+    <row r="167" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B167" s="362"/>
+      <c r="C167" s="363"/>
+      <c r="D167" s="364"/>
+      <c r="E167" s="363"/>
+      <c r="F167" s="364"/>
+      <c r="G167" s="363"/>
+      <c r="H167" s="364"/>
+      <c r="I167" s="364"/>
+      <c r="J167" s="364"/>
+      <c r="K167" s="362"/>
+      <c r="L167" s="364"/>
+    </row>
+    <row r="168" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B168" s="362"/>
+      <c r="C168" s="363"/>
+      <c r="D168" s="364"/>
+      <c r="E168" s="363"/>
+      <c r="F168" s="364"/>
+      <c r="G168" s="363"/>
+      <c r="H168" s="364"/>
+      <c r="I168" s="364"/>
+      <c r="J168" s="364"/>
+      <c r="K168" s="362"/>
+      <c r="L168" s="364"/>
+    </row>
+    <row r="169" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B169" s="362"/>
+      <c r="C169" s="363"/>
+      <c r="D169" s="364"/>
+      <c r="E169" s="363"/>
+      <c r="F169" s="364"/>
+      <c r="G169" s="363"/>
+      <c r="H169" s="364"/>
+      <c r="I169" s="364"/>
+      <c r="J169" s="364"/>
+      <c r="K169" s="362"/>
+      <c r="L169" s="364"/>
+    </row>
+    <row r="170" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B170" s="362"/>
+      <c r="C170" s="363"/>
+      <c r="D170" s="364"/>
+      <c r="E170" s="363"/>
+      <c r="F170" s="364"/>
+      <c r="G170" s="363"/>
+      <c r="H170" s="364"/>
+      <c r="I170" s="364"/>
+      <c r="J170" s="364"/>
+      <c r="K170" s="362"/>
+      <c r="L170" s="364"/>
+    </row>
+    <row r="171" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B171" s="362"/>
+      <c r="C171" s="363"/>
+      <c r="D171" s="364"/>
+      <c r="E171" s="363"/>
+      <c r="F171" s="364"/>
+      <c r="G171" s="363"/>
+      <c r="H171" s="364"/>
+      <c r="I171" s="364"/>
+      <c r="J171" s="364"/>
+      <c r="K171" s="362"/>
+      <c r="L171" s="364"/>
+    </row>
+    <row r="172" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B172" s="362"/>
+      <c r="C172" s="363"/>
+      <c r="D172" s="364"/>
+      <c r="E172" s="363"/>
+      <c r="F172" s="364"/>
+      <c r="G172" s="363"/>
+      <c r="H172" s="364"/>
+      <c r="I172" s="364"/>
+      <c r="J172" s="364"/>
+      <c r="K172" s="362"/>
+      <c r="L172" s="364"/>
+    </row>
+    <row r="173" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B173" s="362"/>
+      <c r="C173" s="363"/>
+      <c r="D173" s="364"/>
+      <c r="E173" s="363"/>
+      <c r="F173" s="364"/>
+      <c r="G173" s="363"/>
+      <c r="H173" s="364"/>
+      <c r="I173" s="364"/>
+      <c r="J173" s="364"/>
+      <c r="K173" s="362"/>
+      <c r="L173" s="364"/>
+    </row>
+    <row r="174" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B174" s="362"/>
+      <c r="C174" s="363"/>
+      <c r="D174" s="364"/>
+      <c r="E174" s="363"/>
+      <c r="F174" s="364"/>
+      <c r="G174" s="363"/>
+      <c r="H174" s="364"/>
+      <c r="I174" s="364"/>
+      <c r="J174" s="364"/>
+      <c r="K174" s="362"/>
+      <c r="L174" s="364"/>
+    </row>
+    <row r="175" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B175" s="362"/>
+      <c r="C175" s="363"/>
+      <c r="D175" s="364"/>
+      <c r="E175" s="363"/>
+      <c r="F175" s="364"/>
+      <c r="G175" s="363"/>
+      <c r="H175" s="364"/>
+      <c r="I175" s="364"/>
+      <c r="J175" s="364"/>
+      <c r="K175" s="362"/>
+      <c r="L175" s="364"/>
+    </row>
+    <row r="176" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B176" s="362"/>
+      <c r="C176" s="363"/>
+      <c r="D176" s="364"/>
+      <c r="E176" s="363"/>
+      <c r="F176" s="364"/>
+      <c r="G176" s="363"/>
+      <c r="H176" s="364"/>
+      <c r="I176" s="364"/>
+      <c r="J176" s="364"/>
+      <c r="K176" s="362"/>
+      <c r="L176" s="364"/>
+    </row>
+    <row r="177" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B177" s="362"/>
+      <c r="C177" s="363"/>
+      <c r="D177" s="364"/>
+      <c r="E177" s="363"/>
+      <c r="F177" s="364"/>
+      <c r="G177" s="363"/>
+      <c r="H177" s="364"/>
+      <c r="I177" s="364"/>
+      <c r="J177" s="364"/>
+      <c r="K177" s="362"/>
+      <c r="L177" s="364"/>
+    </row>
+    <row r="178" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B178" s="362"/>
+      <c r="C178" s="363"/>
+      <c r="D178" s="364"/>
+      <c r="E178" s="363"/>
+      <c r="F178" s="364"/>
+      <c r="G178" s="363"/>
+      <c r="H178" s="364"/>
+      <c r="I178" s="364"/>
+      <c r="J178" s="364"/>
+      <c r="K178" s="362"/>
+      <c r="L178" s="364"/>
+    </row>
+    <row r="179" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B179" s="362"/>
+      <c r="C179" s="363"/>
+      <c r="D179" s="364"/>
+      <c r="E179" s="363"/>
+      <c r="F179" s="364"/>
+      <c r="G179" s="363"/>
+      <c r="H179" s="364"/>
+      <c r="I179" s="364"/>
+      <c r="J179" s="364"/>
+      <c r="K179" s="362"/>
+      <c r="L179" s="364"/>
+    </row>
+    <row r="180" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B180" s="362"/>
+      <c r="C180" s="363"/>
+      <c r="D180" s="364"/>
+      <c r="E180" s="363"/>
+      <c r="F180" s="364"/>
+      <c r="G180" s="363"/>
+      <c r="H180" s="364"/>
+      <c r="I180" s="364"/>
+      <c r="J180" s="364"/>
+      <c r="K180" s="362"/>
+      <c r="L180" s="364"/>
+    </row>
+    <row r="181" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B181" s="362"/>
+      <c r="C181" s="363"/>
+      <c r="D181" s="364"/>
+      <c r="E181" s="363"/>
+      <c r="F181" s="364"/>
+      <c r="G181" s="363"/>
+      <c r="H181" s="364"/>
+      <c r="I181" s="364"/>
+      <c r="J181" s="364"/>
+      <c r="K181" s="362"/>
+      <c r="L181" s="364"/>
+    </row>
+    <row r="182" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B182" s="362"/>
+      <c r="C182" s="363"/>
+      <c r="D182" s="364"/>
+      <c r="E182" s="363"/>
+      <c r="F182" s="364"/>
+      <c r="G182" s="363"/>
+      <c r="H182" s="364"/>
+      <c r="I182" s="364"/>
+      <c r="J182" s="364"/>
+      <c r="K182" s="362"/>
+      <c r="L182" s="364"/>
+    </row>
+    <row r="183" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B183" s="362"/>
+      <c r="C183" s="363"/>
+      <c r="D183" s="364"/>
+      <c r="E183" s="363"/>
+      <c r="F183" s="364"/>
+      <c r="G183" s="363"/>
+      <c r="H183" s="364"/>
+      <c r="I183" s="364"/>
+      <c r="J183" s="364"/>
+      <c r="K183" s="362"/>
+      <c r="L183" s="364"/>
+    </row>
+    <row r="184" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B184" s="362"/>
+      <c r="C184" s="363"/>
+      <c r="D184" s="364"/>
+      <c r="E184" s="363"/>
+      <c r="F184" s="364"/>
+      <c r="G184" s="363"/>
+      <c r="H184" s="364"/>
+      <c r="I184" s="364"/>
+      <c r="J184" s="364"/>
+      <c r="K184" s="362"/>
+      <c r="L184" s="364"/>
+    </row>
+    <row r="185" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B185" s="362"/>
+      <c r="C185" s="363"/>
+      <c r="D185" s="364"/>
+      <c r="E185" s="363"/>
+      <c r="F185" s="364"/>
+      <c r="G185" s="363"/>
+      <c r="H185" s="364"/>
+      <c r="I185" s="364"/>
+      <c r="J185" s="364"/>
+      <c r="K185" s="362"/>
+      <c r="L185" s="364"/>
+    </row>
+    <row r="186" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B186" s="362"/>
+      <c r="C186" s="363"/>
+      <c r="D186" s="364"/>
+      <c r="E186" s="363"/>
+      <c r="F186" s="364"/>
+      <c r="G186" s="363"/>
+      <c r="H186" s="364"/>
+      <c r="I186" s="364"/>
+      <c r="J186" s="364"/>
+      <c r="K186" s="362"/>
+      <c r="L186" s="364"/>
+    </row>
+    <row r="187" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B187" s="362"/>
+      <c r="C187" s="363"/>
+      <c r="D187" s="364"/>
+      <c r="E187" s="363"/>
+      <c r="F187" s="364"/>
+      <c r="G187" s="363"/>
+      <c r="H187" s="364"/>
+      <c r="I187" s="364"/>
+      <c r="J187" s="364"/>
+      <c r="K187" s="362"/>
+      <c r="L187" s="364"/>
+    </row>
+    <row r="188" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B188" s="362"/>
+      <c r="C188" s="363"/>
+      <c r="D188" s="364"/>
+      <c r="E188" s="363"/>
+      <c r="F188" s="364"/>
+      <c r="G188" s="363"/>
+      <c r="H188" s="364"/>
+      <c r="I188" s="364"/>
+      <c r="J188" s="364"/>
+      <c r="K188" s="362"/>
+      <c r="L188" s="364"/>
+    </row>
+    <row r="189" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B189" s="362"/>
+      <c r="C189" s="363"/>
+      <c r="D189" s="364"/>
+      <c r="E189" s="363"/>
+      <c r="F189" s="364"/>
+      <c r="G189" s="363"/>
+      <c r="H189" s="364"/>
+      <c r="I189" s="364"/>
+      <c r="J189" s="364"/>
+      <c r="K189" s="362"/>
+      <c r="L189" s="364"/>
+    </row>
+    <row r="190" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B190" s="362"/>
+      <c r="C190" s="363"/>
+      <c r="D190" s="364"/>
+      <c r="E190" s="363"/>
+      <c r="F190" s="364"/>
+      <c r="G190" s="363"/>
+      <c r="H190" s="364"/>
+      <c r="I190" s="364"/>
+      <c r="J190" s="364"/>
+      <c r="K190" s="362"/>
+      <c r="L190" s="364"/>
+    </row>
+    <row r="191" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B191" s="362"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="364"/>
+      <c r="G191" s="363"/>
+      <c r="H191" s="364"/>
+      <c r="I191" s="364"/>
+      <c r="J191" s="364"/>
+      <c r="K191" s="362"/>
+      <c r="L191" s="364"/>
+    </row>
+    <row r="192" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B192" s="362"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="364"/>
+      <c r="G192" s="363"/>
+      <c r="H192" s="364"/>
+      <c r="I192" s="364"/>
+      <c r="J192" s="364"/>
+      <c r="K192" s="362"/>
+      <c r="L192" s="364"/>
+    </row>
+    <row r="193" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B193" s="362"/>
+      <c r="C193" s="363"/>
+      <c r="D193" s="364"/>
+      <c r="E193" s="363"/>
+      <c r="F193" s="364"/>
+      <c r="G193" s="363"/>
+      <c r="H193" s="364"/>
+      <c r="I193" s="364"/>
+      <c r="J193" s="364"/>
+      <c r="K193" s="362"/>
+      <c r="L193" s="364"/>
+    </row>
+    <row r="194" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B194" s="362"/>
+      <c r="C194" s="363"/>
+      <c r="D194" s="364"/>
+      <c r="E194" s="363"/>
+      <c r="F194" s="364"/>
+      <c r="G194" s="363"/>
+      <c r="H194" s="364"/>
+      <c r="I194" s="364"/>
+      <c r="J194" s="364"/>
+      <c r="K194" s="362"/>
+      <c r="L194" s="364"/>
+    </row>
+    <row r="195" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B195" s="362"/>
+      <c r="C195" s="363"/>
+      <c r="D195" s="364"/>
+      <c r="E195" s="363"/>
+      <c r="F195" s="364"/>
+      <c r="G195" s="363"/>
+      <c r="H195" s="364"/>
+      <c r="I195" s="364"/>
+      <c r="J195" s="364"/>
+      <c r="K195" s="362"/>
+      <c r="L195" s="364"/>
+    </row>
+    <row r="196" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B196" s="362"/>
+      <c r="C196" s="363"/>
+      <c r="D196" s="364"/>
+      <c r="E196" s="363"/>
+      <c r="F196" s="364"/>
+      <c r="G196" s="363"/>
+      <c r="H196" s="364"/>
+      <c r="I196" s="364"/>
+      <c r="J196" s="364"/>
+      <c r="K196" s="362"/>
+      <c r="L196" s="364"/>
+    </row>
+    <row r="197" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B197" s="362"/>
+      <c r="C197" s="363"/>
+      <c r="D197" s="364"/>
+      <c r="E197" s="363"/>
+      <c r="F197" s="364"/>
+      <c r="G197" s="363"/>
+      <c r="H197" s="364"/>
+      <c r="I197" s="364"/>
+      <c r="J197" s="364"/>
+      <c r="K197" s="362"/>
+      <c r="L197" s="364"/>
+    </row>
+    <row r="198" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B198" s="362"/>
+      <c r="C198" s="363"/>
+      <c r="D198" s="364"/>
+      <c r="E198" s="363"/>
+      <c r="F198" s="364"/>
+      <c r="G198" s="363"/>
+      <c r="H198" s="364"/>
+      <c r="I198" s="364"/>
+      <c r="J198" s="364"/>
+      <c r="K198" s="362"/>
+      <c r="L198" s="364"/>
+    </row>
+    <row r="199" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B199" s="362"/>
+      <c r="C199" s="363"/>
+      <c r="D199" s="364"/>
+      <c r="E199" s="363"/>
+      <c r="F199" s="364"/>
+      <c r="G199" s="363"/>
+      <c r="H199" s="364"/>
+      <c r="I199" s="364"/>
+      <c r="J199" s="364"/>
+      <c r="K199" s="362"/>
+      <c r="L199" s="364"/>
+    </row>
+    <row r="200" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B200" s="362"/>
+      <c r="C200" s="363"/>
+      <c r="D200" s="364"/>
+      <c r="E200" s="363"/>
+      <c r="F200" s="364"/>
+      <c r="G200" s="363"/>
+      <c r="H200" s="364"/>
+      <c r="I200" s="364"/>
+      <c r="J200" s="364"/>
+      <c r="K200" s="362"/>
+      <c r="L200" s="364"/>
+    </row>
+    <row r="201" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B201" s="362"/>
+      <c r="C201" s="363"/>
+      <c r="D201" s="364"/>
+      <c r="E201" s="363"/>
+      <c r="F201" s="364"/>
+      <c r="G201" s="363"/>
+      <c r="H201" s="364"/>
+      <c r="I201" s="364"/>
+      <c r="J201" s="364"/>
+      <c r="K201" s="362"/>
+      <c r="L201" s="364"/>
+    </row>
+    <row r="202" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B202" s="362"/>
+      <c r="C202" s="363"/>
+      <c r="D202" s="364"/>
+      <c r="E202" s="363"/>
+      <c r="F202" s="364"/>
+      <c r="G202" s="363"/>
+      <c r="H202" s="364"/>
+      <c r="I202" s="364"/>
+      <c r="J202" s="364"/>
+      <c r="K202" s="362"/>
+      <c r="L202" s="364"/>
+    </row>
+    <row r="203" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B203" s="362"/>
+      <c r="C203" s="363"/>
+      <c r="D203" s="364"/>
+      <c r="E203" s="363"/>
+      <c r="F203" s="364"/>
+      <c r="G203" s="363"/>
+      <c r="H203" s="364"/>
+      <c r="I203" s="364"/>
+      <c r="J203" s="364"/>
+      <c r="K203" s="362"/>
+      <c r="L203" s="364"/>
+    </row>
+    <row r="204" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B204" s="362"/>
+      <c r="C204" s="363"/>
+      <c r="D204" s="364"/>
+      <c r="E204" s="363"/>
+      <c r="F204" s="364"/>
+      <c r="G204" s="363"/>
+      <c r="H204" s="364"/>
+      <c r="I204" s="364"/>
+      <c r="J204" s="364"/>
+      <c r="K204" s="362"/>
+      <c r="L204" s="364"/>
+    </row>
+    <row r="205" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B205" s="362"/>
+      <c r="C205" s="363"/>
+      <c r="D205" s="364"/>
+      <c r="E205" s="363"/>
+      <c r="F205" s="364"/>
+      <c r="G205" s="363"/>
+      <c r="H205" s="364"/>
+      <c r="I205" s="364"/>
+      <c r="J205" s="364"/>
+      <c r="K205" s="362"/>
+      <c r="L205" s="364"/>
+    </row>
+    <row r="206" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B206" s="362"/>
+      <c r="C206" s="363"/>
+      <c r="D206" s="364"/>
+      <c r="E206" s="363"/>
+      <c r="F206" s="364"/>
+      <c r="G206" s="363"/>
+      <c r="H206" s="364"/>
+      <c r="I206" s="364"/>
+      <c r="J206" s="364"/>
+      <c r="K206" s="362"/>
+      <c r="L206" s="364"/>
+    </row>
+    <row r="207" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B207" s="362"/>
+      <c r="C207" s="363"/>
+      <c r="D207" s="364"/>
+      <c r="E207" s="363"/>
+      <c r="F207" s="364"/>
+      <c r="G207" s="363"/>
+      <c r="H207" s="364"/>
+      <c r="I207" s="364"/>
+      <c r="J207" s="364"/>
+      <c r="K207" s="362"/>
+      <c r="L207" s="364"/>
+    </row>
+    <row r="208" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B208" s="362"/>
+      <c r="C208" s="363"/>
+      <c r="D208" s="364"/>
+      <c r="E208" s="363"/>
+      <c r="F208" s="364"/>
+      <c r="G208" s="363"/>
+      <c r="H208" s="364"/>
+      <c r="I208" s="364"/>
+      <c r="J208" s="364"/>
+      <c r="K208" s="362"/>
+      <c r="L208" s="364"/>
+    </row>
+    <row r="209" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B209" s="362"/>
+      <c r="C209" s="363"/>
+      <c r="D209" s="364"/>
+      <c r="E209" s="363"/>
+      <c r="F209" s="364"/>
+      <c r="G209" s="363"/>
+      <c r="H209" s="364"/>
+      <c r="I209" s="364"/>
+      <c r="J209" s="364"/>
+      <c r="K209" s="362"/>
+      <c r="L209" s="364"/>
+    </row>
+    <row r="210" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B210" s="362"/>
+      <c r="C210" s="363"/>
+      <c r="D210" s="364"/>
+      <c r="E210" s="363"/>
+      <c r="F210" s="364"/>
+      <c r="G210" s="363"/>
+      <c r="H210" s="364"/>
+      <c r="I210" s="364"/>
+      <c r="J210" s="364"/>
+      <c r="K210" s="362"/>
+      <c r="L210" s="364"/>
+    </row>
+    <row r="211" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B211" s="362"/>
+      <c r="C211" s="363"/>
+      <c r="D211" s="364"/>
+      <c r="E211" s="363"/>
+      <c r="F211" s="364"/>
+      <c r="G211" s="363"/>
+      <c r="H211" s="364"/>
+      <c r="I211" s="364"/>
+      <c r="J211" s="364"/>
+      <c r="K211" s="362"/>
+      <c r="L211" s="364"/>
+    </row>
+    <row r="212" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B212" s="362"/>
+      <c r="C212" s="363"/>
+      <c r="D212" s="364"/>
+      <c r="E212" s="363"/>
+      <c r="F212" s="364"/>
+      <c r="G212" s="363"/>
+      <c r="H212" s="364"/>
+      <c r="I212" s="364"/>
+      <c r="J212" s="364"/>
+      <c r="K212" s="362"/>
+      <c r="L212" s="364"/>
+    </row>
+    <row r="213" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B213" s="362"/>
+      <c r="C213" s="363"/>
+      <c r="D213" s="364"/>
+      <c r="E213" s="363"/>
+      <c r="F213" s="364"/>
+      <c r="G213" s="363"/>
+      <c r="H213" s="364"/>
+      <c r="I213" s="364"/>
+      <c r="J213" s="364"/>
+      <c r="K213" s="362"/>
+      <c r="L213" s="364"/>
+    </row>
+    <row r="214" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B214" s="362"/>
+      <c r="C214" s="363"/>
+      <c r="D214" s="364"/>
+      <c r="E214" s="363"/>
+      <c r="F214" s="364"/>
+      <c r="G214" s="363"/>
+      <c r="H214" s="364"/>
+      <c r="I214" s="364"/>
+      <c r="J214" s="364"/>
+      <c r="K214" s="362"/>
+      <c r="L214" s="364"/>
+    </row>
+    <row r="215" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B215" s="362"/>
+      <c r="C215" s="363"/>
+      <c r="D215" s="364"/>
+      <c r="E215" s="363"/>
+      <c r="F215" s="364"/>
+      <c r="G215" s="363"/>
+      <c r="H215" s="364"/>
+      <c r="I215" s="364"/>
+      <c r="J215" s="364"/>
+      <c r="K215" s="362"/>
+      <c r="L215" s="364"/>
+    </row>
+    <row r="216" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B216" s="362"/>
+      <c r="C216" s="363"/>
+      <c r="D216" s="364"/>
+      <c r="E216" s="363"/>
+      <c r="F216" s="364"/>
+      <c r="G216" s="363"/>
+      <c r="H216" s="364"/>
+      <c r="I216" s="364"/>
+      <c r="J216" s="364"/>
+      <c r="K216" s="362"/>
+      <c r="L216" s="364"/>
+    </row>
+    <row r="217" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B217" s="362"/>
+      <c r="C217" s="363"/>
+      <c r="D217" s="364"/>
+      <c r="E217" s="363"/>
+      <c r="F217" s="364"/>
+      <c r="G217" s="363"/>
+      <c r="H217" s="364"/>
+      <c r="I217" s="364"/>
+      <c r="J217" s="364"/>
+      <c r="K217" s="362"/>
+      <c r="L217" s="364"/>
+    </row>
+    <row r="218" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B218" s="362"/>
+      <c r="C218" s="363"/>
+      <c r="D218" s="364"/>
+      <c r="E218" s="363"/>
+      <c r="F218" s="364"/>
+      <c r="G218" s="363"/>
+      <c r="H218" s="364"/>
+      <c r="I218" s="364"/>
+      <c r="J218" s="364"/>
+      <c r="K218" s="362"/>
+      <c r="L218" s="364"/>
+    </row>
+    <row r="219" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B219" s="362"/>
+      <c r="C219" s="363"/>
+      <c r="D219" s="364"/>
+      <c r="E219" s="363"/>
+      <c r="F219" s="364"/>
+      <c r="G219" s="363"/>
+      <c r="H219" s="364"/>
+      <c r="I219" s="364"/>
+      <c r="J219" s="364"/>
+      <c r="K219" s="362"/>
+      <c r="L219" s="364"/>
+    </row>
+    <row r="220" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B220" s="362"/>
+      <c r="C220" s="363"/>
+      <c r="D220" s="364"/>
+      <c r="E220" s="363"/>
+      <c r="F220" s="364"/>
+      <c r="G220" s="363"/>
+      <c r="H220" s="364"/>
+      <c r="I220" s="364"/>
+      <c r="J220" s="364"/>
+      <c r="K220" s="362"/>
+      <c r="L220" s="364"/>
+    </row>
+    <row r="221" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B221" s="362"/>
+      <c r="C221" s="363"/>
+      <c r="D221" s="364"/>
+      <c r="E221" s="363"/>
+      <c r="F221" s="364"/>
+      <c r="G221" s="363"/>
+      <c r="H221" s="364"/>
+      <c r="I221" s="364"/>
+      <c r="J221" s="364"/>
+      <c r="K221" s="362"/>
+      <c r="L221" s="364"/>
+    </row>
+    <row r="222" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B222" s="362"/>
+      <c r="C222" s="363"/>
+      <c r="D222" s="364"/>
+      <c r="E222" s="363"/>
+      <c r="F222" s="364"/>
+      <c r="G222" s="363"/>
+      <c r="H222" s="364"/>
+      <c r="I222" s="364"/>
+      <c r="J222" s="364"/>
+      <c r="K222" s="362"/>
+      <c r="L222" s="364"/>
+    </row>
+    <row r="223" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B223" s="362"/>
+      <c r="C223" s="363"/>
+      <c r="D223" s="364"/>
+      <c r="E223" s="363"/>
+      <c r="F223" s="364"/>
+      <c r="G223" s="363"/>
+      <c r="H223" s="364"/>
+      <c r="I223" s="364"/>
+      <c r="J223" s="364"/>
+      <c r="K223" s="362"/>
+      <c r="L223" s="364"/>
+    </row>
+    <row r="224" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B224" s="362"/>
+      <c r="C224" s="363"/>
+      <c r="D224" s="364"/>
+      <c r="E224" s="363"/>
+      <c r="F224" s="364"/>
+      <c r="G224" s="363"/>
+      <c r="H224" s="364"/>
+      <c r="I224" s="364"/>
+      <c r="J224" s="364"/>
+      <c r="K224" s="362"/>
+      <c r="L224" s="364"/>
+    </row>
+    <row r="225" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B225" s="362"/>
+      <c r="C225" s="363"/>
+      <c r="D225" s="364"/>
+      <c r="E225" s="363"/>
+      <c r="F225" s="364"/>
+      <c r="G225" s="363"/>
+      <c r="H225" s="364"/>
+      <c r="I225" s="364"/>
+      <c r="J225" s="364"/>
+      <c r="K225" s="362"/>
+      <c r="L225" s="364"/>
+    </row>
+    <row r="226" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B226" s="362"/>
+      <c r="C226" s="363"/>
+      <c r="D226" s="364"/>
+      <c r="E226" s="363"/>
+      <c r="F226" s="364"/>
+      <c r="G226" s="363"/>
+      <c r="H226" s="364"/>
+      <c r="I226" s="364"/>
+      <c r="J226" s="364"/>
+      <c r="K226" s="362"/>
+      <c r="L226" s="364"/>
+    </row>
+    <row r="227" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B227" s="362"/>
+      <c r="C227" s="363"/>
+      <c r="D227" s="364"/>
+      <c r="E227" s="363"/>
+      <c r="F227" s="364"/>
+      <c r="G227" s="363"/>
+      <c r="H227" s="364"/>
+      <c r="I227" s="364"/>
+      <c r="J227" s="364"/>
+      <c r="K227" s="362"/>
+      <c r="L227" s="364"/>
+    </row>
+    <row r="228" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B228" s="362"/>
+      <c r="C228" s="363"/>
+      <c r="D228" s="364"/>
+      <c r="E228" s="363"/>
+      <c r="F228" s="364"/>
+      <c r="G228" s="363"/>
+      <c r="H228" s="364"/>
+      <c r="I228" s="364"/>
+      <c r="J228" s="364"/>
+      <c r="K228" s="362"/>
+      <c r="L228" s="364"/>
+    </row>
+    <row r="229" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B229" s="362"/>
+      <c r="C229" s="363"/>
+      <c r="D229" s="364"/>
+      <c r="E229" s="363"/>
+      <c r="F229" s="364"/>
+      <c r="G229" s="363"/>
+      <c r="H229" s="364"/>
+      <c r="I229" s="364"/>
+      <c r="J229" s="364"/>
+      <c r="K229" s="362"/>
+      <c r="L229" s="364"/>
+    </row>
+    <row r="230" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B230" s="362"/>
+      <c r="C230" s="363"/>
+      <c r="D230" s="364"/>
+      <c r="E230" s="363"/>
+      <c r="F230" s="364"/>
+      <c r="G230" s="363"/>
+      <c r="H230" s="364"/>
+      <c r="I230" s="364"/>
+      <c r="J230" s="364"/>
+      <c r="K230" s="362"/>
+      <c r="L230" s="364"/>
+    </row>
+    <row r="231" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B231" s="362"/>
+      <c r="C231" s="363"/>
+      <c r="D231" s="364"/>
+      <c r="E231" s="363"/>
+      <c r="F231" s="364"/>
+      <c r="G231" s="363"/>
+      <c r="H231" s="364"/>
+      <c r="I231" s="364"/>
+      <c r="J231" s="364"/>
+      <c r="K231" s="362"/>
+      <c r="L231" s="364"/>
+    </row>
+    <row r="232" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B232" s="362"/>
+      <c r="C232" s="363"/>
+      <c r="D232" s="364"/>
+      <c r="E232" s="363"/>
+      <c r="F232" s="364"/>
+      <c r="G232" s="363"/>
+      <c r="H232" s="364"/>
+      <c r="I232" s="364"/>
+      <c r="J232" s="364"/>
+      <c r="K232" s="362"/>
+      <c r="L232" s="364"/>
+    </row>
+    <row r="233" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B233" s="362"/>
+      <c r="C233" s="363"/>
+      <c r="D233" s="364"/>
+      <c r="E233" s="363"/>
+      <c r="F233" s="364"/>
+      <c r="G233" s="363"/>
+      <c r="H233" s="364"/>
+      <c r="I233" s="364"/>
+      <c r="J233" s="364"/>
+      <c r="K233" s="362"/>
+      <c r="L233" s="364"/>
+    </row>
+    <row r="234" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B234" s="362"/>
+      <c r="C234" s="363"/>
+      <c r="D234" s="364"/>
+      <c r="E234" s="363"/>
+      <c r="F234" s="364"/>
+      <c r="G234" s="363"/>
+      <c r="H234" s="364"/>
+      <c r="I234" s="364"/>
+      <c r="J234" s="364"/>
+      <c r="K234" s="362"/>
+      <c r="L234" s="364"/>
+    </row>
+    <row r="235" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B235" s="362"/>
+      <c r="C235" s="363"/>
+      <c r="D235" s="364"/>
+      <c r="E235" s="363"/>
+      <c r="F235" s="364"/>
+      <c r="G235" s="363"/>
+      <c r="H235" s="364"/>
+      <c r="I235" s="364"/>
+      <c r="J235" s="364"/>
+      <c r="K235" s="362"/>
+      <c r="L235" s="364"/>
+    </row>
+    <row r="236" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B236" s="362"/>
+      <c r="C236" s="363"/>
+      <c r="D236" s="364"/>
+      <c r="E236" s="363"/>
+      <c r="F236" s="364"/>
+      <c r="G236" s="363"/>
+      <c r="H236" s="364"/>
+      <c r="I236" s="364"/>
+      <c r="J236" s="364"/>
+      <c r="K236" s="362"/>
+      <c r="L236" s="364"/>
+    </row>
+    <row r="237" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B237" s="362"/>
+      <c r="C237" s="363"/>
+      <c r="D237" s="364"/>
+      <c r="E237" s="363"/>
+      <c r="F237" s="364"/>
+      <c r="G237" s="363"/>
+      <c r="H237" s="364"/>
+      <c r="I237" s="364"/>
+      <c r="J237" s="364"/>
+      <c r="K237" s="362"/>
+      <c r="L237" s="364"/>
+    </row>
+    <row r="238" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B238" s="362"/>
+      <c r="C238" s="363"/>
+      <c r="D238" s="364"/>
+      <c r="E238" s="363"/>
+      <c r="F238" s="364"/>
+      <c r="G238" s="363"/>
+      <c r="H238" s="364"/>
+      <c r="I238" s="364"/>
+      <c r="J238" s="364"/>
+      <c r="K238" s="362"/>
+      <c r="L238" s="364"/>
+    </row>
+    <row r="239" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B239" s="362"/>
+      <c r="C239" s="363"/>
+      <c r="D239" s="364"/>
+      <c r="E239" s="363"/>
+      <c r="F239" s="364"/>
+      <c r="G239" s="363"/>
+      <c r="H239" s="364"/>
+      <c r="I239" s="364"/>
+      <c r="J239" s="364"/>
+      <c r="K239" s="362"/>
+      <c r="L239" s="364"/>
+    </row>
+    <row r="240" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B240" s="362"/>
+      <c r="C240" s="363"/>
+      <c r="D240" s="364"/>
+      <c r="E240" s="363"/>
+      <c r="F240" s="364"/>
+      <c r="G240" s="363"/>
+      <c r="H240" s="364"/>
+      <c r="I240" s="364"/>
+      <c r="J240" s="364"/>
+      <c r="K240" s="362"/>
+      <c r="L240" s="364"/>
+    </row>
+    <row r="241" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B241" s="362"/>
+      <c r="C241" s="363"/>
+      <c r="D241" s="364"/>
+      <c r="E241" s="363"/>
+      <c r="F241" s="364"/>
+      <c r="G241" s="363"/>
+      <c r="H241" s="364"/>
+      <c r="I241" s="364"/>
+      <c r="J241" s="364"/>
+      <c r="K241" s="362"/>
+      <c r="L241" s="364"/>
+    </row>
+    <row r="242" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B242" s="362"/>
+      <c r="C242" s="363"/>
+      <c r="D242" s="364"/>
+      <c r="E242" s="363"/>
+      <c r="F242" s="364"/>
+      <c r="G242" s="363"/>
+      <c r="H242" s="364"/>
+      <c r="I242" s="364"/>
+      <c r="J242" s="364"/>
+      <c r="K242" s="362"/>
+      <c r="L242" s="364"/>
+    </row>
+    <row r="243" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B243" s="362"/>
+      <c r="C243" s="363"/>
+      <c r="D243" s="364"/>
+      <c r="E243" s="363"/>
+      <c r="F243" s="364"/>
+      <c r="G243" s="363"/>
+      <c r="H243" s="364"/>
+      <c r="I243" s="364"/>
+      <c r="J243" s="364"/>
+      <c r="K243" s="362"/>
+      <c r="L243" s="364"/>
+    </row>
+    <row r="244" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B244" s="362"/>
+      <c r="C244" s="363"/>
+      <c r="D244" s="364"/>
+      <c r="E244" s="363"/>
+      <c r="F244" s="364"/>
+      <c r="G244" s="363"/>
+      <c r="H244" s="364"/>
+      <c r="I244" s="364"/>
+      <c r="J244" s="364"/>
+      <c r="K244" s="362"/>
+      <c r="L244" s="364"/>
+    </row>
+    <row r="245" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B245" s="362"/>
+      <c r="C245" s="363"/>
+      <c r="D245" s="364"/>
+      <c r="E245" s="363"/>
+      <c r="F245" s="364"/>
+      <c r="G245" s="363"/>
+      <c r="H245" s="364"/>
+      <c r="I245" s="364"/>
+      <c r="J245" s="364"/>
+      <c r="K245" s="362"/>
+      <c r="L245" s="364"/>
+    </row>
+    <row r="246" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B246" s="362"/>
+      <c r="C246" s="363"/>
+      <c r="D246" s="364"/>
+      <c r="E246" s="363"/>
+      <c r="F246" s="364"/>
+      <c r="G246" s="363"/>
+      <c r="H246" s="364"/>
+      <c r="I246" s="364"/>
+      <c r="J246" s="364"/>
+      <c r="K246" s="362"/>
+      <c r="L246" s="364"/>
+    </row>
+    <row r="247" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B247" s="362"/>
+      <c r="C247" s="363"/>
+      <c r="D247" s="364"/>
+      <c r="E247" s="363"/>
+      <c r="F247" s="364"/>
+      <c r="G247" s="363"/>
+      <c r="H247" s="364"/>
+      <c r="I247" s="364"/>
+      <c r="J247" s="364"/>
+      <c r="K247" s="362"/>
+      <c r="L247" s="364"/>
+    </row>
+    <row r="248" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B248" s="362"/>
+      <c r="C248" s="363"/>
+      <c r="D248" s="364"/>
+      <c r="E248" s="363"/>
+      <c r="F248" s="364"/>
+      <c r="G248" s="363"/>
+      <c r="H248" s="364"/>
+      <c r="I248" s="364"/>
+      <c r="J248" s="364"/>
+      <c r="K248" s="362"/>
+      <c r="L248" s="364"/>
+    </row>
+    <row r="249" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B249" s="362"/>
+      <c r="C249" s="363"/>
+      <c r="D249" s="364"/>
+      <c r="E249" s="363"/>
+      <c r="F249" s="364"/>
+      <c r="G249" s="363"/>
+      <c r="H249" s="364"/>
+      <c r="I249" s="364"/>
+      <c r="J249" s="364"/>
+      <c r="K249" s="362"/>
+      <c r="L249" s="364"/>
+    </row>
+    <row r="250" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B250" s="362"/>
+      <c r="C250" s="363"/>
+      <c r="D250" s="364"/>
+      <c r="E250" s="363"/>
+      <c r="F250" s="364"/>
+      <c r="G250" s="363"/>
+      <c r="H250" s="364"/>
+      <c r="I250" s="364"/>
+      <c r="J250" s="364"/>
+      <c r="K250" s="362"/>
+      <c r="L250" s="364"/>
+    </row>
+    <row r="251" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B251" s="362"/>
+      <c r="C251" s="363"/>
+      <c r="D251" s="364"/>
+      <c r="E251" s="363"/>
+      <c r="F251" s="364"/>
+      <c r="G251" s="363"/>
+      <c r="H251" s="364"/>
+      <c r="I251" s="364"/>
+      <c r="J251" s="364"/>
+      <c r="K251" s="362"/>
+      <c r="L251" s="364"/>
+    </row>
+    <row r="252" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B252" s="362"/>
+      <c r="C252" s="363"/>
+      <c r="D252" s="364"/>
+      <c r="E252" s="363"/>
+      <c r="F252" s="364"/>
+      <c r="G252" s="363"/>
+      <c r="H252" s="364"/>
+      <c r="I252" s="364"/>
+      <c r="J252" s="364"/>
+      <c r="K252" s="362"/>
+      <c r="L252" s="364"/>
+    </row>
+    <row r="253" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B253" s="362"/>
+      <c r="C253" s="363"/>
+      <c r="D253" s="364"/>
+      <c r="E253" s="363"/>
+      <c r="F253" s="364"/>
+      <c r="G253" s="363"/>
+      <c r="H253" s="364"/>
+      <c r="I253" s="364"/>
+      <c r="J253" s="364"/>
+      <c r="K253" s="362"/>
+      <c r="L253" s="364"/>
+    </row>
+    <row r="254" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B254" s="362"/>
+      <c r="C254" s="363"/>
+      <c r="D254" s="364"/>
+      <c r="E254" s="363"/>
+      <c r="F254" s="364"/>
+      <c r="G254" s="363"/>
+      <c r="H254" s="364"/>
+      <c r="I254" s="364"/>
+      <c r="J254" s="364"/>
+      <c r="K254" s="362"/>
+      <c r="L254" s="364"/>
+    </row>
+    <row r="255" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B255" s="362"/>
+      <c r="C255" s="363"/>
+      <c r="D255" s="364"/>
+      <c r="E255" s="363"/>
+      <c r="F255" s="364"/>
+      <c r="G255" s="363"/>
+      <c r="H255" s="364"/>
+      <c r="I255" s="364"/>
+      <c r="J255" s="364"/>
+      <c r="K255" s="362"/>
+      <c r="L255" s="364"/>
+    </row>
+    <row r="256" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B256" s="362"/>
+      <c r="C256" s="363"/>
+      <c r="D256" s="364"/>
+      <c r="E256" s="363"/>
+      <c r="F256" s="364"/>
+      <c r="G256" s="363"/>
+      <c r="H256" s="364"/>
+      <c r="I256" s="364"/>
+      <c r="J256" s="364"/>
+      <c r="K256" s="362"/>
+      <c r="L256" s="364"/>
+    </row>
+    <row r="257" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B257" s="362"/>
+      <c r="C257" s="363"/>
+      <c r="D257" s="364"/>
+      <c r="E257" s="363"/>
+      <c r="F257" s="364"/>
+      <c r="G257" s="363"/>
+      <c r="H257" s="364"/>
+      <c r="I257" s="364"/>
+      <c r="J257" s="364"/>
+      <c r="K257" s="362"/>
+      <c r="L257" s="364"/>
+    </row>
+    <row r="258" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B258" s="362"/>
+      <c r="C258" s="363"/>
+      <c r="D258" s="364"/>
+      <c r="E258" s="363"/>
+      <c r="F258" s="364"/>
+      <c r="G258" s="363"/>
+      <c r="H258" s="364"/>
+      <c r="I258" s="364"/>
+      <c r="J258" s="364"/>
+      <c r="K258" s="362"/>
+      <c r="L258" s="364"/>
+    </row>
+    <row r="259" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B259" s="362"/>
+      <c r="C259" s="363"/>
+      <c r="D259" s="364"/>
+      <c r="E259" s="363"/>
+      <c r="F259" s="364"/>
+      <c r="G259" s="363"/>
+      <c r="H259" s="364"/>
+      <c r="I259" s="364"/>
+      <c r="J259" s="364"/>
+      <c r="K259" s="362"/>
+      <c r="L259" s="364"/>
+    </row>
+    <row r="260" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B260" s="362"/>
+      <c r="C260" s="363"/>
+      <c r="D260" s="364"/>
+      <c r="E260" s="363"/>
+      <c r="F260" s="364"/>
+      <c r="G260" s="363"/>
+      <c r="H260" s="364"/>
+      <c r="I260" s="364"/>
+      <c r="J260" s="364"/>
+      <c r="K260" s="362"/>
+      <c r="L260" s="364"/>
+    </row>
+    <row r="261" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B261" s="362"/>
+      <c r="C261" s="363"/>
+      <c r="D261" s="364"/>
+      <c r="E261" s="363"/>
+      <c r="F261" s="364"/>
+      <c r="G261" s="363"/>
+      <c r="H261" s="364"/>
+      <c r="I261" s="364"/>
+      <c r="J261" s="364"/>
+      <c r="K261" s="362"/>
+      <c r="L261" s="364"/>
+    </row>
+    <row r="262" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B262" s="362"/>
+      <c r="C262" s="363"/>
+      <c r="D262" s="364"/>
+      <c r="E262" s="363"/>
+      <c r="F262" s="364"/>
+      <c r="G262" s="363"/>
+      <c r="H262" s="364"/>
+      <c r="I262" s="364"/>
+      <c r="J262" s="364"/>
+      <c r="K262" s="362"/>
+      <c r="L262" s="364"/>
+    </row>
+    <row r="263" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B263" s="362"/>
+      <c r="C263" s="363"/>
+      <c r="D263" s="364"/>
+      <c r="E263" s="363"/>
+      <c r="F263" s="364"/>
+      <c r="G263" s="363"/>
+      <c r="H263" s="364"/>
+      <c r="I263" s="364"/>
+      <c r="J263" s="364"/>
+      <c r="K263" s="362"/>
+      <c r="L263" s="364"/>
+    </row>
+    <row r="264" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B264" s="362"/>
+      <c r="C264" s="363"/>
+      <c r="D264" s="364"/>
+      <c r="E264" s="363"/>
+      <c r="F264" s="364"/>
+      <c r="G264" s="363"/>
+      <c r="H264" s="364"/>
+      <c r="I264" s="364"/>
+      <c r="J264" s="364"/>
+      <c r="K264" s="362"/>
+      <c r="L264" s="364"/>
+    </row>
+    <row r="265" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B265" s="362"/>
+      <c r="C265" s="363"/>
+      <c r="D265" s="364"/>
+      <c r="E265" s="363"/>
+      <c r="F265" s="364"/>
+      <c r="G265" s="363"/>
+      <c r="H265" s="364"/>
+      <c r="I265" s="364"/>
+      <c r="J265" s="364"/>
+      <c r="K265" s="362"/>
+      <c r="L265" s="364"/>
+    </row>
+    <row r="266" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B266" s="362"/>
+      <c r="C266" s="363"/>
+      <c r="D266" s="364"/>
+      <c r="E266" s="363"/>
+      <c r="F266" s="364"/>
+      <c r="G266" s="363"/>
+      <c r="H266" s="364"/>
+      <c r="I266" s="364"/>
+      <c r="J266" s="364"/>
+      <c r="K266" s="362"/>
+      <c r="L266" s="364"/>
+    </row>
+    <row r="267" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B267" s="362"/>
+      <c r="C267" s="363"/>
+      <c r="D267" s="364"/>
+      <c r="E267" s="363"/>
+      <c r="F267" s="364"/>
+      <c r="G267" s="363"/>
+      <c r="H267" s="364"/>
+      <c r="I267" s="364"/>
+      <c r="J267" s="364"/>
+      <c r="K267" s="362"/>
+      <c r="L267" s="364"/>
+    </row>
+    <row r="268" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B268" s="362"/>
+      <c r="C268" s="363"/>
+      <c r="D268" s="364"/>
+      <c r="E268" s="363"/>
+      <c r="F268" s="364"/>
+      <c r="G268" s="363"/>
+      <c r="H268" s="364"/>
+      <c r="I268" s="364"/>
+      <c r="J268" s="364"/>
+      <c r="K268" s="362"/>
+      <c r="L268" s="364"/>
+    </row>
+    <row r="269" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B269" s="362"/>
+      <c r="C269" s="363"/>
+      <c r="D269" s="364"/>
+      <c r="E269" s="363"/>
+      <c r="F269" s="364"/>
+      <c r="G269" s="363"/>
+      <c r="H269" s="364"/>
+      <c r="I269" s="364"/>
+      <c r="J269" s="364"/>
+      <c r="K269" s="362"/>
+      <c r="L269" s="364"/>
+    </row>
+    <row r="270" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B270" s="362"/>
+      <c r="C270" s="363"/>
+      <c r="D270" s="364"/>
+      <c r="E270" s="363"/>
+      <c r="F270" s="364"/>
+      <c r="G270" s="363"/>
+      <c r="H270" s="364"/>
+      <c r="I270" s="364"/>
+      <c r="J270" s="364"/>
+      <c r="K270" s="362"/>
+      <c r="L270" s="364"/>
+    </row>
+    <row r="271" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B271" s="362"/>
+      <c r="C271" s="363"/>
+      <c r="D271" s="364"/>
+      <c r="E271" s="363"/>
+      <c r="F271" s="364"/>
+      <c r="G271" s="363"/>
+      <c r="H271" s="364"/>
+      <c r="I271" s="364"/>
+      <c r="J271" s="364"/>
+      <c r="K271" s="362"/>
+      <c r="L271" s="364"/>
+    </row>
+    <row r="272" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B272" s="362"/>
+      <c r="C272" s="363"/>
+      <c r="D272" s="364"/>
+      <c r="E272" s="363"/>
+      <c r="F272" s="364"/>
+      <c r="G272" s="363"/>
+      <c r="H272" s="364"/>
+      <c r="I272" s="364"/>
+      <c r="J272" s="364"/>
+      <c r="K272" s="362"/>
+      <c r="L272" s="364"/>
+    </row>
+    <row r="273" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B273" s="362"/>
+      <c r="C273" s="363"/>
+      <c r="D273" s="364"/>
+      <c r="E273" s="363"/>
+      <c r="F273" s="364"/>
+      <c r="G273" s="363"/>
+      <c r="H273" s="364"/>
+      <c r="I273" s="364"/>
+      <c r="J273" s="364"/>
+      <c r="K273" s="362"/>
+      <c r="L273" s="364"/>
+    </row>
+    <row r="274" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B274" s="362"/>
+      <c r="C274" s="363"/>
+      <c r="D274" s="364"/>
+      <c r="E274" s="363"/>
+      <c r="F274" s="364"/>
+      <c r="G274" s="363"/>
+      <c r="H274" s="364"/>
+      <c r="I274" s="364"/>
+      <c r="J274" s="364"/>
+      <c r="K274" s="362"/>
+      <c r="L274" s="364"/>
+    </row>
+    <row r="275" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B275" s="362"/>
+      <c r="C275" s="363"/>
+      <c r="D275" s="364"/>
+      <c r="E275" s="363"/>
+      <c r="F275" s="364"/>
+      <c r="G275" s="363"/>
+      <c r="H275" s="364"/>
+      <c r="I275" s="364"/>
+      <c r="J275" s="364"/>
+      <c r="K275" s="362"/>
+      <c r="L275" s="364"/>
+    </row>
+    <row r="276" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B276" s="362"/>
+      <c r="C276" s="363"/>
+      <c r="D276" s="364"/>
+      <c r="E276" s="363"/>
+      <c r="F276" s="364"/>
+      <c r="G276" s="363"/>
+      <c r="H276" s="364"/>
+      <c r="I276" s="364"/>
+      <c r="J276" s="364"/>
+      <c r="K276" s="362"/>
+      <c r="L276" s="364"/>
+    </row>
+    <row r="277" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B277" s="362"/>
+      <c r="C277" s="363"/>
+      <c r="D277" s="364"/>
+      <c r="E277" s="363"/>
+      <c r="F277" s="364"/>
+      <c r="G277" s="363"/>
+      <c r="H277" s="364"/>
+      <c r="I277" s="364"/>
+      <c r="J277" s="364"/>
+      <c r="K277" s="362"/>
+      <c r="L277" s="364"/>
+    </row>
+    <row r="278" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B278" s="362"/>
+      <c r="C278" s="363"/>
+      <c r="D278" s="364"/>
+      <c r="E278" s="363"/>
+      <c r="F278" s="364"/>
+      <c r="G278" s="363"/>
+      <c r="H278" s="364"/>
+      <c r="I278" s="364"/>
+      <c r="J278" s="364"/>
+      <c r="K278" s="362"/>
+      <c r="L278" s="364"/>
+    </row>
+    <row r="279" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B279" s="362"/>
+      <c r="C279" s="363"/>
+      <c r="D279" s="364"/>
+      <c r="E279" s="363"/>
+      <c r="F279" s="364"/>
+      <c r="G279" s="363"/>
+      <c r="H279" s="364"/>
+      <c r="I279" s="364"/>
+      <c r="J279" s="364"/>
+      <c r="K279" s="362"/>
+      <c r="L279" s="364"/>
+    </row>
+    <row r="280" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B280" s="362"/>
+      <c r="C280" s="363"/>
+      <c r="D280" s="364"/>
+      <c r="E280" s="363"/>
+      <c r="F280" s="364"/>
+      <c r="G280" s="363"/>
+      <c r="H280" s="364"/>
+      <c r="I280" s="364"/>
+      <c r="J280" s="364"/>
+      <c r="K280" s="362"/>
+      <c r="L280" s="364"/>
+    </row>
+    <row r="281" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B281" s="362"/>
+      <c r="C281" s="363"/>
+      <c r="D281" s="364"/>
+      <c r="E281" s="363"/>
+      <c r="F281" s="364"/>
+      <c r="G281" s="363"/>
+      <c r="H281" s="364"/>
+      <c r="I281" s="364"/>
+      <c r="J281" s="364"/>
+      <c r="K281" s="362"/>
+      <c r="L281" s="364"/>
+    </row>
+    <row r="282" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B282" s="362"/>
+      <c r="C282" s="363"/>
+      <c r="D282" s="364"/>
+      <c r="E282" s="363"/>
+      <c r="F282" s="364"/>
+      <c r="G282" s="363"/>
+      <c r="H282" s="364"/>
+      <c r="I282" s="364"/>
+      <c r="J282" s="364"/>
+      <c r="K282" s="362"/>
+      <c r="L282" s="364"/>
+    </row>
+    <row r="283" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B283" s="362"/>
+      <c r="C283" s="363"/>
+      <c r="D283" s="364"/>
+      <c r="E283" s="363"/>
+      <c r="F283" s="364"/>
+      <c r="G283" s="363"/>
+      <c r="H283" s="364"/>
+      <c r="I283" s="364"/>
+      <c r="J283" s="364"/>
+      <c r="K283" s="362"/>
+      <c r="L283" s="364"/>
+    </row>
+    <row r="284" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B284" s="362"/>
+      <c r="C284" s="363"/>
+      <c r="D284" s="364"/>
+      <c r="E284" s="363"/>
+      <c r="F284" s="364"/>
+      <c r="G284" s="363"/>
+      <c r="H284" s="364"/>
+      <c r="I284" s="364"/>
+      <c r="J284" s="364"/>
+      <c r="K284" s="362"/>
+      <c r="L284" s="364"/>
+    </row>
+    <row r="285" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B285" s="362"/>
+      <c r="C285" s="363"/>
+      <c r="D285" s="364"/>
+      <c r="E285" s="363"/>
+      <c r="F285" s="364"/>
+      <c r="G285" s="363"/>
+      <c r="H285" s="364"/>
+      <c r="I285" s="364"/>
+      <c r="J285" s="364"/>
+      <c r="K285" s="362"/>
+      <c r="L285" s="364"/>
+    </row>
+    <row r="286" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B286" s="362"/>
+      <c r="C286" s="363"/>
+      <c r="D286" s="364"/>
+      <c r="E286" s="363"/>
+      <c r="F286" s="364"/>
+      <c r="G286" s="363"/>
+      <c r="H286" s="364"/>
+      <c r="I286" s="364"/>
+      <c r="J286" s="364"/>
+      <c r="K286" s="362"/>
+      <c r="L286" s="364"/>
+    </row>
+    <row r="287" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B287" s="362"/>
+      <c r="C287" s="363"/>
+      <c r="D287" s="364"/>
+      <c r="E287" s="363"/>
+      <c r="F287" s="364"/>
+      <c r="G287" s="363"/>
+      <c r="H287" s="364"/>
+      <c r="I287" s="364"/>
+      <c r="J287" s="364"/>
+      <c r="K287" s="362"/>
+      <c r="L287" s="364"/>
+    </row>
+    <row r="288" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B288" s="362"/>
+      <c r="C288" s="363"/>
+      <c r="D288" s="364"/>
+      <c r="E288" s="363"/>
+      <c r="F288" s="364"/>
+      <c r="G288" s="363"/>
+      <c r="H288" s="364"/>
+      <c r="I288" s="364"/>
+      <c r="J288" s="364"/>
+      <c r="K288" s="362"/>
+      <c r="L288" s="364"/>
+    </row>
+    <row r="289" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B289" s="362"/>
+      <c r="C289" s="363"/>
+      <c r="D289" s="364"/>
+      <c r="E289" s="363"/>
+      <c r="F289" s="364"/>
+      <c r="G289" s="363"/>
+      <c r="H289" s="364"/>
+      <c r="I289" s="364"/>
+      <c r="J289" s="364"/>
+      <c r="K289" s="362"/>
+      <c r="L289" s="364"/>
+    </row>
+    <row r="290" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B290" s="362"/>
+      <c r="C290" s="363"/>
+      <c r="D290" s="364"/>
+      <c r="E290" s="363"/>
+      <c r="F290" s="364"/>
+      <c r="G290" s="363"/>
+      <c r="H290" s="364"/>
+      <c r="I290" s="364"/>
+      <c r="J290" s="364"/>
+      <c r="K290" s="362"/>
+      <c r="L290" s="364"/>
+    </row>
+    <row r="291" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B291" s="362"/>
+      <c r="C291" s="363"/>
+      <c r="D291" s="364"/>
+      <c r="E291" s="363"/>
+      <c r="F291" s="364"/>
+      <c r="G291" s="363"/>
+      <c r="H291" s="364"/>
+      <c r="I291" s="364"/>
+      <c r="J291" s="364"/>
+      <c r="K291" s="362"/>
+      <c r="L291" s="364"/>
+    </row>
+    <row r="292" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B292" s="362"/>
+      <c r="C292" s="363"/>
+      <c r="D292" s="364"/>
+      <c r="E292" s="363"/>
+      <c r="F292" s="364"/>
+      <c r="G292" s="363"/>
+      <c r="H292" s="364"/>
+      <c r="I292" s="364"/>
+      <c r="J292" s="364"/>
+      <c r="K292" s="362"/>
+      <c r="L292" s="364"/>
+    </row>
+    <row r="293" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B293" s="362"/>
+      <c r="C293" s="363"/>
+      <c r="D293" s="364"/>
+      <c r="E293" s="363"/>
+      <c r="F293" s="364"/>
+      <c r="G293" s="363"/>
+      <c r="H293" s="364"/>
+      <c r="I293" s="364"/>
+      <c r="J293" s="364"/>
+      <c r="K293" s="362"/>
+      <c r="L293" s="364"/>
+    </row>
+    <row r="294" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B294" s="362"/>
+      <c r="C294" s="363"/>
+      <c r="D294" s="364"/>
+      <c r="E294" s="363"/>
+      <c r="F294" s="364"/>
+      <c r="G294" s="363"/>
+      <c r="H294" s="364"/>
+      <c r="I294" s="364"/>
+      <c r="J294" s="364"/>
+      <c r="K294" s="362"/>
+      <c r="L294" s="364"/>
+    </row>
+    <row r="295" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B295" s="362"/>
+      <c r="C295" s="363"/>
+      <c r="D295" s="364"/>
+      <c r="E295" s="363"/>
+      <c r="F295" s="364"/>
+      <c r="G295" s="363"/>
+      <c r="H295" s="364"/>
+      <c r="I295" s="364"/>
+      <c r="J295" s="364"/>
+      <c r="K295" s="362"/>
+      <c r="L295" s="364"/>
+    </row>
+    <row r="296" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B296" s="362"/>
+      <c r="C296" s="363"/>
+      <c r="D296" s="364"/>
+      <c r="E296" s="363"/>
+      <c r="F296" s="364"/>
+      <c r="G296" s="363"/>
+      <c r="H296" s="364"/>
+      <c r="I296" s="364"/>
+      <c r="J296" s="364"/>
+      <c r="K296" s="362"/>
+      <c r="L296" s="364"/>
+    </row>
+    <row r="297" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B297" s="362"/>
+      <c r="C297" s="363"/>
+      <c r="D297" s="364"/>
+      <c r="E297" s="363"/>
+      <c r="F297" s="364"/>
+      <c r="G297" s="363"/>
+      <c r="H297" s="364"/>
+      <c r="I297" s="364"/>
+      <c r="J297" s="364"/>
+      <c r="K297" s="362"/>
+      <c r="L297" s="364"/>
+    </row>
+    <row r="298" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B298" s="362"/>
+      <c r="C298" s="363"/>
+      <c r="D298" s="364"/>
+      <c r="E298" s="363"/>
+      <c r="F298" s="364"/>
+      <c r="G298" s="363"/>
+      <c r="H298" s="364"/>
+      <c r="I298" s="364"/>
+      <c r="J298" s="364"/>
+      <c r="K298" s="362"/>
+      <c r="L298" s="364"/>
+    </row>
+    <row r="299" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B299" s="362"/>
+      <c r="C299" s="363"/>
+      <c r="D299" s="364"/>
+      <c r="E299" s="363"/>
+      <c r="F299" s="364"/>
+      <c r="G299" s="363"/>
+      <c r="H299" s="364"/>
+      <c r="I299" s="364"/>
+      <c r="J299" s="364"/>
+      <c r="K299" s="362"/>
+      <c r="L299" s="364"/>
+    </row>
+    <row r="300" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B300" s="362"/>
+      <c r="C300" s="363"/>
+      <c r="D300" s="364"/>
+      <c r="E300" s="363"/>
+      <c r="F300" s="364"/>
+      <c r="G300" s="363"/>
+      <c r="H300" s="364"/>
+      <c r="I300" s="364"/>
+      <c r="J300" s="364"/>
+      <c r="K300" s="362"/>
+      <c r="L300" s="364"/>
+    </row>
+    <row r="301" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B301" s="362"/>
+      <c r="C301" s="363"/>
+      <c r="D301" s="364"/>
+      <c r="E301" s="363"/>
+      <c r="F301" s="364"/>
+      <c r="G301" s="363"/>
+      <c r="H301" s="364"/>
+      <c r="I301" s="364"/>
+      <c r="J301" s="364"/>
+      <c r="K301" s="362"/>
+      <c r="L301" s="364"/>
+    </row>
+    <row r="302" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B302" s="362"/>
+      <c r="C302" s="363"/>
+      <c r="D302" s="364"/>
+      <c r="E302" s="363"/>
+      <c r="F302" s="364"/>
+      <c r="G302" s="363"/>
+      <c r="H302" s="364"/>
+      <c r="I302" s="364"/>
+      <c r="J302" s="364"/>
+      <c r="K302" s="362"/>
+      <c r="L302" s="364"/>
+    </row>
+    <row r="303" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B303" s="362"/>
+      <c r="C303" s="363"/>
+      <c r="D303" s="364"/>
+      <c r="E303" s="363"/>
+      <c r="F303" s="364"/>
+      <c r="G303" s="363"/>
+      <c r="H303" s="364"/>
+      <c r="I303" s="364"/>
+      <c r="J303" s="364"/>
+      <c r="K303" s="362"/>
+      <c r="L303" s="364"/>
+    </row>
+    <row r="304" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B304" s="362"/>
+      <c r="C304" s="363"/>
+      <c r="D304" s="364"/>
+      <c r="E304" s="363"/>
+      <c r="F304" s="364"/>
+      <c r="G304" s="363"/>
+      <c r="H304" s="364"/>
+      <c r="I304" s="364"/>
+      <c r="J304" s="364"/>
+      <c r="K304" s="362"/>
+      <c r="L304" s="364"/>
+    </row>
+    <row r="305" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B305" s="362"/>
+      <c r="C305" s="363"/>
+      <c r="D305" s="364"/>
+      <c r="E305" s="363"/>
+      <c r="F305" s="364"/>
+      <c r="G305" s="363"/>
+      <c r="H305" s="364"/>
+      <c r="I305" s="364"/>
+      <c r="J305" s="364"/>
+      <c r="K305" s="362"/>
+      <c r="L305" s="364"/>
+    </row>
+    <row r="306" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B306" s="362"/>
+      <c r="C306" s="363"/>
+      <c r="D306" s="364"/>
+      <c r="E306" s="363"/>
+      <c r="F306" s="364"/>
+      <c r="G306" s="363"/>
+      <c r="H306" s="364"/>
+      <c r="I306" s="364"/>
+      <c r="J306" s="364"/>
+      <c r="K306" s="362"/>
+      <c r="L306" s="364"/>
+    </row>
+    <row r="307" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B307" s="362"/>
+      <c r="C307" s="363"/>
+      <c r="D307" s="364"/>
+      <c r="E307" s="363"/>
+      <c r="F307" s="364"/>
+      <c r="G307" s="363"/>
+      <c r="H307" s="364"/>
+      <c r="I307" s="364"/>
+      <c r="J307" s="364"/>
+      <c r="K307" s="362"/>
+      <c r="L307" s="364"/>
+    </row>
+    <row r="308" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B308" s="362"/>
+      <c r="C308" s="363"/>
+      <c r="D308" s="364"/>
+      <c r="E308" s="363"/>
+      <c r="F308" s="364"/>
+      <c r="G308" s="363"/>
+      <c r="H308" s="364"/>
+      <c r="I308" s="364"/>
+      <c r="J308" s="364"/>
+      <c r="K308" s="362"/>
+      <c r="L308" s="364"/>
+    </row>
+    <row r="309" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B309" s="362"/>
+      <c r="C309" s="363"/>
+      <c r="D309" s="364"/>
+      <c r="E309" s="363"/>
+      <c r="F309" s="364"/>
+      <c r="G309" s="363"/>
+      <c r="H309" s="364"/>
+      <c r="I309" s="364"/>
+      <c r="J309" s="364"/>
+      <c r="K309" s="362"/>
+      <c r="L309" s="364"/>
+    </row>
+    <row r="310" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B310" s="362"/>
+      <c r="C310" s="363"/>
+      <c r="D310" s="364"/>
+      <c r="E310" s="363"/>
+      <c r="F310" s="364"/>
+      <c r="G310" s="363"/>
+      <c r="H310" s="364"/>
+      <c r="I310" s="364"/>
+      <c r="J310" s="364"/>
+      <c r="K310" s="362"/>
+      <c r="L310" s="364"/>
+    </row>
+    <row r="311" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B311" s="362"/>
+      <c r="C311" s="363"/>
+      <c r="D311" s="364"/>
+      <c r="E311" s="363"/>
+      <c r="F311" s="364"/>
+      <c r="G311" s="363"/>
+      <c r="H311" s="364"/>
+      <c r="I311" s="364"/>
+      <c r="J311" s="364"/>
+      <c r="K311" s="362"/>
+      <c r="L311" s="364"/>
+    </row>
+    <row r="312" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B312" s="362"/>
+      <c r="C312" s="363"/>
+      <c r="D312" s="364"/>
+      <c r="E312" s="363"/>
+      <c r="F312" s="364"/>
+      <c r="G312" s="363"/>
+      <c r="H312" s="364"/>
+      <c r="I312" s="364"/>
+      <c r="J312" s="364"/>
+      <c r="K312" s="362"/>
+      <c r="L312" s="364"/>
+    </row>
+    <row r="313" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B313" s="362"/>
+      <c r="C313" s="363"/>
+      <c r="D313" s="364"/>
+      <c r="E313" s="363"/>
+      <c r="F313" s="364"/>
+      <c r="G313" s="363"/>
+      <c r="H313" s="364"/>
+      <c r="I313" s="364"/>
+      <c r="J313" s="364"/>
+      <c r="K313" s="362"/>
+      <c r="L313" s="364"/>
+    </row>
+    <row r="314" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B314" s="362"/>
+      <c r="C314" s="363"/>
+      <c r="D314" s="364"/>
+      <c r="E314" s="363"/>
+      <c r="F314" s="364"/>
+      <c r="G314" s="363"/>
+      <c r="H314" s="364"/>
+      <c r="I314" s="364"/>
+      <c r="J314" s="364"/>
+      <c r="K314" s="362"/>
+      <c r="L314" s="364"/>
+    </row>
+    <row r="315" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B315" s="362"/>
+      <c r="C315" s="363"/>
+      <c r="D315" s="364"/>
+      <c r="E315" s="363"/>
+      <c r="F315" s="364"/>
+      <c r="G315" s="363"/>
+      <c r="H315" s="364"/>
+      <c r="I315" s="364"/>
+      <c r="J315" s="364"/>
+      <c r="K315" s="362"/>
+      <c r="L315" s="364"/>
+    </row>
+    <row r="316" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B316" s="362"/>
+      <c r="C316" s="363"/>
+      <c r="D316" s="364"/>
+      <c r="E316" s="363"/>
+      <c r="F316" s="364"/>
+      <c r="G316" s="363"/>
+      <c r="H316" s="364"/>
+      <c r="I316" s="364"/>
+      <c r="J316" s="364"/>
+      <c r="K316" s="362"/>
+      <c r="L316" s="364"/>
+    </row>
+    <row r="317" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B317" s="362"/>
+      <c r="C317" s="363"/>
+      <c r="D317" s="364"/>
+      <c r="E317" s="363"/>
+      <c r="F317" s="364"/>
+      <c r="G317" s="363"/>
+      <c r="H317" s="364"/>
+      <c r="I317" s="364"/>
+      <c r="J317" s="364"/>
+      <c r="K317" s="362"/>
+      <c r="L317" s="364"/>
+    </row>
+    <row r="318" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B318" s="362"/>
+      <c r="C318" s="363"/>
+      <c r="D318" s="364"/>
+      <c r="E318" s="363"/>
+      <c r="F318" s="364"/>
+      <c r="G318" s="363"/>
+      <c r="H318" s="364"/>
+      <c r="I318" s="364"/>
+      <c r="J318" s="364"/>
+      <c r="K318" s="362"/>
+      <c r="L318" s="364"/>
+    </row>
+    <row r="319" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B319" s="362"/>
+      <c r="C319" s="363"/>
+      <c r="D319" s="364"/>
+      <c r="E319" s="363"/>
+      <c r="F319" s="364"/>
+      <c r="G319" s="363"/>
+      <c r="H319" s="364"/>
+      <c r="I319" s="364"/>
+      <c r="J319" s="364"/>
+      <c r="K319" s="362"/>
+      <c r="L319" s="364"/>
+    </row>
+    <row r="320" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B320" s="362"/>
+      <c r="C320" s="363"/>
+      <c r="D320" s="364"/>
+      <c r="E320" s="363"/>
+      <c r="F320" s="364"/>
+      <c r="G320" s="363"/>
+      <c r="H320" s="364"/>
+      <c r="I320" s="364"/>
+      <c r="J320" s="364"/>
+      <c r="K320" s="362"/>
+      <c r="L320" s="364"/>
+    </row>
+    <row r="321" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B321" s="362"/>
+      <c r="C321" s="363"/>
+      <c r="D321" s="364"/>
+      <c r="E321" s="363"/>
+      <c r="F321" s="364"/>
+      <c r="G321" s="363"/>
+      <c r="H321" s="364"/>
+      <c r="I321" s="364"/>
+      <c r="J321" s="364"/>
+      <c r="K321" s="362"/>
+      <c r="L321" s="364"/>
+    </row>
+    <row r="322" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B322" s="362"/>
+      <c r="C322" s="363"/>
+      <c r="D322" s="364"/>
+      <c r="E322" s="363"/>
+      <c r="F322" s="364"/>
+      <c r="G322" s="363"/>
+      <c r="H322" s="364"/>
+      <c r="I322" s="364"/>
+      <c r="J322" s="364"/>
+      <c r="K322" s="362"/>
+      <c r="L322" s="364"/>
+    </row>
+    <row r="323" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B323" s="362"/>
+      <c r="C323" s="363"/>
+      <c r="D323" s="364"/>
+      <c r="E323" s="363"/>
+      <c r="F323" s="364"/>
+      <c r="G323" s="363"/>
+      <c r="H323" s="364"/>
+      <c r="I323" s="364"/>
+      <c r="J323" s="364"/>
+      <c r="K323" s="362"/>
+      <c r="L323" s="364"/>
+    </row>
+    <row r="324" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B324" s="362"/>
+      <c r="C324" s="363"/>
+      <c r="D324" s="364"/>
+      <c r="E324" s="363"/>
+      <c r="F324" s="364"/>
+      <c r="G324" s="363"/>
+      <c r="H324" s="364"/>
+      <c r="I324" s="364"/>
+      <c r="J324" s="364"/>
+      <c r="K324" s="362"/>
+      <c r="L324" s="364"/>
+    </row>
+    <row r="325" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B325" s="362"/>
+      <c r="C325" s="363"/>
+      <c r="D325" s="364"/>
+      <c r="E325" s="363"/>
+      <c r="F325" s="364"/>
+      <c r="G325" s="363"/>
+      <c r="H325" s="364"/>
+      <c r="I325" s="364"/>
+      <c r="J325" s="364"/>
+      <c r="K325" s="362"/>
+      <c r="L325" s="364"/>
+    </row>
+    <row r="326" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B326" s="362"/>
+      <c r="C326" s="363"/>
+      <c r="D326" s="364"/>
+      <c r="E326" s="363"/>
+      <c r="F326" s="364"/>
+      <c r="G326" s="363"/>
+      <c r="H326" s="364"/>
+      <c r="I326" s="364"/>
+      <c r="J326" s="364"/>
+      <c r="K326" s="362"/>
+      <c r="L326" s="364"/>
+    </row>
+    <row r="327" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B327" s="362"/>
+      <c r="C327" s="363"/>
+      <c r="D327" s="364"/>
+      <c r="E327" s="363"/>
+      <c r="F327" s="364"/>
+      <c r="G327" s="363"/>
+      <c r="H327" s="364"/>
+      <c r="I327" s="364"/>
+      <c r="J327" s="364"/>
+      <c r="K327" s="362"/>
+      <c r="L327" s="364"/>
+    </row>
+    <row r="328" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B328" s="362"/>
+      <c r="C328" s="363"/>
+      <c r="D328" s="364"/>
+      <c r="E328" s="363"/>
+      <c r="F328" s="364"/>
+      <c r="G328" s="363"/>
+      <c r="H328" s="364"/>
+      <c r="I328" s="364"/>
+      <c r="J328" s="364"/>
+      <c r="K328" s="362"/>
+      <c r="L328" s="364"/>
+    </row>
+    <row r="329" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B329" s="362"/>
+      <c r="C329" s="363"/>
+      <c r="D329" s="364"/>
+      <c r="E329" s="363"/>
+      <c r="F329" s="364"/>
+      <c r="G329" s="363"/>
+      <c r="H329" s="364"/>
+      <c r="I329" s="364"/>
+      <c r="J329" s="364"/>
+      <c r="K329" s="362"/>
+      <c r="L329" s="364"/>
+    </row>
+    <row r="330" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B330" s="362"/>
+      <c r="C330" s="363"/>
+      <c r="D330" s="364"/>
+      <c r="E330" s="363"/>
+      <c r="F330" s="364"/>
+      <c r="G330" s="363"/>
+      <c r="H330" s="364"/>
+      <c r="I330" s="364"/>
+      <c r="J330" s="364"/>
+      <c r="K330" s="362"/>
+      <c r="L330" s="364"/>
+    </row>
+    <row r="331" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B331" s="362"/>
+      <c r="C331" s="363"/>
+      <c r="D331" s="364"/>
+      <c r="E331" s="363"/>
+      <c r="F331" s="364"/>
+      <c r="G331" s="363"/>
+      <c r="H331" s="364"/>
+      <c r="I331" s="364"/>
+      <c r="J331" s="364"/>
+      <c r="K331" s="362"/>
+      <c r="L331" s="364"/>
+    </row>
+    <row r="332" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B332" s="362"/>
+      <c r="C332" s="363"/>
+      <c r="D332" s="364"/>
+      <c r="E332" s="363"/>
+      <c r="F332" s="364"/>
+      <c r="G332" s="363"/>
+      <c r="H332" s="364"/>
+      <c r="I332" s="364"/>
+      <c r="J332" s="364"/>
+      <c r="K332" s="362"/>
+      <c r="L332" s="364"/>
+    </row>
+    <row r="333" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B333" s="362"/>
+      <c r="C333" s="363"/>
+      <c r="D333" s="364"/>
+      <c r="E333" s="363"/>
+      <c r="F333" s="364"/>
+      <c r="G333" s="363"/>
+      <c r="H333" s="364"/>
+      <c r="I333" s="364"/>
+      <c r="J333" s="364"/>
+      <c r="K333" s="362"/>
+      <c r="L333" s="364"/>
+    </row>
+    <row r="334" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B334" s="362"/>
+      <c r="C334" s="363"/>
+      <c r="D334" s="364"/>
+      <c r="E334" s="363"/>
+      <c r="F334" s="364"/>
+      <c r="G334" s="363"/>
+      <c r="H334" s="364"/>
+      <c r="I334" s="364"/>
+      <c r="J334" s="364"/>
+      <c r="K334" s="362"/>
+      <c r="L334" s="364"/>
+    </row>
+    <row r="335" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B335" s="362"/>
+      <c r="C335" s="363"/>
+      <c r="D335" s="364"/>
+      <c r="E335" s="363"/>
+      <c r="F335" s="364"/>
+      <c r="G335" s="363"/>
+      <c r="H335" s="364"/>
+      <c r="I335" s="364"/>
+      <c r="J335" s="364"/>
+      <c r="K335" s="362"/>
+      <c r="L335" s="364"/>
+    </row>
+    <row r="336" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B336" s="362"/>
+      <c r="C336" s="363"/>
+      <c r="D336" s="364"/>
+      <c r="E336" s="363"/>
+      <c r="F336" s="364"/>
+      <c r="G336" s="363"/>
+      <c r="H336" s="364"/>
+      <c r="I336" s="364"/>
+      <c r="J336" s="364"/>
+      <c r="K336" s="362"/>
+      <c r="L336" s="364"/>
+    </row>
+    <row r="337" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B337" s="362"/>
+      <c r="C337" s="363"/>
+      <c r="D337" s="364"/>
+      <c r="E337" s="363"/>
+      <c r="F337" s="364"/>
+      <c r="G337" s="363"/>
+      <c r="H337" s="364"/>
+      <c r="I337" s="364"/>
+      <c r="J337" s="364"/>
+      <c r="K337" s="362"/>
+      <c r="L337" s="364"/>
+    </row>
+    <row r="338" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B338" s="362"/>
+      <c r="C338" s="363"/>
+      <c r="D338" s="364"/>
+      <c r="E338" s="363"/>
+      <c r="F338" s="364"/>
+      <c r="G338" s="363"/>
+      <c r="H338" s="364"/>
+      <c r="I338" s="364"/>
+      <c r="J338" s="364"/>
+      <c r="K338" s="362"/>
+      <c r="L338" s="364"/>
+    </row>
+    <row r="339" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B339" s="362"/>
+      <c r="C339" s="363"/>
+      <c r="D339" s="364"/>
+      <c r="E339" s="363"/>
+      <c r="F339" s="364"/>
+      <c r="G339" s="363"/>
+      <c r="H339" s="364"/>
+      <c r="I339" s="364"/>
+      <c r="J339" s="364"/>
+      <c r="K339" s="362"/>
+      <c r="L339" s="364"/>
+    </row>
+    <row r="340" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B340" s="362"/>
+      <c r="C340" s="363"/>
+      <c r="D340" s="364"/>
+      <c r="E340" s="363"/>
+      <c r="F340" s="364"/>
+      <c r="G340" s="363"/>
+      <c r="H340" s="364"/>
+      <c r="I340" s="364"/>
+      <c r="J340" s="364"/>
+      <c r="K340" s="362"/>
+      <c r="L340" s="364"/>
+    </row>
+    <row r="341" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B341" s="362"/>
+      <c r="C341" s="363"/>
+      <c r="D341" s="364"/>
+      <c r="E341" s="363"/>
+      <c r="F341" s="364"/>
+      <c r="G341" s="363"/>
+      <c r="H341" s="364"/>
+      <c r="I341" s="364"/>
+      <c r="J341" s="364"/>
+      <c r="K341" s="362"/>
+      <c r="L341" s="364"/>
+    </row>
+    <row r="342" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B342" s="362"/>
+      <c r="C342" s="363"/>
+      <c r="D342" s="364"/>
+      <c r="E342" s="363"/>
+      <c r="F342" s="364"/>
+      <c r="G342" s="363"/>
+      <c r="H342" s="364"/>
+      <c r="I342" s="364"/>
+      <c r="J342" s="364"/>
+      <c r="K342" s="362"/>
+      <c r="L342" s="364"/>
+    </row>
+    <row r="343" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B343" s="362"/>
+      <c r="C343" s="363"/>
+      <c r="D343" s="364"/>
+      <c r="E343" s="363"/>
+      <c r="F343" s="364"/>
+      <c r="G343" s="363"/>
+      <c r="H343" s="364"/>
+      <c r="I343" s="364"/>
+      <c r="J343" s="364"/>
+      <c r="K343" s="362"/>
+      <c r="L343" s="364"/>
+    </row>
+    <row r="344" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B344" s="362"/>
+      <c r="C344" s="363"/>
+      <c r="D344" s="364"/>
+      <c r="E344" s="363"/>
+      <c r="F344" s="364"/>
+      <c r="G344" s="363"/>
+      <c r="H344" s="364"/>
+      <c r="I344" s="364"/>
+      <c r="J344" s="364"/>
+      <c r="K344" s="362"/>
+      <c r="L344" s="364"/>
+    </row>
+    <row r="345" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B345" s="362"/>
+      <c r="C345" s="363"/>
+      <c r="D345" s="364"/>
+      <c r="E345" s="363"/>
+      <c r="F345" s="364"/>
+      <c r="G345" s="363"/>
+      <c r="H345" s="364"/>
+      <c r="I345" s="364"/>
+      <c r="J345" s="364"/>
+      <c r="K345" s="362"/>
+      <c r="L345" s="364"/>
+    </row>
+    <row r="346" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B346" s="362"/>
+      <c r="C346" s="363"/>
+      <c r="D346" s="364"/>
+      <c r="E346" s="363"/>
+      <c r="F346" s="364"/>
+      <c r="G346" s="363"/>
+      <c r="H346" s="364"/>
+      <c r="I346" s="364"/>
+      <c r="J346" s="364"/>
+      <c r="K346" s="362"/>
+      <c r="L346" s="364"/>
+    </row>
+    <row r="347" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B347" s="362"/>
+      <c r="C347" s="363"/>
+      <c r="D347" s="364"/>
+      <c r="E347" s="363"/>
+      <c r="F347" s="364"/>
+      <c r="G347" s="363"/>
+      <c r="H347" s="364"/>
+      <c r="I347" s="364"/>
+      <c r="J347" s="364"/>
+      <c r="K347" s="362"/>
+      <c r="L347" s="364"/>
+    </row>
+    <row r="348" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B348" s="362"/>
+      <c r="C348" s="363"/>
+      <c r="D348" s="364"/>
+      <c r="E348" s="363"/>
+      <c r="F348" s="364"/>
+      <c r="G348" s="363"/>
+      <c r="H348" s="364"/>
+      <c r="I348" s="364"/>
+      <c r="J348" s="364"/>
+      <c r="K348" s="362"/>
+      <c r="L348" s="364"/>
+    </row>
+    <row r="349" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B349" s="362"/>
+      <c r="C349" s="363"/>
+      <c r="D349" s="364"/>
+      <c r="E349" s="363"/>
+      <c r="F349" s="364"/>
+      <c r="G349" s="363"/>
+      <c r="H349" s="364"/>
+      <c r="I349" s="364"/>
+      <c r="J349" s="364"/>
+      <c r="K349" s="362"/>
+      <c r="L349" s="364"/>
+    </row>
+    <row r="350" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B350" s="362"/>
+      <c r="C350" s="363"/>
+      <c r="D350" s="364"/>
+      <c r="E350" s="363"/>
+      <c r="F350" s="364"/>
+      <c r="G350" s="363"/>
+      <c r="H350" s="364"/>
+      <c r="I350" s="364"/>
+      <c r="J350" s="364"/>
+      <c r="K350" s="362"/>
+      <c r="L350" s="364"/>
+    </row>
+    <row r="351" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B351" s="362"/>
+      <c r="C351" s="363"/>
+      <c r="D351" s="364"/>
+      <c r="E351" s="363"/>
+      <c r="F351" s="364"/>
+      <c r="G351" s="363"/>
+      <c r="H351" s="364"/>
+      <c r="I351" s="364"/>
+      <c r="J351" s="364"/>
+      <c r="K351" s="362"/>
+      <c r="L351" s="364"/>
+    </row>
+    <row r="352" spans="2:12" ht="27.75" customHeight="1">
+      <c r="B352" s="362"/>
+      <c r="C352" s="363"/>
+      <c r="D352" s="364"/>
+      <c r="E352" s="363"/>
+      <c r="F352" s="364"/>
+      <c r="G352" s="363"/>
+      <c r="H352" s="364"/>
+      <c r="I352" s="364"/>
+      <c r="J352" s="364"/>
+      <c r="K352" s="362"/>
+      <c r="L352" s="364"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="L11:P11"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="K43:P43"/>
+    <mergeCell ref="K44:P44"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="L21:N22"/>
+    <mergeCell ref="L17:P17"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="K46:P46"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="K45:P45"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="K48:P48"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N6:P7"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:P5"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="L8:P8"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="L31:P31"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C30:F31"/>
     <mergeCell ref="L9:O10"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="C29:G29"/>
@@ -25518,59 +29578,6 @@
     <mergeCell ref="L23:N24"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="L12:P12"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="L18:P18"/>
-    <mergeCell ref="L31:P31"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N6:P7"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:P5"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="L8:P8"/>
-    <mergeCell ref="C30:F31"/>
-    <mergeCell ref="L21:N22"/>
-    <mergeCell ref="L17:P17"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="K46:P46"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="K45:P45"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="K48:P48"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L11:P11"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="K43:P43"/>
-    <mergeCell ref="K44:P44"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.47244094488188981" right="0.23622047244094491" top="0.70866141732283472" bottom="0.70866141732283472" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -25585,91 +29592,91 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F6ADA4-B2CF-4C37-B21D-101B85CBFE52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AL59"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="10.8"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="12.796875" style="164" customWidth="1"/>
-    <col min="2" max="2" width="5.296875" style="164" customWidth="1"/>
-    <col min="3" max="20" width="2.8984375" style="164" customWidth="1"/>
-    <col min="21" max="21" width="1.09765625" style="164" customWidth="1"/>
-    <col min="22" max="22" width="2.8984375" style="164" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="164" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="164" customWidth="1"/>
+    <col min="3" max="20" width="2.88671875" style="164" customWidth="1"/>
+    <col min="21" max="21" width="1.109375" style="164" customWidth="1"/>
+    <col min="22" max="22" width="2.88671875" style="164" customWidth="1"/>
     <col min="23" max="23" width="1" style="164" customWidth="1"/>
-    <col min="24" max="24" width="7.3984375" style="164" customWidth="1"/>
-    <col min="25" max="16384" width="8.8984375" style="164"/>
+    <col min="24" max="24" width="7.44140625" style="164" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="164"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="39" customHeight="1">
-      <c r="A1" s="334" t="s">
+      <c r="A1" s="340" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="334"/>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="334"/>
-      <c r="L1" s="334"/>
-      <c r="M1" s="334"/>
-      <c r="N1" s="334"/>
-      <c r="O1" s="334"/>
-      <c r="P1" s="334"/>
-      <c r="Q1" s="334"/>
-      <c r="R1" s="334"/>
-      <c r="S1" s="334"/>
-      <c r="T1" s="334"/>
-      <c r="U1" s="334"/>
-      <c r="V1" s="334"/>
-      <c r="W1" s="334"/>
-      <c r="X1" s="334"/>
+      <c r="B1" s="340"/>
+      <c r="C1" s="340"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
+      <c r="G1" s="340"/>
+      <c r="H1" s="340"/>
+      <c r="I1" s="340"/>
+      <c r="J1" s="340"/>
+      <c r="K1" s="340"/>
+      <c r="L1" s="340"/>
+      <c r="M1" s="340"/>
+      <c r="N1" s="340"/>
+      <c r="O1" s="340"/>
+      <c r="P1" s="340"/>
+      <c r="Q1" s="340"/>
+      <c r="R1" s="340"/>
+      <c r="S1" s="340"/>
+      <c r="T1" s="340"/>
+      <c r="U1" s="340"/>
+      <c r="V1" s="340"/>
+      <c r="W1" s="340"/>
+      <c r="X1" s="340"/>
     </row>
     <row r="2" spans="1:38" ht="14.25" customHeight="1">
-      <c r="S2" s="355" t="s">
+      <c r="S2" s="358" t="s">
         <v>235</v>
       </c>
-      <c r="T2" s="355"/>
-      <c r="U2" s="355"/>
-      <c r="V2" s="355"/>
-      <c r="W2" s="355"/>
-      <c r="X2" s="355"/>
+      <c r="T2" s="358"/>
+      <c r="U2" s="358"/>
+      <c r="V2" s="358"/>
+      <c r="W2" s="358"/>
+      <c r="X2" s="358"/>
     </row>
     <row r="3" spans="1:38" ht="18" customHeight="1">
       <c r="A3" s="165"/>
-      <c r="B3" s="356" t="s">
+      <c r="B3" s="359" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="356"/>
-      <c r="D3" s="356"/>
-      <c r="E3" s="356"/>
-      <c r="F3" s="356"/>
-      <c r="G3" s="356"/>
-      <c r="H3" s="356"/>
-      <c r="I3" s="356"/>
-      <c r="J3" s="356"/>
-      <c r="K3" s="356"/>
-      <c r="L3" s="356"/>
-      <c r="M3" s="356"/>
-      <c r="N3" s="357"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="359"/>
+      <c r="N3" s="360"/>
       <c r="O3" s="166" t="s">
         <v>2</v>
       </c>
       <c r="P3" s="166"/>
       <c r="Q3" s="167"/>
-      <c r="R3" s="335" t="str">
+      <c r="R3" s="341" t="str">
         <f>갑100A!N4</f>
         <v>서울에너지공사</v>
       </c>
-      <c r="S3" s="336"/>
-      <c r="T3" s="336"/>
-      <c r="U3" s="336"/>
-      <c r="V3" s="336"/>
-      <c r="W3" s="336"/>
-      <c r="X3" s="337"/>
+      <c r="S3" s="342"/>
+      <c r="T3" s="342"/>
+      <c r="U3" s="342"/>
+      <c r="V3" s="342"/>
+      <c r="W3" s="342"/>
+      <c r="X3" s="343"/>
     </row>
     <row r="4" spans="1:38" ht="12.75" customHeight="1">
       <c r="A4" s="168"/>
@@ -25682,46 +29689,46 @@
       </c>
       <c r="P4" s="171"/>
       <c r="Q4" s="172"/>
-      <c r="R4" s="338"/>
-      <c r="S4" s="339"/>
-      <c r="T4" s="339"/>
-      <c r="U4" s="339"/>
-      <c r="V4" s="339"/>
-      <c r="W4" s="339"/>
-      <c r="X4" s="340"/>
+      <c r="R4" s="344"/>
+      <c r="S4" s="345"/>
+      <c r="T4" s="345"/>
+      <c r="U4" s="345"/>
+      <c r="V4" s="345"/>
+      <c r="W4" s="345"/>
+      <c r="X4" s="346"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
       <c r="A5" s="168"/>
-      <c r="B5" s="341" t="s">
+      <c r="B5" s="347" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="341"/>
-      <c r="D5" s="341"/>
-      <c r="E5" s="341"/>
-      <c r="F5" s="341"/>
-      <c r="G5" s="341"/>
-      <c r="H5" s="341"/>
-      <c r="I5" s="341"/>
-      <c r="J5" s="341"/>
-      <c r="K5" s="341"/>
-      <c r="L5" s="341"/>
-      <c r="M5" s="341"/>
-      <c r="N5" s="342"/>
+      <c r="C5" s="347"/>
+      <c r="D5" s="347"/>
+      <c r="E5" s="347"/>
+      <c r="F5" s="347"/>
+      <c r="G5" s="347"/>
+      <c r="H5" s="347"/>
+      <c r="I5" s="347"/>
+      <c r="J5" s="347"/>
+      <c r="K5" s="347"/>
+      <c r="L5" s="347"/>
+      <c r="M5" s="347"/>
+      <c r="N5" s="348"/>
       <c r="O5" s="173" t="s">
         <v>4</v>
       </c>
       <c r="P5" s="173"/>
       <c r="Q5" s="174"/>
-      <c r="R5" s="343" t="str">
+      <c r="R5" s="349" t="str">
         <f>갑100A!N6</f>
         <v>SIS/GI-SE-RT-TNTFLYSH001</v>
       </c>
-      <c r="S5" s="344"/>
-      <c r="T5" s="344"/>
-      <c r="U5" s="344"/>
-      <c r="V5" s="344"/>
-      <c r="W5" s="344"/>
-      <c r="X5" s="345"/>
+      <c r="S5" s="350"/>
+      <c r="T5" s="350"/>
+      <c r="U5" s="350"/>
+      <c r="V5" s="350"/>
+      <c r="W5" s="350"/>
+      <c r="X5" s="351"/>
     </row>
     <row r="6" spans="1:38" ht="12.75" customHeight="1">
       <c r="A6" s="175"/>
@@ -25745,13 +29752,13 @@
       </c>
       <c r="P6" s="178"/>
       <c r="Q6" s="179"/>
-      <c r="R6" s="346"/>
-      <c r="S6" s="347"/>
-      <c r="T6" s="347"/>
-      <c r="U6" s="347"/>
-      <c r="V6" s="347"/>
-      <c r="W6" s="347"/>
-      <c r="X6" s="348"/>
+      <c r="R6" s="352"/>
+      <c r="S6" s="353"/>
+      <c r="T6" s="353"/>
+      <c r="U6" s="353"/>
+      <c r="V6" s="353"/>
+      <c r="W6" s="353"/>
+      <c r="X6" s="354"/>
     </row>
     <row r="7" spans="1:38" s="9" customFormat="1" ht="10.5" customHeight="1">
       <c r="A7" s="3"/>
@@ -25979,9 +29986,9 @@
       <c r="T10" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U10" s="349"/>
-      <c r="V10" s="350"/>
-      <c r="W10" s="351"/>
+      <c r="U10" s="355"/>
+      <c r="V10" s="356"/>
+      <c r="W10" s="357"/>
       <c r="X10" s="120" t="s">
         <v>217</v>
       </c>
@@ -26007,9 +30014,9 @@
       <c r="R11" s="187"/>
       <c r="S11" s="187"/>
       <c r="T11" s="188"/>
-      <c r="U11" s="352"/>
-      <c r="V11" s="353"/>
-      <c r="W11" s="354"/>
+      <c r="U11" s="334"/>
+      <c r="V11" s="335"/>
+      <c r="W11" s="336"/>
       <c r="X11" s="184"/>
     </row>
     <row r="12" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -26621,42 +30628,42 @@
       <c r="R34" s="192"/>
       <c r="S34" s="192"/>
       <c r="T34" s="193"/>
-      <c r="U34" s="352" t="s">
+      <c r="U34" s="334" t="s">
         <v>219</v>
       </c>
-      <c r="V34" s="353"/>
-      <c r="W34" s="354"/>
+      <c r="V34" s="335"/>
+      <c r="W34" s="336"/>
       <c r="X34" s="184" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="18.75" customHeight="1">
-      <c r="A35" s="358" t="s">
+      <c r="A35" s="337" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="359"/>
-      <c r="C35" s="359"/>
-      <c r="D35" s="359"/>
-      <c r="E35" s="359"/>
-      <c r="F35" s="359"/>
-      <c r="G35" s="359"/>
-      <c r="H35" s="359"/>
-      <c r="I35" s="359"/>
-      <c r="J35" s="359"/>
-      <c r="K35" s="359"/>
-      <c r="L35" s="359"/>
-      <c r="M35" s="359"/>
-      <c r="N35" s="359"/>
-      <c r="O35" s="359"/>
-      <c r="P35" s="359"/>
-      <c r="Q35" s="359"/>
-      <c r="R35" s="359"/>
-      <c r="S35" s="359"/>
-      <c r="T35" s="359"/>
-      <c r="U35" s="359"/>
-      <c r="V35" s="359"/>
-      <c r="W35" s="359"/>
-      <c r="X35" s="360"/>
+      <c r="B35" s="338"/>
+      <c r="C35" s="338"/>
+      <c r="D35" s="338"/>
+      <c r="E35" s="338"/>
+      <c r="F35" s="338"/>
+      <c r="G35" s="338"/>
+      <c r="H35" s="338"/>
+      <c r="I35" s="338"/>
+      <c r="J35" s="338"/>
+      <c r="K35" s="338"/>
+      <c r="L35" s="338"/>
+      <c r="M35" s="338"/>
+      <c r="N35" s="338"/>
+      <c r="O35" s="338"/>
+      <c r="P35" s="338"/>
+      <c r="Q35" s="338"/>
+      <c r="R35" s="338"/>
+      <c r="S35" s="338"/>
+      <c r="T35" s="338"/>
+      <c r="U35" s="338"/>
+      <c r="V35" s="338"/>
+      <c r="W35" s="338"/>
+      <c r="X35" s="339"/>
     </row>
     <row r="36" spans="1:24" ht="19.5" customHeight="1"/>
     <row r="37" spans="1:24" ht="19.5" customHeight="1"/>
@@ -26684,24 +30691,6 @@
     <row r="59" ht="19.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="U32:W32"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="U34:W34"/>
-    <mergeCell ref="A35:X35"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="U28:W28"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="U31:W31"/>
     <mergeCell ref="U17:W17"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="R3:X4"/>
@@ -26716,6 +30705,24 @@
     <mergeCell ref="U14:W14"/>
     <mergeCell ref="U15:W15"/>
     <mergeCell ref="U16:W16"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="A35:X35"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="U31:W31"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="U22:W22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.49" right="0.31" top="0.57999999999999996" bottom="0.73" header="0.5" footer="0.51"/>

--- a/Na-aba/home/data/RT KS양식.xlsx
+++ b/Na-aba/home/data/RT KS양식.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjch2\Desktop\보고서\Project PROVIDENCE\Request\PMI\Na-aba\home\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\-\OneDrive\바탕 화면\home\Na-aba\home\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3394553E-D5E8-478C-BABE-C1133984E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="951" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="951" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="갑100A" sheetId="1782" r:id="rId1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="230">
   <si>
     <t xml:space="preserve">□    </t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -291,10 +290,6 @@
   </si>
   <si>
     <t>⑮</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>V</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -820,14 +815,6 @@
     <t>■</t>
   </si>
   <si>
-    <t>2-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Item Name / No.           제품명 / 번호   </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -916,14 +903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2024.12.18</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>030/031</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">      Page  </t>
     </r>
@@ -1002,10 +981,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Film Contrast</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1023,10 +998,6 @@
   </si>
   <si>
     <t xml:space="preserve">               30 초</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4“- 100A PIPE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1095,7 +1066,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="10">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2018,7 +1989,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="362">
+  <cellXfs count="363">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="31" applyBorder="1">
       <alignment vertical="center"/>
@@ -2746,6 +2717,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="22" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="22" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3105,39 +3079,39 @@
     </xf>
   </cellXfs>
   <cellStyles count="33">
-    <cellStyle name="AeE­ [0]_INQUIRY ¿μ¾÷AßAø " xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="AeE­_INQUIRY ¿μ¾÷AßAø " xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="AÞ¸¶ [0]_INQUIRY ¿μ¾÷AßAø " xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="AÞ¸¶_INQUIRY ¿μ¾÷AßAø " xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="C￥AØ_¿μ¾÷CoE² " xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Comma0" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Currency0" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Date" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Fixed" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Heading 1" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Heading 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Total" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="뷭?_BOOKSHIP" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="콤마 [0]_1202" xfId="19" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="콤마_1202" xfId="20" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="AeE­ [0]_INQUIRY ¿μ¾÷AßAø " xfId="1"/>
+    <cellStyle name="AeE­_INQUIRY ¿μ¾÷AßAø " xfId="2"/>
+    <cellStyle name="AÞ¸¶ [0]_INQUIRY ¿μ¾÷AßAø " xfId="3"/>
+    <cellStyle name="AÞ¸¶_INQUIRY ¿μ¾÷AßAø " xfId="4"/>
+    <cellStyle name="C￥AØ_¿μ¾÷CoE² " xfId="5"/>
+    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="6"/>
+    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="7"/>
+    <cellStyle name="Comma0" xfId="8"/>
+    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="9"/>
+    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="10"/>
+    <cellStyle name="Currency0" xfId="11"/>
+    <cellStyle name="Date" xfId="12"/>
+    <cellStyle name="Fixed" xfId="13"/>
+    <cellStyle name="Heading 1" xfId="14"/>
+    <cellStyle name="Heading 2" xfId="15"/>
+    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="16"/>
+    <cellStyle name="Total" xfId="17"/>
+    <cellStyle name="뷭?_BOOKSHIP" xfId="18"/>
+    <cellStyle name="콤마 [0]_1202" xfId="19"/>
+    <cellStyle name="콤마_1202" xfId="20"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 10" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="표준 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="표준 3" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="표준 4" xfId="24" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="표준 5" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="표준 6" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="표준 7" xfId="27" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="표준 8" xfId="28" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="표준 9" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="표준_002 RT" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="표준_개정 성적서KS_036~039RT" xfId="31" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="표준_개정 성적서KS_064~067 RT" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="표준 10" xfId="21"/>
+    <cellStyle name="표준 2" xfId="22"/>
+    <cellStyle name="표준 3" xfId="23"/>
+    <cellStyle name="표준 4" xfId="24"/>
+    <cellStyle name="표준 5" xfId="25"/>
+    <cellStyle name="표준 6" xfId="26"/>
+    <cellStyle name="표준 7" xfId="27"/>
+    <cellStyle name="표준 8" xfId="28"/>
+    <cellStyle name="표준 9" xfId="29"/>
+    <cellStyle name="표준_002 RT" xfId="30"/>
+    <cellStyle name="표준_개정 성적서KS_036~039RT" xfId="31"/>
+    <cellStyle name="표준_개정 성적서KS_064~067 RT" xfId="32"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3172,7 +3146,7 @@
         <xdr:cNvPr id="2" name="Text Box 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98FAC1F-D651-492D-E939-17587CBF9C0A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98FAC1F-D651-492D-E939-17587CBF9C0A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3248,7 +3222,7 @@
         <xdr:cNvPr id="3" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33108353-919B-AD37-8380-B598B2AC622C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33108353-919B-AD37-8380-B598B2AC622C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3324,7 +3298,7 @@
         <xdr:cNvPr id="4" name="Text Box 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B09A7BCE-0182-22AD-800F-A6D64C804990}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B09A7BCE-0182-22AD-800F-A6D64C804990}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3407,7 +3381,7 @@
         <xdr:cNvPr id="5" name="Text Box 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC40579B-DD36-D58B-BF25-6475A330D45E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC40579B-DD36-D58B-BF25-6475A330D45E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3490,7 +3464,7 @@
         <xdr:cNvPr id="6" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBF231F-67C1-7044-4C04-A985C4802126}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBF231F-67C1-7044-4C04-A985C4802126}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3566,7 +3540,7 @@
         <xdr:cNvPr id="7" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42E42894-DD26-B890-153E-FEFBC93C5BB0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42E42894-DD26-B890-153E-FEFBC93C5BB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3642,7 +3616,7 @@
         <xdr:cNvPr id="3426053" name="Group 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EBFC3CA-1D9F-2B8F-FFEA-E3129C88045D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EBFC3CA-1D9F-2B8F-FFEA-E3129C88045D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3652,8 +3626,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1112520" y="7094220"/>
-          <a:ext cx="4853940" cy="960120"/>
+          <a:off x="1240155" y="7210425"/>
+          <a:ext cx="5408295" cy="971550"/>
           <a:chOff x="126" y="704"/>
           <a:chExt cx="571" cy="102"/>
         </a:xfrm>
@@ -3663,7 +3637,7 @@
           <xdr:cNvPr id="3426302" name="Oval 8" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB2D715-B3BA-72D1-7663-481940195AD6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB2D715-B3BA-72D1-7663-481940195AD6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3699,7 +3673,7 @@
           <xdr:cNvPr id="3426303" name="Oval 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57C72CF8-8A22-1FD4-1C87-1D9B53477408}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57C72CF8-8A22-1FD4-1C87-1D9B53477408}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3733,7 +3707,7 @@
           <xdr:cNvPr id="3426304" name="Freeform 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DECE7171-E42E-E6B6-7560-BAB3E453D084}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DECE7171-E42E-E6B6-7560-BAB3E453D084}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3820,7 +3794,7 @@
           <xdr:cNvPr id="12" name="Text Box 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50664E67-AC03-5680-08F1-67FED1FF9199}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50664E67-AC03-5680-08F1-67FED1FF9199}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3902,7 +3876,7 @@
           <xdr:cNvPr id="3426306" name="Line 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07D8A4A6-7E19-57C3-D5EE-6778B716BF37}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07D8A4A6-7E19-57C3-D5EE-6778B716BF37}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3941,7 +3915,7 @@
           <xdr:cNvPr id="3426307" name="Line 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0693E5E6-724B-45C8-AA51-BD6E7F9288BD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0693E5E6-724B-45C8-AA51-BD6E7F9288BD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3981,7 +3955,7 @@
           <xdr:cNvPr id="3426308" name="Line 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF5752C-9583-23DE-97FC-8BCF64E31B31}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF5752C-9583-23DE-97FC-8BCF64E31B31}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4021,7 +3995,7 @@
           <xdr:cNvPr id="3426309" name="Freeform 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44EE272A-98B8-A1DD-595F-FE9FCB493EF9}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44EE272A-98B8-A1DD-595F-FE9FCB493EF9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4113,7 +4087,7 @@
           <xdr:cNvPr id="3426310" name="Freeform 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46EAA80D-4F1E-2C49-CF64-E53C758C844B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46EAA80D-4F1E-2C49-CF64-E53C758C844B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4222,7 +4196,7 @@
           <xdr:cNvPr id="3426311" name="Rectangle 17" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB911486-1244-7A20-A27F-32973082E77D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB911486-1244-7A20-A27F-32973082E77D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4258,7 +4232,7 @@
           <xdr:cNvPr id="3426312" name="Rectangle 18" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1564D9F-73D7-4F14-31EF-84142B173058}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1564D9F-73D7-4F14-31EF-84142B173058}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4294,7 +4268,7 @@
           <xdr:cNvPr id="3426313" name="Freeform 19">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAEA1E1-3FFC-25F7-D054-6E320EF527C6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAEA1E1-3FFC-25F7-D054-6E320EF527C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4452,7 +4426,7 @@
           <xdr:cNvPr id="21" name="Text Box 20">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C5190DE-F310-DD96-090C-6F83B34DD216}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C5190DE-F310-DD96-090C-6F83B34DD216}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4534,7 +4508,7 @@
           <xdr:cNvPr id="3426315" name="Line 21">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872B52D8-8449-B7DF-E30F-48DA080C380B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872B52D8-8449-B7DF-E30F-48DA080C380B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4573,7 +4547,7 @@
           <xdr:cNvPr id="3426316" name="Line 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAA66FB-9C57-605C-A8FA-90F36E4A9101}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAA66FB-9C57-605C-A8FA-90F36E4A9101}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4612,7 +4586,7 @@
           <xdr:cNvPr id="3426317" name="Line 23">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50D9CFD-42FE-886B-E983-EDBCEC5AE6D0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50D9CFD-42FE-886B-E983-EDBCEC5AE6D0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4652,7 +4626,7 @@
           <xdr:cNvPr id="3426318" name="Line 24">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DBF658-A7FA-E45F-D99A-E81B7714669B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DBF658-A7FA-E45F-D99A-E81B7714669B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4692,7 +4666,7 @@
           <xdr:cNvPr id="3426319" name="Freeform 25">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9464587C-B90F-D562-13CA-532EB2EC585F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9464587C-B90F-D562-13CA-532EB2EC585F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4779,7 +4753,7 @@
           <xdr:cNvPr id="3426320" name="Freeform 26" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4695B5DE-36AB-9E91-6472-92279588E80A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4695B5DE-36AB-9E91-6472-92279588E80A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4884,7 +4858,7 @@
           <xdr:cNvPr id="3426321" name="Oval 27" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2572122B-3C59-710B-AA97-632F09B5B6D8}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2572122B-3C59-710B-AA97-632F09B5B6D8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4920,7 +4894,7 @@
           <xdr:cNvPr id="3426322" name="Oval 28">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09773257-DEAE-736F-F796-142B2C536BB3}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09773257-DEAE-736F-F796-142B2C536BB3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4954,7 +4928,7 @@
           <xdr:cNvPr id="3426323" name="Freeform 29">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A173643-2A40-1E90-C76C-BBAA1644008E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A173643-2A40-1E90-C76C-BBAA1644008E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5041,7 +5015,7 @@
           <xdr:cNvPr id="31" name="Text Box 30">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6C877C-1FA0-1586-20B8-80C95CD2870D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6C877C-1FA0-1586-20B8-80C95CD2870D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5123,7 +5097,7 @@
           <xdr:cNvPr id="3426325" name="Line 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E59B9CD-9318-B259-4B58-45254C9389C7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E59B9CD-9318-B259-4B58-45254C9389C7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5162,7 +5136,7 @@
           <xdr:cNvPr id="3426326" name="Line 32">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF4915B2-ED67-B6DE-1061-3E1D9B6B95DA}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF4915B2-ED67-B6DE-1061-3E1D9B6B95DA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5202,7 +5176,7 @@
           <xdr:cNvPr id="3426327" name="Line 33">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68D33C33-5690-4953-C852-754679B37D0D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68D33C33-5690-4953-C852-754679B37D0D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5242,7 +5216,7 @@
           <xdr:cNvPr id="3426328" name="Freeform 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C218D996-5BA5-8B07-3910-DBD29E2C0182}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C218D996-5BA5-8B07-3910-DBD29E2C0182}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5334,7 +5308,7 @@
           <xdr:cNvPr id="3426329" name="Freeform 35">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FA2D215-2902-7EEE-27C6-2609BC661BB9}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FA2D215-2902-7EEE-27C6-2609BC661BB9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5443,7 +5417,7 @@
           <xdr:cNvPr id="3426330" name="Rectangle 36" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F86858F-5AB7-D1D4-6F6A-77589C0BDB80}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F86858F-5AB7-D1D4-6F6A-77589C0BDB80}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5479,7 +5453,7 @@
           <xdr:cNvPr id="3426331" name="Rectangle 37" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69970C06-A64D-3272-7649-CBC0387D73B0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69970C06-A64D-3272-7649-CBC0387D73B0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5515,7 +5489,7 @@
           <xdr:cNvPr id="3426332" name="Freeform 38">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737F9507-8146-8D69-27D2-551E7F28B575}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737F9507-8146-8D69-27D2-551E7F28B575}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5673,7 +5647,7 @@
           <xdr:cNvPr id="40" name="Text Box 39">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FEBCC9E-844D-A558-B182-18A74105FDF2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FEBCC9E-844D-A558-B182-18A74105FDF2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5755,7 +5729,7 @@
           <xdr:cNvPr id="3426334" name="Line 40">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{124D42B8-E2C5-0E68-85D9-A0A76AC4FC66}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{124D42B8-E2C5-0E68-85D9-A0A76AC4FC66}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5794,7 +5768,7 @@
           <xdr:cNvPr id="3426335" name="Line 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433B5DA4-B752-C4B3-6D79-5E3AFB999842}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433B5DA4-B752-C4B3-6D79-5E3AFB999842}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5833,7 +5807,7 @@
           <xdr:cNvPr id="3426336" name="Freeform 42">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{774E1440-D564-9AC1-37FD-FAD4EB6DEB0D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{774E1440-D564-9AC1-37FD-FAD4EB6DEB0D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5920,7 +5894,7 @@
           <xdr:cNvPr id="3426337" name="Freeform 43" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE1DAC56-076E-C78B-F2E3-424BA00F692A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE1DAC56-076E-C78B-F2E3-424BA00F692A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6043,7 +6017,7 @@
           <xdr:cNvPr id="3426338" name="Line 44">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B071D06C-A4F8-7274-3DFF-D3412A36EC91}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B071D06C-A4F8-7274-3DFF-D3412A36EC91}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6083,7 +6057,7 @@
           <xdr:cNvPr id="3426339" name="Line 45">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFB49859-D88B-619F-DD7C-FAEE67EA407A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFB49859-D88B-619F-DD7C-FAEE67EA407A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6123,7 +6097,7 @@
           <xdr:cNvPr id="3426340" name="Freeform 46">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44647F3-C900-A7B0-F775-6F410E5D21CB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44647F3-C900-A7B0-F775-6F410E5D21CB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6245,7 +6219,7 @@
           <xdr:cNvPr id="3426341" name="Freeform 47">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4A771CB-7DAC-31BF-480B-D133F696B61D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4A771CB-7DAC-31BF-480B-D133F696B61D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6367,7 +6341,7 @@
           <xdr:cNvPr id="3426342" name="Oval 48" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FDC2419-5EDE-55A5-C717-EB0D58EE3D9A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FDC2419-5EDE-55A5-C717-EB0D58EE3D9A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6403,7 +6377,7 @@
           <xdr:cNvPr id="3426343" name="Oval 49">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F71CB4F-90C7-49F6-0C8D-2A717C497939}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F71CB4F-90C7-49F6-0C8D-2A717C497939}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6437,7 +6411,7 @@
           <xdr:cNvPr id="3426344" name="Line 50">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AEC434-2635-248C-ACEF-8B92DA2B1111}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AEC434-2635-248C-ACEF-8B92DA2B1111}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6476,7 +6450,7 @@
           <xdr:cNvPr id="3426345" name="Line 51">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2D53B0-90D4-2988-F589-05C44EF2F018}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2D53B0-90D4-2988-F589-05C44EF2F018}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6516,7 +6490,7 @@
           <xdr:cNvPr id="3426346" name="Freeform 52">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{710B5F45-290D-B37E-2491-B7FD74E256E6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{710B5F45-290D-B37E-2491-B7FD74E256E6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6608,7 +6582,7 @@
           <xdr:cNvPr id="3426347" name="Freeform 53">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FB52224-71C0-58B4-D286-EED141FD4FB5}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FB52224-71C0-58B4-D286-EED141FD4FB5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6717,7 +6691,7 @@
           <xdr:cNvPr id="3426348" name="Rectangle 54" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A2B03D3-ADAF-FB71-E515-3F249C12BD89}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A2B03D3-ADAF-FB71-E515-3F249C12BD89}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6753,7 +6727,7 @@
           <xdr:cNvPr id="3426349" name="Line 55">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C716F34-8AC0-E246-90A8-77FF8D724164}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C716F34-8AC0-E246-90A8-77FF8D724164}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6793,7 +6767,7 @@
           <xdr:cNvPr id="3426350" name="Line 56">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7DD7220-82FE-66FB-98CF-BE6E627773F5}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7DD7220-82FE-66FB-98CF-BE6E627773F5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6833,7 +6807,7 @@
           <xdr:cNvPr id="3426351" name="Line 57">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C671D2B-9CF3-B0AE-49C0-8AE7A098936B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C671D2B-9CF3-B0AE-49C0-8AE7A098936B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6872,7 +6846,7 @@
           <xdr:cNvPr id="3426352" name="Line 58">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8B856E1-F3A6-6044-16B6-EFEBA81D9D41}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8B856E1-F3A6-6044-16B6-EFEBA81D9D41}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6911,7 +6885,7 @@
           <xdr:cNvPr id="3426353" name="Line 59">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6AFD834-2451-3E6E-19D9-25FE123ACC0A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6AFD834-2451-3E6E-19D9-25FE123ACC0A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6951,7 +6925,7 @@
           <xdr:cNvPr id="3426354" name="Freeform 60" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D16C236-8CC6-9169-7FEC-441DAB0C4655}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D16C236-8CC6-9169-7FEC-441DAB0C4655}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7033,7 +7007,7 @@
           <xdr:cNvPr id="3426355" name="Oval 61" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A63C2A9-AE9A-0925-D6E1-0320DF7989F1}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A63C2A9-AE9A-0925-D6E1-0320DF7989F1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7076,7 +7050,7 @@
           <xdr:cNvPr id="3426356" name="Freeform 62">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3CEDCF-48B8-6A88-7100-D60B8D845DA8}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3CEDCF-48B8-6A88-7100-D60B8D845DA8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7156,7 +7130,7 @@
           <xdr:cNvPr id="3426357" name="Line 63">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBDD475D-5E5F-5FE2-B67A-4F70F2B0A8D7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBDD475D-5E5F-5FE2-B67A-4F70F2B0A8D7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7195,7 +7169,7 @@
           <xdr:cNvPr id="3426358" name="Line 64">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7622C82A-704E-9E4A-4867-6D0E1235FFE7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7622C82A-704E-9E4A-4867-6D0E1235FFE7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7235,7 +7209,7 @@
           <xdr:cNvPr id="3426359" name="Line 65">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61087BAD-35AA-A724-802F-0B15B7221EC4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61087BAD-35AA-A724-802F-0B15B7221EC4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7275,7 +7249,7 @@
           <xdr:cNvPr id="3426360" name="Oval 66" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DE614A0-5065-15AE-086E-3C07CE8B12AD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DE614A0-5065-15AE-086E-3C07CE8B12AD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7311,7 +7285,7 @@
           <xdr:cNvPr id="3426361" name="Oval 67">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC882F86-215D-716E-310D-883A5FDA1E89}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC882F86-215D-716E-310D-883A5FDA1E89}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7345,7 +7319,7 @@
           <xdr:cNvPr id="3426362" name="Line 68">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3CCB6BB-79A3-89C7-4FF2-0B15D9BCA850}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3CCB6BB-79A3-89C7-4FF2-0B15D9BCA850}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7384,7 +7358,7 @@
           <xdr:cNvPr id="3426363" name="Line 69">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644AC0D5-7C23-CA66-B4EA-2387CD92B099}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644AC0D5-7C23-CA66-B4EA-2387CD92B099}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7424,7 +7398,7 @@
           <xdr:cNvPr id="3426364" name="Freeform 70">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{043C11A5-D967-21F9-D426-88C6ECCB8835}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{043C11A5-D967-21F9-D426-88C6ECCB8835}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7516,7 +7490,7 @@
           <xdr:cNvPr id="3426365" name="Freeform 71">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D950DA3-EFC4-48EF-FD7F-189A54D1413F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D950DA3-EFC4-48EF-FD7F-189A54D1413F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7625,7 +7599,7 @@
           <xdr:cNvPr id="3426366" name="Rectangle 72" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51234E0C-4F85-D8D6-4BAB-15D62EEEA602}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51234E0C-4F85-D8D6-4BAB-15D62EEEA602}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7661,7 +7635,7 @@
           <xdr:cNvPr id="3426367" name="Line 73">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC4019F9-1102-F352-48CD-189A3FC0393C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC4019F9-1102-F352-48CD-189A3FC0393C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7701,7 +7675,7 @@
           <xdr:cNvPr id="3426368" name="Line 74">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FC979E4-50F6-6D7A-2926-44649FAF462C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FC979E4-50F6-6D7A-2926-44649FAF462C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7741,7 +7715,7 @@
           <xdr:cNvPr id="3426369" name="Line 75">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0A1BF8B-5026-0FED-FA74-61A298124600}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0A1BF8B-5026-0FED-FA74-61A298124600}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7780,7 +7754,7 @@
           <xdr:cNvPr id="3426370" name="Line 76">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC9CAA3-1FEF-C1A2-385F-7806B57BF1DF}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC9CAA3-1FEF-C1A2-385F-7806B57BF1DF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7820,7 +7794,7 @@
           <xdr:cNvPr id="3426371" name="Freeform 77" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C0E6CD3-17D4-A128-7D61-BFE007FDCAE9}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C0E6CD3-17D4-A128-7D61-BFE007FDCAE9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7902,7 +7876,7 @@
           <xdr:cNvPr id="3426372" name="Oval 78" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90829CD4-EB5E-B81B-0452-04EC1271C954}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90829CD4-EB5E-B81B-0452-04EC1271C954}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7945,7 +7919,7 @@
           <xdr:cNvPr id="3426373" name="Freeform 79">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9A8B62-405D-1800-F4A8-94DCBC2DA8BC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9A8B62-405D-1800-F4A8-94DCBC2DA8BC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8025,7 +7999,7 @@
           <xdr:cNvPr id="3426374" name="Line 80">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC2518C-1B81-F7C2-591C-3B61BF7F77AA}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC2518C-1B81-F7C2-591C-3B61BF7F77AA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8064,7 +8038,7 @@
           <xdr:cNvPr id="3426375" name="Line 81">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDA586C-1B9D-D9FD-0169-AEEF933D9CCE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDA586C-1B9D-D9FD-0169-AEEF933D9CCE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8104,7 +8078,7 @@
           <xdr:cNvPr id="3426376" name="Line 82">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2A94FEE-2F75-6223-EF85-634B0A71DADD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2A94FEE-2F75-6223-EF85-634B0A71DADD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8160,7 +8134,7 @@
         <xdr:cNvPr id="3426054" name="Group 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EE51EF4-DF1A-7DE5-A402-F9624DB6D3C6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EE51EF4-DF1A-7DE5-A402-F9624DB6D3C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8170,8 +8144,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1318260" y="5867400"/>
-          <a:ext cx="4648200" cy="1120140"/>
+          <a:off x="1461135" y="5972175"/>
+          <a:ext cx="5187315" cy="1131570"/>
           <a:chOff x="150" y="536"/>
           <a:chExt cx="540" cy="120"/>
         </a:xfrm>
@@ -8181,7 +8155,7 @@
           <xdr:cNvPr id="3426223" name="Rectangle 84" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46DA9E74-5DC3-DC5B-594E-E033691940F2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46DA9E74-5DC3-DC5B-594E-E033691940F2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8217,7 +8191,7 @@
           <xdr:cNvPr id="3426224" name="Freeform 85">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{038DE85B-ACD4-A011-62B8-87F89CD8A9AB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{038DE85B-ACD4-A011-62B8-87F89CD8A9AB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8339,7 +8313,7 @@
           <xdr:cNvPr id="87" name="Text Box 86">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52ECB7DB-198D-BDC4-9E68-8E414F6EA2C4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52ECB7DB-198D-BDC4-9E68-8E414F6EA2C4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8388,7 +8362,7 @@
           <xdr:cNvPr id="3426226" name="Line 87">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8252AC3-8671-9826-8925-C4B246C540D8}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8252AC3-8671-9826-8925-C4B246C540D8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8427,7 +8401,7 @@
           <xdr:cNvPr id="3426227" name="Line 88">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E17AA20-29D1-0BC7-FA2A-C872831A792E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E17AA20-29D1-0BC7-FA2A-C872831A792E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8467,7 +8441,7 @@
           <xdr:cNvPr id="3426228" name="Line 89">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BE32EB0-732B-7310-B31B-82B933D6E057}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BE32EB0-732B-7310-B31B-82B933D6E057}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8507,7 +8481,7 @@
           <xdr:cNvPr id="3426229" name="Line 90">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72BF71E1-4200-4F57-E8D7-BDA4E057E54B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72BF71E1-4200-4F57-E8D7-BDA4E057E54B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8546,7 +8520,7 @@
           <xdr:cNvPr id="92" name="Text Box 91">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9CD1108-FB52-74D5-12A0-C04F7992D1C7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9CD1108-FB52-74D5-12A0-C04F7992D1C7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8595,7 +8569,7 @@
           <xdr:cNvPr id="93" name="Text Box 92">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1DE41A9-32F5-6F9D-1ABE-32F99068BF85}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1DE41A9-32F5-6F9D-1ABE-32F99068BF85}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8644,7 +8618,7 @@
           <xdr:cNvPr id="3426232" name="Oval 93" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6864B039-C9F6-DE9F-6172-F64F68759CEC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6864B039-C9F6-DE9F-6172-F64F68759CEC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8680,7 +8654,7 @@
           <xdr:cNvPr id="3426233" name="Oval 94">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2801247-BF8F-EDD4-2C50-0DAEFBC6078E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2801247-BF8F-EDD4-2C50-0DAEFBC6078E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8714,7 +8688,7 @@
           <xdr:cNvPr id="96" name="Text Box 95">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01E2D569-ECD2-5995-191A-8F6FB01250A6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01E2D569-ECD2-5995-191A-8F6FB01250A6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8775,7 +8749,7 @@
           <xdr:cNvPr id="3426235" name="Line 96">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DB60D59-6F3A-6685-2D52-3799EB16040D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DB60D59-6F3A-6685-2D52-3799EB16040D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8814,7 +8788,7 @@
           <xdr:cNvPr id="3426236" name="Line 97">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B612424-6BB9-8201-19F0-3C902518092D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B612424-6BB9-8201-19F0-3C902518092D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8853,7 +8827,7 @@
           <xdr:cNvPr id="3426237" name="Line 98">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6395BB3-E5CC-7ECF-E095-A78FDB29A60D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6395BB3-E5CC-7ECF-E095-A78FDB29A60D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8892,7 +8866,7 @@
           <xdr:cNvPr id="3426238" name="Line 99">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{790F8A3F-FF8F-06BB-C9A4-316245040E76}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{790F8A3F-FF8F-06BB-C9A4-316245040E76}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8931,7 +8905,7 @@
           <xdr:cNvPr id="3426239" name="Arc 100">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41D7A27F-C0D8-B8ED-A432-256A4DB48132}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41D7A27F-C0D8-B8ED-A432-256A4DB48132}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9029,7 +9003,7 @@
           <xdr:cNvPr id="3426240" name="Arc 101">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E79F42B-1BED-4521-812B-EEF266EC90A1}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E79F42B-1BED-4521-812B-EEF266EC90A1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9127,7 +9101,7 @@
           <xdr:cNvPr id="3426241" name="Arc 102">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54F8C81-9478-3D21-9B59-CAF412ADD8D6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F54F8C81-9478-3D21-9B59-CAF412ADD8D6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9225,7 +9199,7 @@
           <xdr:cNvPr id="3426242" name="Arc 103">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87A12D66-1305-1365-423D-EF0C73087BC2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87A12D66-1305-1365-423D-EF0C73087BC2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9323,7 +9297,7 @@
           <xdr:cNvPr id="3426243" name="Freeform 104">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA86188-1C16-A505-4E71-306F3792CBB2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA86188-1C16-A505-4E71-306F3792CBB2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9415,7 +9389,7 @@
           <xdr:cNvPr id="3426244" name="Freeform 105">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA988642-037F-ACFC-63A9-9ED14E419620}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA988642-037F-ACFC-63A9-9ED14E419620}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9524,7 +9498,7 @@
           <xdr:cNvPr id="3426245" name="Rectangle 106" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA5D6BF-DAF1-881F-E2D6-69DA02384F2C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA5D6BF-DAF1-881F-E2D6-69DA02384F2C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9560,7 +9534,7 @@
           <xdr:cNvPr id="3426246" name="Rectangle 107" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D04E6B-F17F-EEDE-1276-1CE43C75CF40}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D04E6B-F17F-EEDE-1276-1CE43C75CF40}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9596,7 +9570,7 @@
           <xdr:cNvPr id="3426247" name="Line 108">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA7D1EB9-3A3D-A6B2-3157-B6B0D0717B87}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA7D1EB9-3A3D-A6B2-3157-B6B0D0717B87}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9635,7 +9609,7 @@
           <xdr:cNvPr id="3426248" name="Freeform 109">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCA62FFD-6FA3-B517-22EC-90FA76D41FE1}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCA62FFD-6FA3-B517-22EC-90FA76D41FE1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9722,7 +9696,7 @@
           <xdr:cNvPr id="3426249" name="Freeform 110" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA348F30-0FBF-5AB4-4953-B7D5DF46B6C6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA348F30-0FBF-5AB4-4953-B7D5DF46B6C6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9827,7 +9801,7 @@
           <xdr:cNvPr id="3426250" name="Line 111">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B320389-4457-5DE4-7F2F-720CBB1AC17E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B320389-4457-5DE4-7F2F-720CBB1AC17E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9867,7 +9841,7 @@
           <xdr:cNvPr id="3426251" name="Line 112">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27582639-D742-E655-FB57-09B0B2D29342}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27582639-D742-E655-FB57-09B0B2D29342}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9907,7 +9881,7 @@
           <xdr:cNvPr id="3426252" name="Freeform 113">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50D5212A-E377-ADF8-9C4B-744C36491BB6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50D5212A-E377-ADF8-9C4B-744C36491BB6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10154,7 +10128,7 @@
           <xdr:cNvPr id="115" name="Text Box 114">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{303B1D54-E961-1A56-D4EE-70AC0D694145}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{303B1D54-E961-1A56-D4EE-70AC0D694145}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10215,7 +10189,7 @@
           <xdr:cNvPr id="3426254" name="Line 115">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B519D1CB-112B-937C-D406-7CAE32C61FBE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B519D1CB-112B-937C-D406-7CAE32C61FBE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10254,7 +10228,7 @@
           <xdr:cNvPr id="3426255" name="Line 116">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CCE304-C76A-F586-08C6-613FD1D607F9}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CCE304-C76A-F586-08C6-613FD1D607F9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10294,7 +10268,7 @@
           <xdr:cNvPr id="3426256" name="Line 117">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E90F25B-F483-DF3A-40DC-8C4A6D00B07C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E90F25B-F483-DF3A-40DC-8C4A6D00B07C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10334,7 +10308,7 @@
           <xdr:cNvPr id="3426257" name="Oval 118" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B85C85-F0EB-005D-2819-EC72579AA5C9}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B85C85-F0EB-005D-2819-EC72579AA5C9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10370,7 +10344,7 @@
           <xdr:cNvPr id="3426258" name="Oval 119">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D317AF-3380-FA25-1A4D-40403A2272AB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D317AF-3380-FA25-1A4D-40403A2272AB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10404,7 +10378,7 @@
           <xdr:cNvPr id="3426259" name="Freeform 120">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1EF327A-9D45-0B1A-3308-4B005F01729B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1EF327A-9D45-0B1A-3308-4B005F01729B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10491,7 +10465,7 @@
           <xdr:cNvPr id="3426260" name="Line 121">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F00123A-B8C7-1EA1-2C3C-5503615BBB19}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F00123A-B8C7-1EA1-2C3C-5503615BBB19}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10530,7 +10504,7 @@
           <xdr:cNvPr id="3426261" name="Line 122">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20635BB3-B634-F06A-7630-DDF038A3DDEB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20635BB3-B634-F06A-7630-DDF038A3DDEB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10570,7 +10544,7 @@
           <xdr:cNvPr id="3426262" name="Line 123">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A8A054-5C75-4AF5-6887-81F5D2A3EF11}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A8A054-5C75-4AF5-6887-81F5D2A3EF11}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10610,7 +10584,7 @@
           <xdr:cNvPr id="125" name="Text Box 124">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E34E6B31-3F11-6D7C-186C-3A0D563B53CC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E34E6B31-3F11-6D7C-186C-3A0D563B53CC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10671,7 +10645,7 @@
           <xdr:cNvPr id="126" name="Text Box 125">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35324F7-5B95-CEAF-3E16-F6D575331BA2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35324F7-5B95-CEAF-3E16-F6D575331BA2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10732,7 +10706,7 @@
           <xdr:cNvPr id="3426265" name="Freeform 126">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E800F296-CB02-E588-DD1D-98F2557E1C81}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E800F296-CB02-E588-DD1D-98F2557E1C81}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10824,7 +10798,7 @@
           <xdr:cNvPr id="3426266" name="Freeform 127">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3032F14C-6BD1-2E3E-E9D2-3FC9E4816A1F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3032F14C-6BD1-2E3E-E9D2-3FC9E4816A1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10933,7 +10907,7 @@
           <xdr:cNvPr id="3426267" name="Rectangle 128" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30CC88B7-E076-73F2-DA33-936D2D27D867}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30CC88B7-E076-73F2-DA33-936D2D27D867}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10969,7 +10943,7 @@
           <xdr:cNvPr id="3426268" name="Rectangle 129" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEEBF1A-81C7-F1A3-1879-F27AB8C93646}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEEBF1A-81C7-F1A3-1879-F27AB8C93646}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11005,7 +10979,7 @@
           <xdr:cNvPr id="3426269" name="Freeform 130">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DDA93EF-66B7-5E36-EA64-4B6E8D63E2E0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DDA93EF-66B7-5E36-EA64-4B6E8D63E2E0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11092,7 +11066,7 @@
           <xdr:cNvPr id="3426270" name="Freeform 131" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{173CE644-B2D6-6E6C-B0B1-A0E165E738ED}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{173CE644-B2D6-6E6C-B0B1-A0E165E738ED}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11197,7 +11171,7 @@
           <xdr:cNvPr id="3426271" name="Line 132">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBBFE3D5-F6AB-D07B-E7BE-6DBA9050F28C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBBFE3D5-F6AB-D07B-E7BE-6DBA9050F28C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11237,7 +11211,7 @@
           <xdr:cNvPr id="3426272" name="Line 133">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B6072E8-7679-B4B4-C2B7-54AC9F151BEB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B6072E8-7679-B4B4-C2B7-54AC9F151BEB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11277,7 +11251,7 @@
           <xdr:cNvPr id="3426273" name="Freeform 134">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BE60EB1-3CB2-B621-3733-40070652F20D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BE60EB1-3CB2-B621-3733-40070652F20D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11524,7 +11498,7 @@
           <xdr:cNvPr id="136" name="Text Box 135">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0515C86D-CB2F-6788-3040-E98ECE5BDCC5}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0515C86D-CB2F-6788-3040-E98ECE5BDCC5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11585,7 +11559,7 @@
           <xdr:cNvPr id="3426275" name="Freeform 136">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{757E0CB5-825D-4914-D2D7-F917BA41425E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{757E0CB5-825D-4914-D2D7-F917BA41425E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11707,7 +11681,7 @@
           <xdr:cNvPr id="3426276" name="Freeform 137">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1E585E-2894-6C8B-E498-9542EBCB8890}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1E585E-2894-6C8B-E498-9542EBCB8890}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11829,7 +11803,7 @@
           <xdr:cNvPr id="3426277" name="Line 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{613FEA6E-C272-A597-76A1-16FA0220EBF6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{613FEA6E-C272-A597-76A1-16FA0220EBF6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11868,7 +11842,7 @@
           <xdr:cNvPr id="3426278" name="Line 139">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916E7F06-7C05-04BC-EEDC-AE8BC76707D7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916E7F06-7C05-04BC-EEDC-AE8BC76707D7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11908,7 +11882,7 @@
           <xdr:cNvPr id="3426279" name="Line 140">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61E23609-F7D5-8963-F580-2351D3C83B51}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61E23609-F7D5-8963-F580-2351D3C83B51}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11948,7 +11922,7 @@
           <xdr:cNvPr id="3426280" name="Line 141">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12FF408C-BD85-ECB7-9915-D0DCBF137BBF}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12FF408C-BD85-ECB7-9915-D0DCBF137BBF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11987,7 +11961,7 @@
           <xdr:cNvPr id="3426281" name="Oval 142" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB1B4402-D5CC-E1E8-D10A-778AE87C7D24}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB1B4402-D5CC-E1E8-D10A-778AE87C7D24}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12023,7 +11997,7 @@
           <xdr:cNvPr id="3426282" name="Oval 143">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F3F4C6A-C8C9-D374-3FB3-36D3A6975273}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F3F4C6A-C8C9-D374-3FB3-36D3A6975273}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12057,7 +12031,7 @@
           <xdr:cNvPr id="3426283" name="Line 144">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D25896E-F5F4-80A3-151F-D21EFC33A7E4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D25896E-F5F4-80A3-151F-D21EFC33A7E4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12096,7 +12070,7 @@
           <xdr:cNvPr id="3426284" name="Line 145">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{726083FD-3151-E2D8-1300-7337EBC41497}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{726083FD-3151-E2D8-1300-7337EBC41497}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12136,7 +12110,7 @@
           <xdr:cNvPr id="3426285" name="Freeform 146">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75230C73-ED7C-05AA-1823-63A74DDACECC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75230C73-ED7C-05AA-1823-63A74DDACECC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12228,7 +12202,7 @@
           <xdr:cNvPr id="3426286" name="Freeform 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4950B46-5821-6A65-A5F1-64712537732F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4950B46-5821-6A65-A5F1-64712537732F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12337,7 +12311,7 @@
           <xdr:cNvPr id="3426287" name="Rectangle 148" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC7FEDE1-0B57-1583-C2F6-25BA209B843D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC7FEDE1-0B57-1583-C2F6-25BA209B843D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12373,7 +12347,7 @@
           <xdr:cNvPr id="3426288" name="Rectangle 149" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA9FCDF6-79B4-614D-36EE-3DD7307E4D12}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA9FCDF6-79B4-614D-36EE-3DD7307E4D12}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12409,7 +12383,7 @@
           <xdr:cNvPr id="3426289" name="Freeform 150">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F524231-44F6-5DB6-D609-FEBBC3F1582A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F524231-44F6-5DB6-D609-FEBBC3F1582A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12496,7 +12470,7 @@
           <xdr:cNvPr id="3426290" name="Freeform 151" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D4FB9B1-016C-8745-2D95-83C4B8EDE198}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D4FB9B1-016C-8745-2D95-83C4B8EDE198}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12601,7 +12575,7 @@
           <xdr:cNvPr id="3426291" name="Line 152">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{386A7781-D34D-D465-1A3D-EB1641146E5A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{386A7781-D34D-D465-1A3D-EB1641146E5A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12641,7 +12615,7 @@
           <xdr:cNvPr id="3426292" name="Line 153">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D5EBAEB-6484-8A00-89FE-66271E2DB7E2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D5EBAEB-6484-8A00-89FE-66271E2DB7E2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12681,7 +12655,7 @@
           <xdr:cNvPr id="3426293" name="Freeform 154">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96DA03F2-44DB-8656-7C69-BF63FE9C7FCC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96DA03F2-44DB-8656-7C69-BF63FE9C7FCC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -12928,7 +12902,7 @@
           <xdr:cNvPr id="3426294" name="Freeform 155">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DFA85E1-387E-0134-0518-D17AC42F7C60}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DFA85E1-387E-0134-0518-D17AC42F7C60}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13050,7 +13024,7 @@
           <xdr:cNvPr id="3426295" name="Line 156">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4142565B-7175-408E-2D38-21FD09DC3BC7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4142565B-7175-408E-2D38-21FD09DC3BC7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13089,7 +13063,7 @@
           <xdr:cNvPr id="3426296" name="Freeform 157">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCFE9EB7-7FB8-5E60-4BDC-6BA968FC8A7D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCFE9EB7-7FB8-5E60-4BDC-6BA968FC8A7D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13176,7 +13150,7 @@
           <xdr:cNvPr id="3426297" name="Line 158">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E95A4C3-3988-3863-9E31-577559B373CC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E95A4C3-3988-3863-9E31-577559B373CC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13216,7 +13190,7 @@
           <xdr:cNvPr id="160" name="Text Box 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1225691D-88F9-EB7C-56AD-21C5C34F2601}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1225691D-88F9-EB7C-56AD-21C5C34F2601}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13277,7 +13251,7 @@
           <xdr:cNvPr id="3426299" name="Line 160">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3081FA7-1246-0AD4-C831-2AD5A26CEDCD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3081FA7-1246-0AD4-C831-2AD5A26CEDCD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13316,7 +13290,7 @@
           <xdr:cNvPr id="3426300" name="Line 161">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C98BE2A5-9661-EFE8-4F07-946A693E013F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C98BE2A5-9661-EFE8-4F07-946A693E013F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13356,7 +13330,7 @@
           <xdr:cNvPr id="3426301" name="Line 162">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74752195-E220-955E-D73D-2D0DD58B300A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74752195-E220-955E-D73D-2D0DD58B300A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13412,7 +13386,7 @@
         <xdr:cNvPr id="169" name="Text Box 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A363919A-F1DE-636D-84E1-B6B5595380DF}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A363919A-F1DE-636D-84E1-B6B5595380DF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13488,7 +13462,7 @@
         <xdr:cNvPr id="170" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C071E74A-6EE5-C4CC-8C18-58EE6F589C31}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C071E74A-6EE5-C4CC-8C18-58EE6F589C31}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13564,7 +13538,7 @@
         <xdr:cNvPr id="173" name="Text Box 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ABD7379-64FE-1FC5-CDED-99C3BA6AE5AB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ABD7379-64FE-1FC5-CDED-99C3BA6AE5AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13640,7 +13614,7 @@
         <xdr:cNvPr id="174" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042D797F-DB9F-F39F-FF6C-AE47842C3C68}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042D797F-DB9F-F39F-FF6C-AE47842C3C68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13716,7 +13690,7 @@
         <xdr:cNvPr id="3426064" name="Group 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3D5C0E-B65A-1908-8334-E38DD303E343}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3D5C0E-B65A-1908-8334-E38DD303E343}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13726,8 +13700,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1112520" y="7094220"/>
-          <a:ext cx="4853940" cy="960120"/>
+          <a:off x="1240155" y="7210425"/>
+          <a:ext cx="5408295" cy="971550"/>
           <a:chOff x="126" y="704"/>
           <a:chExt cx="571" cy="102"/>
         </a:xfrm>
@@ -13737,7 +13711,7 @@
           <xdr:cNvPr id="3426148" name="Oval 8" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91EDA04-9AFA-FCB4-7487-49A750481F81}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91EDA04-9AFA-FCB4-7487-49A750481F81}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13773,7 +13747,7 @@
           <xdr:cNvPr id="3426149" name="Oval 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD142D74-9A76-5CFB-BB4E-27B6632877FD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD142D74-9A76-5CFB-BB4E-27B6632877FD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13807,7 +13781,7 @@
           <xdr:cNvPr id="3426150" name="Freeform 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B5BE5DB-9681-5FEB-3E4A-477BAEFE1692}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B5BE5DB-9681-5FEB-3E4A-477BAEFE1692}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13893,7 +13867,7 @@
           <xdr:cNvPr id="179" name="Text Box 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4EBE38-ED01-8DC7-FB41-A9B377E75319}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4EBE38-ED01-8DC7-FB41-A9B377E75319}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -13972,7 +13946,7 @@
           <xdr:cNvPr id="3426152" name="Line 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5E7929-4EFC-A07E-70BF-0F0D81076487}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5E7929-4EFC-A07E-70BF-0F0D81076487}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14011,7 +13985,7 @@
           <xdr:cNvPr id="3426153" name="Line 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A79D3466-0FA5-617C-B9F2-10B0290AF247}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A79D3466-0FA5-617C-B9F2-10B0290AF247}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14051,7 +14025,7 @@
           <xdr:cNvPr id="3426154" name="Line 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B21DC6-19BB-9C07-8C55-6AC278C80E9F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B21DC6-19BB-9C07-8C55-6AC278C80E9F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14091,7 +14065,7 @@
           <xdr:cNvPr id="3426155" name="Freeform 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5146E7-CE65-A680-5BBC-EB98D92E7772}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5146E7-CE65-A680-5BBC-EB98D92E7772}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14182,7 +14156,7 @@
           <xdr:cNvPr id="3426156" name="Freeform 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D936D30-889F-19D6-2F9B-8177273360BF}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D936D30-889F-19D6-2F9B-8177273360BF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14290,7 +14264,7 @@
           <xdr:cNvPr id="3426157" name="Rectangle 17" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DCBF7BB-FD2A-BC8F-36A1-89E7E411ECCD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DCBF7BB-FD2A-BC8F-36A1-89E7E411ECCD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14326,7 +14300,7 @@
           <xdr:cNvPr id="3426158" name="Rectangle 18" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCB9900D-FC6A-C20C-8A3C-EAE454216A57}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCB9900D-FC6A-C20C-8A3C-EAE454216A57}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14362,7 +14336,7 @@
           <xdr:cNvPr id="3426159" name="Freeform 19">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988001A1-1BE2-E3F2-CFC1-668EC9FDDE3E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988001A1-1BE2-E3F2-CFC1-668EC9FDDE3E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14519,7 +14493,7 @@
           <xdr:cNvPr id="188" name="Text Box 20">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57DFAF6-2B59-2AC2-D3DF-A91DD23334B5}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57DFAF6-2B59-2AC2-D3DF-A91DD23334B5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14598,7 +14572,7 @@
           <xdr:cNvPr id="3426161" name="Line 21">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{499E48F0-C3F5-D320-767A-6DDF4AD796FA}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{499E48F0-C3F5-D320-767A-6DDF4AD796FA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14637,7 +14611,7 @@
           <xdr:cNvPr id="3426162" name="Line 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31B03450-B821-BA83-DDD9-CA471563E476}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31B03450-B821-BA83-DDD9-CA471563E476}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14676,7 +14650,7 @@
           <xdr:cNvPr id="3426163" name="Line 23">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7500CA25-B22E-516C-17AF-0E0B3A47F4D1}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7500CA25-B22E-516C-17AF-0E0B3A47F4D1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14716,7 +14690,7 @@
           <xdr:cNvPr id="3426164" name="Line 24">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4F0D4A-91D3-2AB6-CB71-5980A345EC0B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4F0D4A-91D3-2AB6-CB71-5980A345EC0B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14756,7 +14730,7 @@
           <xdr:cNvPr id="3426165" name="Freeform 25">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3EFD27E-C82E-DCF3-B66A-50BF7E845BEC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3EFD27E-C82E-DCF3-B66A-50BF7E845BEC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14842,7 +14816,7 @@
           <xdr:cNvPr id="3426166" name="Freeform 26" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B96CC863-465D-4569-C562-8494D826D9E8}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B96CC863-465D-4569-C562-8494D826D9E8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14946,7 +14920,7 @@
           <xdr:cNvPr id="3426167" name="Oval 27" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A894F6E-41F4-1F4C-62AF-11FB7772FA35}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A894F6E-41F4-1F4C-62AF-11FB7772FA35}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -14982,7 +14956,7 @@
           <xdr:cNvPr id="3426168" name="Oval 28">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F45C8D-78CF-E907-CB4B-866B50A8D9F8}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F45C8D-78CF-E907-CB4B-866B50A8D9F8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15016,7 +14990,7 @@
           <xdr:cNvPr id="3426169" name="Freeform 29">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820E49E2-A42E-F74B-B8BB-8FFCC2B1FA1F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820E49E2-A42E-F74B-B8BB-8FFCC2B1FA1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15102,7 +15076,7 @@
           <xdr:cNvPr id="198" name="Text Box 30">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B90D0E1-44A4-B12B-EB5C-6E16D82566ED}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B90D0E1-44A4-B12B-EB5C-6E16D82566ED}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15181,7 +15155,7 @@
           <xdr:cNvPr id="3426171" name="Line 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552E979C-83AC-5636-A824-B6D2D7721188}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552E979C-83AC-5636-A824-B6D2D7721188}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15220,7 +15194,7 @@
           <xdr:cNvPr id="3426172" name="Line 32">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B48FAFD4-AEA1-6C73-32B5-CEB20F041E23}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B48FAFD4-AEA1-6C73-32B5-CEB20F041E23}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15260,7 +15234,7 @@
           <xdr:cNvPr id="3426173" name="Line 33">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8050A2BB-1EE1-1EFF-49E3-075574C2FF72}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8050A2BB-1EE1-1EFF-49E3-075574C2FF72}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15300,7 +15274,7 @@
           <xdr:cNvPr id="3426174" name="Freeform 34">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA991A8D-FB0F-7361-25D3-B1A48A9B974B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA991A8D-FB0F-7361-25D3-B1A48A9B974B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15391,7 +15365,7 @@
           <xdr:cNvPr id="3426175" name="Freeform 35">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634D408A-C49D-9A36-7E4A-8ABE205CCBAE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634D408A-C49D-9A36-7E4A-8ABE205CCBAE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15499,7 +15473,7 @@
           <xdr:cNvPr id="3426176" name="Rectangle 36" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4BD6EAD-02BC-6816-4C4E-326260D20CC4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4BD6EAD-02BC-6816-4C4E-326260D20CC4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15535,7 +15509,7 @@
           <xdr:cNvPr id="3426177" name="Rectangle 37" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CD9FB71-8DE1-7BC0-B29E-76E1103314E4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CD9FB71-8DE1-7BC0-B29E-76E1103314E4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15571,7 +15545,7 @@
           <xdr:cNvPr id="3426178" name="Freeform 38">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC99814-8A74-CA8A-F037-1CC21532747E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC99814-8A74-CA8A-F037-1CC21532747E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15728,7 +15702,7 @@
           <xdr:cNvPr id="207" name="Text Box 39">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2E7B2F-32B8-45BE-EB96-0478783E3C62}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2E7B2F-32B8-45BE-EB96-0478783E3C62}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15807,7 +15781,7 @@
           <xdr:cNvPr id="3426180" name="Line 40">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E564B577-DC7B-72A7-B2F8-DB7C973EF291}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E564B577-DC7B-72A7-B2F8-DB7C973EF291}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15846,7 +15820,7 @@
           <xdr:cNvPr id="3426181" name="Line 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B4708D1-DB37-05E1-643F-28A77099B9DE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B4708D1-DB37-05E1-643F-28A77099B9DE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15885,7 +15859,7 @@
           <xdr:cNvPr id="3426182" name="Freeform 42">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0559A0DF-1060-E40E-B19A-5A6C420F5D67}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0559A0DF-1060-E40E-B19A-5A6C420F5D67}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -15971,7 +15945,7 @@
           <xdr:cNvPr id="3426183" name="Freeform 43" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3C0E6F-7415-983D-1BC0-C193AB96CDF0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3C0E6F-7415-983D-1BC0-C193AB96CDF0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16093,7 +16067,7 @@
           <xdr:cNvPr id="3426184" name="Line 44">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3F4C4CB-1766-0B7C-437E-B0D939554F7B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3F4C4CB-1766-0B7C-437E-B0D939554F7B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16133,7 +16107,7 @@
           <xdr:cNvPr id="3426185" name="Line 45">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B33E89C3-E960-CA31-5DDE-2415A19972DC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B33E89C3-E960-CA31-5DDE-2415A19972DC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16173,7 +16147,7 @@
           <xdr:cNvPr id="3426186" name="Freeform 46">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1860B16-0F15-019A-9E07-0AF42C9E0C08}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1860B16-0F15-019A-9E07-0AF42C9E0C08}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16294,7 +16268,7 @@
           <xdr:cNvPr id="3426187" name="Freeform 47">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{592860B5-2699-8E38-461C-247647098588}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{592860B5-2699-8E38-461C-247647098588}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16415,7 +16389,7 @@
           <xdr:cNvPr id="3426188" name="Oval 48" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7A06C5E-02EC-B394-6F1D-C4D1DFE6923E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7A06C5E-02EC-B394-6F1D-C4D1DFE6923E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16451,7 +16425,7 @@
           <xdr:cNvPr id="3426189" name="Oval 49">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80BC19A1-A2CF-AD2B-0444-894ABC258EDC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80BC19A1-A2CF-AD2B-0444-894ABC258EDC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16485,7 +16459,7 @@
           <xdr:cNvPr id="3426190" name="Line 50">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10882EC4-581F-E88B-38BE-FA600845ABBD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10882EC4-581F-E88B-38BE-FA600845ABBD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16524,7 +16498,7 @@
           <xdr:cNvPr id="3426191" name="Line 51">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{339EC3E4-A176-F1A4-E29F-BA56E57ABDA0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{339EC3E4-A176-F1A4-E29F-BA56E57ABDA0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16564,7 +16538,7 @@
           <xdr:cNvPr id="3426192" name="Freeform 52">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC904DD7-C682-E58A-D051-30D382C932ED}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC904DD7-C682-E58A-D051-30D382C932ED}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16655,7 +16629,7 @@
           <xdr:cNvPr id="3426193" name="Freeform 53">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2A25EAC-D696-01ED-4346-9087D773B9FD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2A25EAC-D696-01ED-4346-9087D773B9FD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16763,7 +16737,7 @@
           <xdr:cNvPr id="3426194" name="Rectangle 54" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F14B252-9101-390E-49BC-ADC0947FB40B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F14B252-9101-390E-49BC-ADC0947FB40B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16799,7 +16773,7 @@
           <xdr:cNvPr id="3426195" name="Line 55">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8996386E-7EB6-37D4-5578-51480BC33642}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8996386E-7EB6-37D4-5578-51480BC33642}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16839,7 +16813,7 @@
           <xdr:cNvPr id="3426196" name="Line 56">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{300A8D23-4513-FAD2-0FCE-D6E6379549CF}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{300A8D23-4513-FAD2-0FCE-D6E6379549CF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16879,7 +16853,7 @@
           <xdr:cNvPr id="3426197" name="Line 57">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5C2C53-41EE-EE56-0303-0218B3C25BC2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5C2C53-41EE-EE56-0303-0218B3C25BC2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16918,7 +16892,7 @@
           <xdr:cNvPr id="3426198" name="Line 58">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFA70F51-47CB-F84B-7259-B815641DB569}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFA70F51-47CB-F84B-7259-B815641DB569}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16957,7 +16931,7 @@
           <xdr:cNvPr id="3426199" name="Line 59">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A504A8E-CB45-69EB-8B11-F97CBF3E20E0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A504A8E-CB45-69EB-8B11-F97CBF3E20E0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -16997,7 +16971,7 @@
           <xdr:cNvPr id="3426200" name="Freeform 60" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABE9C3C7-4F02-46FF-294E-C9BD4D4D6C28}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABE9C3C7-4F02-46FF-294E-C9BD4D4D6C28}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17078,7 +17052,7 @@
           <xdr:cNvPr id="3426201" name="Oval 61" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8677084-9414-322A-86DA-D8056E1DB481}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8677084-9414-322A-86DA-D8056E1DB481}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17121,7 +17095,7 @@
           <xdr:cNvPr id="3426202" name="Freeform 62">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C8CEB54-5A1C-C8A5-4871-6C3BD85235C9}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C8CEB54-5A1C-C8A5-4871-6C3BD85235C9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17200,7 +17174,7 @@
           <xdr:cNvPr id="3426203" name="Line 63">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2D575F2-8B18-4E32-7CB0-06F55B9AF961}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2D575F2-8B18-4E32-7CB0-06F55B9AF961}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17239,7 +17213,7 @@
           <xdr:cNvPr id="3426204" name="Line 64">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D34BE1F-5462-0D3F-E019-A29CED2D69CB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D34BE1F-5462-0D3F-E019-A29CED2D69CB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17279,7 +17253,7 @@
           <xdr:cNvPr id="3426205" name="Line 65">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF3D8E12-F817-23A1-4B40-8E42EE9CA273}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF3D8E12-F817-23A1-4B40-8E42EE9CA273}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17319,7 +17293,7 @@
           <xdr:cNvPr id="3426206" name="Oval 66" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D783B4-CBC0-7462-9F92-12617D2F6C00}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D783B4-CBC0-7462-9F92-12617D2F6C00}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17355,7 +17329,7 @@
           <xdr:cNvPr id="3426207" name="Oval 67">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B7F7F6E-2898-3B4B-0070-14F0522F8D36}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B7F7F6E-2898-3B4B-0070-14F0522F8D36}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17389,7 +17363,7 @@
           <xdr:cNvPr id="3426208" name="Line 68">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A0FE706-1FE1-811F-EEE9-259CE9A1957A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A0FE706-1FE1-811F-EEE9-259CE9A1957A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17428,7 +17402,7 @@
           <xdr:cNvPr id="3426209" name="Line 69">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71459369-8327-DF22-B87B-52187EBD146D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71459369-8327-DF22-B87B-52187EBD146D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17468,7 +17442,7 @@
           <xdr:cNvPr id="3426210" name="Freeform 70">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF7F07F3-816B-47C4-187F-E5DD65030C67}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF7F07F3-816B-47C4-187F-E5DD65030C67}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17559,7 +17533,7 @@
           <xdr:cNvPr id="3426211" name="Freeform 71">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E8B2A10-1896-09EF-3B5C-83E9580D53D7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E8B2A10-1896-09EF-3B5C-83E9580D53D7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17667,7 +17641,7 @@
           <xdr:cNvPr id="3426212" name="Rectangle 72" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBF30957-20D8-E176-8CC4-131F51136BDE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBF30957-20D8-E176-8CC4-131F51136BDE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17703,7 +17677,7 @@
           <xdr:cNvPr id="3426213" name="Line 73">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DE060E-4059-C3C2-8105-9B1389B2CDA5}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DE060E-4059-C3C2-8105-9B1389B2CDA5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17743,7 +17717,7 @@
           <xdr:cNvPr id="3426214" name="Line 74">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B444B81E-6878-4C96-A8D7-64715F1D9B64}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B444B81E-6878-4C96-A8D7-64715F1D9B64}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17783,7 +17757,7 @@
           <xdr:cNvPr id="3426215" name="Line 75">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F9AB64B-AF9A-AEC4-4E57-9430909D642E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F9AB64B-AF9A-AEC4-4E57-9430909D642E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17822,7 +17796,7 @@
           <xdr:cNvPr id="3426216" name="Line 76">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F93C76-0E44-E9F9-2245-68DED5AC6E1B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F93C76-0E44-E9F9-2245-68DED5AC6E1B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17862,7 +17836,7 @@
           <xdr:cNvPr id="3426217" name="Freeform 77" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E4CECF-AF58-6EFA-E680-DF1D596B706B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E4CECF-AF58-6EFA-E680-DF1D596B706B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17943,7 +17917,7 @@
           <xdr:cNvPr id="3426218" name="Oval 78" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E729013D-7100-3A84-0BB2-77B7C0E3EBBC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E729013D-7100-3A84-0BB2-77B7C0E3EBBC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -17986,7 +17960,7 @@
           <xdr:cNvPr id="3426219" name="Freeform 79">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDEECB7-4403-8FB9-D388-20C3AC032D4E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDEECB7-4403-8FB9-D388-20C3AC032D4E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18065,7 +18039,7 @@
           <xdr:cNvPr id="3426220" name="Line 80">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDE77B8D-8142-E5B2-74BA-85BC6A425D68}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDE77B8D-8142-E5B2-74BA-85BC6A425D68}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18104,7 +18078,7 @@
           <xdr:cNvPr id="3426221" name="Line 81">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2493C94-E508-22E5-222A-BAA9F556FAA4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2493C94-E508-22E5-222A-BAA9F556FAA4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18144,7 +18118,7 @@
           <xdr:cNvPr id="3426222" name="Line 82">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF11FAA-1F44-9B14-DEE7-582334C50D87}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF11FAA-1F44-9B14-DEE7-582334C50D87}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18200,7 +18174,7 @@
         <xdr:cNvPr id="3426065" name="Group 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{876EDBA7-CB63-3146-2069-5DFB00917133}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{876EDBA7-CB63-3146-2069-5DFB00917133}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18210,8 +18184,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1318260" y="5867400"/>
-          <a:ext cx="4648200" cy="1120140"/>
+          <a:off x="1461135" y="5972175"/>
+          <a:ext cx="5187315" cy="1131570"/>
           <a:chOff x="150" y="536"/>
           <a:chExt cx="540" cy="120"/>
         </a:xfrm>
@@ -18221,7 +18195,7 @@
           <xdr:cNvPr id="3426069" name="Rectangle 84" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A73DB8B-B7D3-0F26-AC56-58505E932806}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A73DB8B-B7D3-0F26-AC56-58505E932806}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18257,7 +18231,7 @@
           <xdr:cNvPr id="3426070" name="Freeform 85">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22A24246-BE5C-34F1-448A-A1B87549D0F2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22A24246-BE5C-34F1-448A-A1B87549D0F2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18378,7 +18352,7 @@
           <xdr:cNvPr id="254" name="Text Box 86">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{059527C1-B45A-707C-8EE5-F4205DC5361B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{059527C1-B45A-707C-8EE5-F4205DC5361B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18427,7 +18401,7 @@
           <xdr:cNvPr id="3426072" name="Line 87">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C5247D-7CCF-9CE5-79CA-B0D66FBBD884}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C5247D-7CCF-9CE5-79CA-B0D66FBBD884}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18466,7 +18440,7 @@
           <xdr:cNvPr id="3426073" name="Line 88">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF15BCF-FFA1-B751-B073-B978F25F7457}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF15BCF-FFA1-B751-B073-B978F25F7457}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18506,7 +18480,7 @@
           <xdr:cNvPr id="3426074" name="Line 89">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D87E2B0C-E1E8-8042-B0BC-A3DC98A76D25}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D87E2B0C-E1E8-8042-B0BC-A3DC98A76D25}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18546,7 +18520,7 @@
           <xdr:cNvPr id="3426075" name="Line 90">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CDD4ACE-D1BD-9318-A4DE-24D31608EC8D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CDD4ACE-D1BD-9318-A4DE-24D31608EC8D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18585,7 +18559,7 @@
           <xdr:cNvPr id="259" name="Text Box 91">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6FE8C91-A745-137E-3C6F-7B0C5D58003F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6FE8C91-A745-137E-3C6F-7B0C5D58003F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18634,7 +18608,7 @@
           <xdr:cNvPr id="260" name="Text Box 92">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3A0D67A-0C2D-25E9-A45B-3548A6FBEF2A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3A0D67A-0C2D-25E9-A45B-3548A6FBEF2A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18683,7 +18657,7 @@
           <xdr:cNvPr id="3426078" name="Oval 93" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8D2BF0-80A3-4101-EF33-1CC70AD0E2D0}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8D2BF0-80A3-4101-EF33-1CC70AD0E2D0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18719,7 +18693,7 @@
           <xdr:cNvPr id="3426079" name="Oval 94">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51273C5B-51B6-D41D-D5F3-D0C56F4428BB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51273C5B-51B6-D41D-D5F3-D0C56F4428BB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18753,7 +18727,7 @@
           <xdr:cNvPr id="263" name="Text Box 95">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C181CF8-3F03-E011-C5BC-A155E767C534}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C181CF8-3F03-E011-C5BC-A155E767C534}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18820,7 +18794,7 @@
           <xdr:cNvPr id="3426081" name="Line 96">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFC68C92-1009-8315-DC8A-E87B2D15DF6E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFC68C92-1009-8315-DC8A-E87B2D15DF6E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18859,7 +18833,7 @@
           <xdr:cNvPr id="3426082" name="Line 97">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65918EFA-1B81-32D7-3379-1F35FA49B029}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65918EFA-1B81-32D7-3379-1F35FA49B029}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18898,7 +18872,7 @@
           <xdr:cNvPr id="3426083" name="Line 98">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5034D995-9EA8-F456-3F64-CDD98E08045B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5034D995-9EA8-F456-3F64-CDD98E08045B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18937,7 +18911,7 @@
           <xdr:cNvPr id="3426084" name="Line 99">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7879408F-738E-EE3D-ACDA-17E38FB4FBF1}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7879408F-738E-EE3D-ACDA-17E38FB4FBF1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -18976,7 +18950,7 @@
           <xdr:cNvPr id="3426085" name="Arc 100">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1998B37-8C11-CAE3-4078-F1C41C670963}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1998B37-8C11-CAE3-4078-F1C41C670963}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19074,7 +19048,7 @@
           <xdr:cNvPr id="3426086" name="Arc 101">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4441C2C-193E-0B53-C84C-8F5F47467F6B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4441C2C-193E-0B53-C84C-8F5F47467F6B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19172,7 +19146,7 @@
           <xdr:cNvPr id="3426087" name="Arc 102">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40494613-FBE6-65CC-6142-2A0FB9E2CA13}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40494613-FBE6-65CC-6142-2A0FB9E2CA13}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19270,7 +19244,7 @@
           <xdr:cNvPr id="3426088" name="Arc 103">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B511D19-F1BD-F252-350E-0EC112881806}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B511D19-F1BD-F252-350E-0EC112881806}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19368,7 +19342,7 @@
           <xdr:cNvPr id="3426089" name="Freeform 104">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08EC917E-1A55-DF5E-4865-3107E4F685AC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08EC917E-1A55-DF5E-4865-3107E4F685AC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19459,7 +19433,7 @@
           <xdr:cNvPr id="3426090" name="Freeform 105">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{306D10FE-4DF9-2321-A7EE-6E85ADF94D7C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{306D10FE-4DF9-2321-A7EE-6E85ADF94D7C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19567,7 +19541,7 @@
           <xdr:cNvPr id="3426091" name="Rectangle 106" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F9AE31-1BA0-8E51-7C7C-479636464185}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F9AE31-1BA0-8E51-7C7C-479636464185}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19603,7 +19577,7 @@
           <xdr:cNvPr id="3426092" name="Rectangle 107" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B5D84A-EC95-881E-B451-AA18082C1A58}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B5D84A-EC95-881E-B451-AA18082C1A58}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19639,7 +19613,7 @@
           <xdr:cNvPr id="3426093" name="Line 108">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B788542-D4CF-150B-72D2-1E4B72713C58}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B788542-D4CF-150B-72D2-1E4B72713C58}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19678,7 +19652,7 @@
           <xdr:cNvPr id="3426094" name="Freeform 109">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535DD355-B86B-5FF9-0987-482AC9712AB5}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535DD355-B86B-5FF9-0987-482AC9712AB5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19764,7 +19738,7 @@
           <xdr:cNvPr id="3426095" name="Freeform 110" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A410C5FA-9345-1EE6-BC3F-FC13FB69809E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A410C5FA-9345-1EE6-BC3F-FC13FB69809E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19868,7 +19842,7 @@
           <xdr:cNvPr id="3426096" name="Line 111">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B324D3-9C33-016D-1670-AFF8AE5DB30D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B324D3-9C33-016D-1670-AFF8AE5DB30D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19908,7 +19882,7 @@
           <xdr:cNvPr id="3426097" name="Line 112">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD825C9E-7B34-061A-339D-E4DF60619D90}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD825C9E-7B34-061A-339D-E4DF60619D90}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -19948,7 +19922,7 @@
           <xdr:cNvPr id="3426098" name="Freeform 113">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D18D2DFF-0091-4479-D300-AF4140499F36}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D18D2DFF-0091-4479-D300-AF4140499F36}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20194,7 +20168,7 @@
           <xdr:cNvPr id="282" name="Text Box 114">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C421DD3-CA25-0095-15CB-A5642321F95A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C421DD3-CA25-0095-15CB-A5642321F95A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20261,7 +20235,7 @@
           <xdr:cNvPr id="3426100" name="Line 115">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2614C6F7-2B78-87C8-18F4-C24F5FED4984}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2614C6F7-2B78-87C8-18F4-C24F5FED4984}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20300,7 +20274,7 @@
           <xdr:cNvPr id="3426101" name="Line 116">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A23C59-9221-787C-AF19-5DF7F58BCDFE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A23C59-9221-787C-AF19-5DF7F58BCDFE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20340,7 +20314,7 @@
           <xdr:cNvPr id="3426102" name="Line 117">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{627DB02D-00AC-3F70-9E6C-99DB663C92BB}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{627DB02D-00AC-3F70-9E6C-99DB663C92BB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20380,7 +20354,7 @@
           <xdr:cNvPr id="3426103" name="Oval 118" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E489024-016D-55DB-175B-03630F816FAD}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E489024-016D-55DB-175B-03630F816FAD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20416,7 +20390,7 @@
           <xdr:cNvPr id="3426104" name="Oval 119">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B63D80-9E0C-9637-73E1-6D3755148692}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B63D80-9E0C-9637-73E1-6D3755148692}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20450,7 +20424,7 @@
           <xdr:cNvPr id="3426105" name="Freeform 120">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C60DDD-ED85-9623-9F55-BED48EA32313}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C60DDD-ED85-9623-9F55-BED48EA32313}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20536,7 +20510,7 @@
           <xdr:cNvPr id="3426106" name="Line 121">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46CFF6F4-E2E4-A5D6-96D5-17FE14307DDE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46CFF6F4-E2E4-A5D6-96D5-17FE14307DDE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20575,7 +20549,7 @@
           <xdr:cNvPr id="3426107" name="Line 122">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B34EEE1-3E4C-4DB1-6F27-3239E35A7FFE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B34EEE1-3E4C-4DB1-6F27-3239E35A7FFE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20615,7 +20589,7 @@
           <xdr:cNvPr id="3426108" name="Line 123">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D134361-BD1D-66A9-9FAA-AD0983DA0F94}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D134361-BD1D-66A9-9FAA-AD0983DA0F94}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20655,7 +20629,7 @@
           <xdr:cNvPr id="292" name="Text Box 124">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFD738E2-345B-5389-7A73-44DCDFA949DA}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFD738E2-345B-5389-7A73-44DCDFA949DA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20716,7 +20690,7 @@
           <xdr:cNvPr id="293" name="Text Box 125">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A2069A3-627D-124B-6719-054783EE0EFC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A2069A3-627D-124B-6719-054783EE0EFC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20783,7 +20757,7 @@
           <xdr:cNvPr id="3426111" name="Freeform 126">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC7B2CAD-27DD-EFB9-4DBB-3E19B5FC7F10}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC7B2CAD-27DD-EFB9-4DBB-3E19B5FC7F10}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20874,7 +20848,7 @@
           <xdr:cNvPr id="3426112" name="Freeform 127">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31354BD8-EC6C-843B-5F9A-85DF6EB6BC31}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31354BD8-EC6C-843B-5F9A-85DF6EB6BC31}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -20982,7 +20956,7 @@
           <xdr:cNvPr id="3426113" name="Rectangle 128" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEFA94DC-6CEA-039D-42B3-430B4DE49D98}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEFA94DC-6CEA-039D-42B3-430B4DE49D98}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21018,7 +20992,7 @@
           <xdr:cNvPr id="3426114" name="Rectangle 129" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5405F755-1983-A412-6D7B-8EA610FBE64E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5405F755-1983-A412-6D7B-8EA610FBE64E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21054,7 +21028,7 @@
           <xdr:cNvPr id="3426115" name="Freeform 130">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39AB44B5-7329-FE1D-2136-74649672D3B6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39AB44B5-7329-FE1D-2136-74649672D3B6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21140,7 +21114,7 @@
           <xdr:cNvPr id="3426116" name="Freeform 131" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{960E3166-B228-7D30-BEBC-FF8B60F51DD8}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{960E3166-B228-7D30-BEBC-FF8B60F51DD8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21244,7 +21218,7 @@
           <xdr:cNvPr id="3426117" name="Line 132">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21151EFD-1A21-209A-2178-ED611F1F87F6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21151EFD-1A21-209A-2178-ED611F1F87F6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21284,7 +21258,7 @@
           <xdr:cNvPr id="3426118" name="Line 133">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF13E9-330D-16DB-E14C-474F8C330F2A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AF13E9-330D-16DB-E14C-474F8C330F2A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21324,7 +21298,7 @@
           <xdr:cNvPr id="3426119" name="Freeform 134">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5538123E-B653-ABDF-6B10-8FC9C47521A2}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5538123E-B653-ABDF-6B10-8FC9C47521A2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21570,7 +21544,7 @@
           <xdr:cNvPr id="303" name="Text Box 135">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401D0606-9C96-5634-B5C5-EF830454E849}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401D0606-9C96-5634-B5C5-EF830454E849}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21637,7 +21611,7 @@
           <xdr:cNvPr id="3426121" name="Freeform 136">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FF04289-CAC4-57A5-C81B-7A54EE1A34A4}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FF04289-CAC4-57A5-C81B-7A54EE1A34A4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21758,7 +21732,7 @@
           <xdr:cNvPr id="3426122" name="Freeform 137">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0B7100-43CC-6262-BA59-1CFFED50FADA}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0B7100-43CC-6262-BA59-1CFFED50FADA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21879,7 +21853,7 @@
           <xdr:cNvPr id="3426123" name="Line 138">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB1F00B3-3D2A-F225-C553-75AE883FF51E}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB1F00B3-3D2A-F225-C553-75AE883FF51E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21918,7 +21892,7 @@
           <xdr:cNvPr id="3426124" name="Line 139">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FF28ACD-D9C6-A9F7-BD03-C3E47E077FA3}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FF28ACD-D9C6-A9F7-BD03-C3E47E077FA3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21958,7 +21932,7 @@
           <xdr:cNvPr id="3426125" name="Line 140">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207CA2E1-86D4-3AFE-7EFC-2E3932AA6276}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207CA2E1-86D4-3AFE-7EFC-2E3932AA6276}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -21998,7 +21972,7 @@
           <xdr:cNvPr id="3426126" name="Line 141">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1537142-2B38-83F7-E97A-D34931C91631}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1537142-2B38-83F7-E97A-D34931C91631}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22037,7 +22011,7 @@
           <xdr:cNvPr id="3426127" name="Oval 142" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DF405C-BAFF-55D5-62EF-637AE2F8584B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DF405C-BAFF-55D5-62EF-637AE2F8584B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22073,7 +22047,7 @@
           <xdr:cNvPr id="3426128" name="Oval 143">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDC49F74-1FCF-DECD-EEAE-440A0BA255AE}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDC49F74-1FCF-DECD-EEAE-440A0BA255AE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22107,7 +22081,7 @@
           <xdr:cNvPr id="3426129" name="Line 144">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E968BC8A-BE85-0C1E-04A7-246D9C535FD6}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E968BC8A-BE85-0C1E-04A7-246D9C535FD6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22146,7 +22120,7 @@
           <xdr:cNvPr id="3426130" name="Line 145">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED207D2E-5615-FBBC-7913-7FEF56FA5147}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED207D2E-5615-FBBC-7913-7FEF56FA5147}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22186,7 +22160,7 @@
           <xdr:cNvPr id="3426131" name="Freeform 146">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDD6E5C-FC0F-C567-9769-4ADF3AE3609C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDD6E5C-FC0F-C567-9769-4ADF3AE3609C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22277,7 +22251,7 @@
           <xdr:cNvPr id="3426132" name="Freeform 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D3BD76-7C46-1906-8DF8-7739B9D657DC}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D3BD76-7C46-1906-8DF8-7739B9D657DC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22385,7 +22359,7 @@
           <xdr:cNvPr id="3426133" name="Rectangle 148" descr="밝은 수평선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3CCB519-AA81-63DB-5444-AFA33448C52B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3CCB519-AA81-63DB-5444-AFA33448C52B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22421,7 +22395,7 @@
           <xdr:cNvPr id="3426134" name="Rectangle 149" descr="밝은 상향 대각선">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D23CB8C-5653-B4EB-E646-778DBAF247A3}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D23CB8C-5653-B4EB-E646-778DBAF247A3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22457,7 +22431,7 @@
           <xdr:cNvPr id="3426135" name="Freeform 150">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{069F2632-5E3B-7BAA-5D5F-BDF970BAC81D}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{069F2632-5E3B-7BAA-5D5F-BDF970BAC81D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22543,7 +22517,7 @@
           <xdr:cNvPr id="3426136" name="Freeform 151" descr="25%">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D8428C-897C-2734-E221-0CF6E1B08C80}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D8428C-897C-2734-E221-0CF6E1B08C80}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22647,7 +22621,7 @@
           <xdr:cNvPr id="3426137" name="Line 152">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0285CFF0-4FA4-B965-F6D2-F7063E28BF71}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0285CFF0-4FA4-B965-F6D2-F7063E28BF71}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22687,7 +22661,7 @@
           <xdr:cNvPr id="3426138" name="Line 153">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D62A3B-A8ED-AECE-5D9F-8FB03769E7E7}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D62A3B-A8ED-AECE-5D9F-8FB03769E7E7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22727,7 +22701,7 @@
           <xdr:cNvPr id="3426139" name="Freeform 154">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16365616-9894-8064-2B07-35BBFAB6922F}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16365616-9894-8064-2B07-35BBFAB6922F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -22973,7 +22947,7 @@
           <xdr:cNvPr id="3426140" name="Freeform 155">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23D4359-C1C2-A571-A977-0DB6779C552B}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23D4359-C1C2-A571-A977-0DB6779C552B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23094,7 +23068,7 @@
           <xdr:cNvPr id="3426141" name="Line 156">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1480A8F4-CB5E-3CC6-0DD7-D6EBE3AC49AF}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1480A8F4-CB5E-3CC6-0DD7-D6EBE3AC49AF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23133,7 +23107,7 @@
           <xdr:cNvPr id="3426142" name="Freeform 157">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C42FCD57-36C8-EDBE-C16D-E69E3EC5732A}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C42FCD57-36C8-EDBE-C16D-E69E3EC5732A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23219,7 +23193,7 @@
           <xdr:cNvPr id="3426143" name="Line 158">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51F9A7FA-7DF9-97A6-51DF-570D0F3D6C45}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51F9A7FA-7DF9-97A6-51DF-570D0F3D6C45}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23259,7 +23233,7 @@
           <xdr:cNvPr id="327" name="Text Box 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90002F1-50FE-4EB8-4B2B-22658A06706C}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90002F1-50FE-4EB8-4B2B-22658A06706C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23320,7 +23294,7 @@
           <xdr:cNvPr id="3426145" name="Line 160">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B71913B-4F67-2599-63F9-8F75B4DD0A10}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B71913B-4F67-2599-63F9-8F75B4DD0A10}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23359,7 +23333,7 @@
           <xdr:cNvPr id="3426146" name="Line 161">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79513DC5-7EC0-15F0-E660-0E6D43F2A140}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79513DC5-7EC0-15F0-E660-0E6D43F2A140}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23399,7 +23373,7 @@
           <xdr:cNvPr id="3426147" name="Line 162">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C44CC300-4B47-396E-09AD-AA33F7319503}"/>
+                <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C44CC300-4B47-396E-09AD-AA33F7319503}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -23455,7 +23429,7 @@
         <xdr:cNvPr id="3426066" name="Picture 444">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BCF11A-2599-36A1-E12E-DCCBAE7F2E9B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BCF11A-2599-36A1-E12E-DCCBAE7F2E9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23540,7 +23514,7 @@
         <xdr:cNvPr id="3426067" name="_x298645232" descr="EMB000059a8045b">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E06BB8-CF7F-4ACA-0F9E-9B78AFF46CDF}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E06BB8-CF7F-4ACA-0F9E-9B78AFF46CDF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23624,7 +23598,7 @@
         <xdr:cNvPr id="8" name="그림 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23648,6 +23622,61 @@
         <a:xfrm>
           <a:off x="68579" y="744854"/>
           <a:ext cx="923925" cy="574698"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1009650</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>94638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="85725" y="752475"/>
+          <a:ext cx="923925" cy="580413"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -24006,37 +24035,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P352"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="27.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="27.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="0.59765625" style="122" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="124" customWidth="1"/>
-    <col min="3" max="3" width="1.796875" style="122" customWidth="1"/>
-    <col min="4" max="4" width="6.19921875" style="123" customWidth="1"/>
-    <col min="5" max="5" width="1.796875" style="122" customWidth="1"/>
-    <col min="6" max="6" width="5.796875" style="123" customWidth="1"/>
-    <col min="7" max="7" width="1.796875" style="122" customWidth="1"/>
-    <col min="8" max="8" width="8.8984375" style="123"/>
+    <col min="1" max="1" width="0.5546875" style="122" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="124" customWidth="1"/>
+    <col min="3" max="3" width="1.77734375" style="122" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="123" customWidth="1"/>
+    <col min="5" max="5" width="1.77734375" style="122" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" style="123" customWidth="1"/>
+    <col min="7" max="7" width="1.77734375" style="122" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="123"/>
     <col min="9" max="9" width="1" style="123" customWidth="1"/>
-    <col min="10" max="10" width="0.69921875" style="125" customWidth="1"/>
-    <col min="11" max="11" width="12.69921875" style="124" customWidth="1"/>
-    <col min="12" max="12" width="8.09765625" style="123" customWidth="1"/>
-    <col min="13" max="13" width="1.796875" style="122" customWidth="1"/>
-    <col min="14" max="14" width="7.69921875" style="123" customWidth="1"/>
-    <col min="15" max="15" width="1.796875" style="122" customWidth="1"/>
-    <col min="16" max="16" width="9.59765625" style="123" customWidth="1"/>
-    <col min="17" max="17" width="5.796875" style="122" customWidth="1"/>
-    <col min="18" max="18" width="5.19921875" style="122" customWidth="1"/>
-    <col min="19" max="19" width="8.8984375" style="122"/>
-    <col min="20" max="20" width="4.69921875" style="122" customWidth="1"/>
-    <col min="21" max="16384" width="8.8984375" style="122"/>
+    <col min="10" max="10" width="0.6640625" style="125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="124" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" style="123" customWidth="1"/>
+    <col min="13" max="13" width="1.77734375" style="122" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" style="123" customWidth="1"/>
+    <col min="15" max="15" width="1.77734375" style="122" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" style="123" customWidth="1"/>
+    <col min="17" max="17" width="5.77734375" style="122" customWidth="1"/>
+    <col min="18" max="18" width="5.21875" style="122" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="122"/>
+    <col min="20" max="20" width="4.6640625" style="122" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="122"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21.75" customHeight="1">
       <c r="A1" s="205" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="206"/>
       <c r="C1" s="206"/>
@@ -24056,7 +24085,7 @@
     </row>
     <row r="2" spans="1:16" ht="18.75" customHeight="1">
       <c r="A2" s="205" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="206"/>
       <c r="C2" s="206"/>
@@ -24089,7 +24118,7 @@
       <c r="L3" s="161"/>
       <c r="M3" s="161"/>
       <c r="N3" s="215" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="O3" s="216"/>
       <c r="P3" s="216"/>
@@ -24098,7 +24127,7 @@
       <c r="A4" s="160"/>
       <c r="B4" s="159"/>
       <c r="C4" s="217" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" s="218"/>
       <c r="E4" s="218"/>
@@ -24108,21 +24137,21 @@
       <c r="I4" s="218"/>
       <c r="J4" s="218"/>
       <c r="K4" s="219"/>
-      <c r="L4" s="258" t="s">
-        <v>76</v>
-      </c>
-      <c r="M4" s="259"/>
-      <c r="N4" s="260" t="s">
-        <v>211</v>
-      </c>
-      <c r="O4" s="261"/>
-      <c r="P4" s="262"/>
+      <c r="L4" s="259" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="260"/>
+      <c r="N4" s="261" t="s">
+        <v>208</v>
+      </c>
+      <c r="O4" s="262"/>
+      <c r="P4" s="263"/>
     </row>
     <row r="5" spans="1:16" ht="12.75" customHeight="1">
       <c r="A5" s="160"/>
       <c r="B5" s="159"/>
       <c r="C5" s="220" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="220"/>
       <c r="E5" s="220"/>
@@ -24133,18 +24162,18 @@
       <c r="J5" s="220"/>
       <c r="K5" s="221"/>
       <c r="L5" s="228" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M5" s="229"/>
-      <c r="N5" s="263"/>
-      <c r="O5" s="264"/>
-      <c r="P5" s="265"/>
+      <c r="N5" s="264"/>
+      <c r="O5" s="265"/>
+      <c r="P5" s="266"/>
     </row>
     <row r="6" spans="1:16" ht="12.75" customHeight="1">
       <c r="A6" s="160"/>
       <c r="B6" s="159"/>
       <c r="C6" s="222" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D6" s="222"/>
       <c r="E6" s="222"/>
@@ -24155,20 +24184,20 @@
       <c r="J6" s="222"/>
       <c r="K6" s="223"/>
       <c r="L6" s="203" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M6" s="204"/>
-      <c r="N6" s="252" t="s">
-        <v>221</v>
-      </c>
-      <c r="O6" s="253"/>
-      <c r="P6" s="254"/>
+      <c r="N6" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="O6" s="254"/>
+      <c r="P6" s="255"/>
     </row>
     <row r="7" spans="1:16" ht="12.75" customHeight="1">
       <c r="A7" s="158"/>
       <c r="B7" s="157"/>
       <c r="C7" s="201" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" s="201"/>
       <c r="E7" s="201"/>
@@ -24178,122 +24207,122 @@
       <c r="I7" s="201"/>
       <c r="J7" s="201"/>
       <c r="K7" s="202"/>
-      <c r="L7" s="250" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7" s="251"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="256"/>
-      <c r="P7" s="257"/>
+      <c r="L7" s="251" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="252"/>
+      <c r="N7" s="256"/>
+      <c r="O7" s="257"/>
+      <c r="P7" s="258"/>
     </row>
     <row r="8" spans="1:16" s="145" customFormat="1" ht="24" customHeight="1">
       <c r="A8" s="156"/>
       <c r="B8" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="266" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="267"/>
-      <c r="E8" s="267"/>
-      <c r="F8" s="267"/>
-      <c r="G8" s="267"/>
-      <c r="H8" s="267"/>
-      <c r="I8" s="268"/>
+        <v>79</v>
+      </c>
+      <c r="C8" s="267" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="268"/>
+      <c r="E8" s="268"/>
+      <c r="F8" s="268"/>
+      <c r="G8" s="268"/>
+      <c r="H8" s="268"/>
+      <c r="I8" s="269"/>
       <c r="J8" s="51"/>
       <c r="K8" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="L8" s="269" t="s">
-        <v>234</v>
-      </c>
-      <c r="M8" s="270"/>
-      <c r="N8" s="270"/>
-      <c r="O8" s="270"/>
-      <c r="P8" s="271"/>
+        <v>193</v>
+      </c>
+      <c r="L8" s="270" t="s">
+        <v>227</v>
+      </c>
+      <c r="M8" s="271"/>
+      <c r="N8" s="271"/>
+      <c r="O8" s="271"/>
+      <c r="P8" s="272"/>
     </row>
     <row r="9" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A9" s="146"/>
       <c r="B9" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="230" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="312"/>
-      <c r="E9" s="312"/>
-      <c r="F9" s="312"/>
-      <c r="G9" s="312"/>
-      <c r="H9" s="312"/>
-      <c r="I9" s="313"/>
+        <v>211</v>
+      </c>
+      <c r="D9" s="313"/>
+      <c r="E9" s="313"/>
+      <c r="F9" s="313"/>
+      <c r="G9" s="313"/>
+      <c r="H9" s="313"/>
+      <c r="I9" s="314"/>
       <c r="J9" s="53"/>
       <c r="K9" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="302" t="s">
+        <v>217</v>
+      </c>
+      <c r="M9" s="303"/>
+      <c r="N9" s="303"/>
+      <c r="O9" s="303"/>
+      <c r="P9" s="54" t="s">
         <v>82</v>
-      </c>
-      <c r="L9" s="301" t="s">
-        <v>222</v>
-      </c>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="302"/>
-      <c r="P9" s="54" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A10" s="146"/>
       <c r="B10" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="314"/>
-      <c r="D10" s="315"/>
-      <c r="E10" s="315"/>
-      <c r="F10" s="315"/>
-      <c r="G10" s="315"/>
-      <c r="H10" s="315"/>
-      <c r="I10" s="316"/>
+        <v>83</v>
+      </c>
+      <c r="C10" s="315"/>
+      <c r="D10" s="316"/>
+      <c r="E10" s="316"/>
+      <c r="F10" s="316"/>
+      <c r="G10" s="316"/>
+      <c r="H10" s="316"/>
+      <c r="I10" s="317"/>
       <c r="J10" s="56"/>
       <c r="K10" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="303"/>
-      <c r="M10" s="304"/>
-      <c r="N10" s="304"/>
-      <c r="O10" s="304"/>
+        <v>84</v>
+      </c>
+      <c r="L10" s="304"/>
+      <c r="M10" s="305"/>
+      <c r="N10" s="305"/>
+      <c r="O10" s="305"/>
       <c r="P10" s="57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A11" s="154"/>
       <c r="B11" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="90" t="s">
+      <c r="D11" s="52" t="s">
         <v>87</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>88</v>
       </c>
       <c r="E11" s="52" t="s">
         <v>0</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="52" t="s">
         <v>0</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I11" s="60"/>
       <c r="J11" s="53"/>
       <c r="K11" s="182" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L11" s="198" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M11" s="199"/>
       <c r="N11" s="199"/>
@@ -24303,211 +24332,211 @@
     <row r="12" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A12" s="155"/>
       <c r="B12" s="62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" s="114"/>
       <c r="D12" s="62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="62"/>
       <c r="F12" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I12" s="65"/>
       <c r="J12" s="49"/>
       <c r="K12" s="183" t="s">
-        <v>230</v>
-      </c>
-      <c r="L12" s="274" t="s">
-        <v>231</v>
-      </c>
-      <c r="M12" s="275"/>
-      <c r="N12" s="275"/>
-      <c r="O12" s="275"/>
-      <c r="P12" s="276"/>
+        <v>224</v>
+      </c>
+      <c r="L12" s="275" t="s">
+        <v>225</v>
+      </c>
+      <c r="M12" s="276"/>
+      <c r="N12" s="276"/>
+      <c r="O12" s="276"/>
+      <c r="P12" s="277"/>
     </row>
     <row r="13" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A13" s="154"/>
       <c r="B13" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>0</v>
       </c>
       <c r="D13" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="52" t="s">
         <v>97</v>
-      </c>
-      <c r="E13" s="90" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>98</v>
       </c>
       <c r="G13" s="52" t="s">
         <v>0</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I13" s="60"/>
       <c r="J13" s="53"/>
       <c r="K13" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="L13" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="L13" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="M13" s="327" t="s">
-        <v>204</v>
-      </c>
-      <c r="N13" s="327"/>
+      <c r="M13" s="328" t="s">
+        <v>201</v>
+      </c>
+      <c r="N13" s="328"/>
       <c r="O13" s="52" t="s">
         <v>0</v>
       </c>
       <c r="P13" s="68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A14" s="146"/>
       <c r="B14" s="55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C14" s="85"/>
       <c r="D14" s="55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E14" s="69"/>
       <c r="F14" s="55" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G14" s="55"/>
       <c r="H14" s="55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I14" s="70"/>
       <c r="J14" s="56"/>
       <c r="K14" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="L14" s="71" t="s">
+      <c r="M14" s="329">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="N14" s="329"/>
+      <c r="O14" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="M14" s="328">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="N14" s="328"/>
-      <c r="O14" s="62" t="s">
+      <c r="P14" s="72" t="s">
         <v>108</v>
-      </c>
-      <c r="P14" s="72" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A15" s="146"/>
       <c r="B15" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="318" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="90" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="317" t="s">
+      <c r="E15" s="326"/>
+      <c r="F15" s="326"/>
+      <c r="G15" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="318" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="325"/>
-      <c r="F15" s="325"/>
-      <c r="G15" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="317" t="s">
-        <v>112</v>
-      </c>
-      <c r="I15" s="318"/>
+      <c r="I15" s="319"/>
       <c r="J15" s="53"/>
       <c r="K15" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="L15" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="M15" s="305">
+      <c r="M15" s="306">
         <v>1.2</v>
       </c>
-      <c r="N15" s="306"/>
+      <c r="N15" s="307"/>
       <c r="O15" s="52" t="s">
         <v>0</v>
       </c>
       <c r="P15" s="68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="145" customFormat="1" ht="13.5" customHeight="1">
       <c r="A16" s="146"/>
       <c r="B16" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="114" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="288" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="114" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="287" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
+      <c r="E16" s="283"/>
+      <c r="F16" s="283"/>
       <c r="G16" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="H16" s="287" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="319"/>
+      <c r="H16" s="288" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="320"/>
       <c r="J16" s="49"/>
       <c r="K16" s="62" t="s">
+        <v>117</v>
+      </c>
+      <c r="L16" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="L16" s="66" t="s">
-        <v>119</v>
-      </c>
-      <c r="M16" s="247"/>
-      <c r="N16" s="326"/>
+      <c r="M16" s="248"/>
+      <c r="N16" s="327"/>
       <c r="O16" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="P16" s="67" t="s">
         <v>108</v>
-      </c>
-      <c r="P16" s="67" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="145" customFormat="1" ht="12.75" customHeight="1">
       <c r="A17" s="146"/>
       <c r="B17" s="52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="90" t="s">
         <v>0</v>
       </c>
       <c r="D17" s="73" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" s="59"/>
       <c r="F17" s="73"/>
       <c r="G17" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H17" s="73" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I17" s="75"/>
       <c r="J17" s="53"/>
       <c r="K17" s="52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L17" s="234" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M17" s="231"/>
       <c r="N17" s="231"/>
@@ -24517,133 +24546,133 @@
     <row r="18" spans="1:16" s="145" customFormat="1" ht="12.75" customHeight="1">
       <c r="A18" s="146"/>
       <c r="B18" s="55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C18" s="66"/>
       <c r="D18" s="108">
         <v>25.1</v>
       </c>
       <c r="E18" s="110" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="111" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G18" s="116"/>
       <c r="H18" s="108" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I18" s="76"/>
       <c r="J18" s="56"/>
       <c r="K18" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="L18" s="282" t="s">
         <v>124</v>
       </c>
-      <c r="L18" s="281" t="s">
-        <v>125</v>
-      </c>
-      <c r="M18" s="282"/>
-      <c r="N18" s="282"/>
-      <c r="O18" s="282"/>
-      <c r="P18" s="283"/>
+      <c r="M18" s="283"/>
+      <c r="N18" s="283"/>
+      <c r="O18" s="283"/>
+      <c r="P18" s="284"/>
     </row>
     <row r="19" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A19" s="150"/>
       <c r="B19" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="321" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="320" t="s">
-        <v>127</v>
-      </c>
       <c r="D19" s="113" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E19" s="59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="113" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G19" s="52" t="s">
         <v>0</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I19" s="77"/>
       <c r="J19" s="59"/>
       <c r="K19" s="52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L19" s="58"/>
       <c r="M19" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N19" s="59"/>
       <c r="O19" s="52" t="s">
         <v>0</v>
       </c>
       <c r="P19" s="68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A20" s="152"/>
       <c r="B20" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="321"/>
+        <v>129</v>
+      </c>
+      <c r="C20" s="322"/>
       <c r="D20" s="112"/>
       <c r="E20" s="64"/>
       <c r="F20" s="112"/>
       <c r="G20" s="55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I20" s="78"/>
       <c r="J20" s="64"/>
       <c r="K20" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="L20" s="249" t="s">
-        <v>204</v>
+        <v>130</v>
+      </c>
+      <c r="L20" s="250" t="s">
+        <v>201</v>
       </c>
       <c r="M20" s="233"/>
       <c r="N20" s="233"/>
       <c r="O20" s="62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P20" s="67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A21" s="150"/>
       <c r="B21" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="80" t="s">
         <v>132</v>
-      </c>
-      <c r="D21" s="80" t="s">
-        <v>133</v>
       </c>
       <c r="E21" s="81"/>
       <c r="F21" s="109" t="s">
-        <v>209</v>
-      </c>
-      <c r="G21" s="288" t="s">
-        <v>215</v>
-      </c>
-      <c r="H21" s="288"/>
-      <c r="I21" s="277"/>
+        <v>206</v>
+      </c>
+      <c r="G21" s="289" t="s">
+        <v>212</v>
+      </c>
+      <c r="H21" s="289"/>
+      <c r="I21" s="278"/>
       <c r="J21" s="59"/>
       <c r="K21" s="52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L21" s="230" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M21" s="231"/>
       <c r="N21" s="231"/>
@@ -24651,155 +24680,155 @@
         <v>0</v>
       </c>
       <c r="P21" s="68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A22" s="152"/>
       <c r="B22" s="62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" s="82"/>
       <c r="D22" s="83" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22" s="84"/>
       <c r="F22" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" s="295" t="s">
-        <v>232</v>
-      </c>
-      <c r="H22" s="296"/>
-      <c r="I22" s="278"/>
+        <v>136</v>
+      </c>
+      <c r="G22" s="296" t="s">
+        <v>226</v>
+      </c>
+      <c r="H22" s="297"/>
+      <c r="I22" s="279"/>
       <c r="J22" s="64"/>
       <c r="K22" s="55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L22" s="232"/>
       <c r="M22" s="233"/>
       <c r="N22" s="233"/>
       <c r="O22" s="62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P22" s="67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="147" customFormat="1" ht="14.25" customHeight="1">
       <c r="A23" s="153"/>
       <c r="B23" s="55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="85"/>
       <c r="D23" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23" s="330">
+        <v>139</v>
+      </c>
+      <c r="E23" s="331">
         <v>119.4</v>
       </c>
-      <c r="F23" s="331"/>
+      <c r="F23" s="332"/>
       <c r="G23" s="52" t="s">
         <v>0</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I23" s="87"/>
       <c r="J23" s="69"/>
       <c r="K23" s="52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L23" s="230" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M23" s="231"/>
       <c r="N23" s="231"/>
       <c r="O23" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P23" s="88" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="147" customFormat="1" ht="14.25" customHeight="1">
       <c r="A24" s="153"/>
       <c r="B24" s="55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C24" s="85"/>
       <c r="D24" s="86" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="289">
+        <v>144</v>
+      </c>
+      <c r="E24" s="290">
         <f>M14+M15</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="F24" s="290"/>
+      <c r="F24" s="291"/>
       <c r="G24" s="55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H24" s="55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I24" s="87"/>
       <c r="J24" s="69"/>
       <c r="K24" s="55" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L24" s="232"/>
       <c r="M24" s="233"/>
       <c r="N24" s="233"/>
       <c r="O24" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P24" s="89" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A25" s="150"/>
       <c r="B25" s="52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="90"/>
-      <c r="D25" s="291" t="s">
-        <v>200</v>
-      </c>
-      <c r="E25" s="292"/>
-      <c r="F25" s="292"/>
+      <c r="D25" s="292" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="293"/>
+      <c r="F25" s="293"/>
       <c r="G25" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H25" s="52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I25" s="77"/>
       <c r="J25" s="59"/>
       <c r="K25" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="L25" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="L25" s="90" t="s">
+      <c r="M25" s="306" t="s">
         <v>151</v>
       </c>
-      <c r="M25" s="305" t="s">
-        <v>152</v>
-      </c>
-      <c r="N25" s="305"/>
-      <c r="O25" s="305"/>
-      <c r="P25" s="329"/>
+      <c r="N25" s="306"/>
+      <c r="O25" s="306"/>
+      <c r="P25" s="330"/>
     </row>
     <row r="26" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A26" s="148"/>
       <c r="B26" s="91" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C26" s="85"/>
       <c r="D26" s="107" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E26" s="69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F26" s="69">
         <v>12</v>
@@ -24808,89 +24837,89 @@
         <v>0</v>
       </c>
       <c r="H26" s="55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I26" s="87"/>
       <c r="J26" s="69"/>
       <c r="K26" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="L26" s="85" t="s">
         <v>155</v>
       </c>
-      <c r="L26" s="85" t="s">
+      <c r="M26" s="248" t="s">
         <v>156</v>
       </c>
-      <c r="M26" s="247" t="s">
-        <v>157</v>
-      </c>
-      <c r="N26" s="247"/>
-      <c r="O26" s="247"/>
-      <c r="P26" s="248"/>
+      <c r="N26" s="248"/>
+      <c r="O26" s="248"/>
+      <c r="P26" s="249"/>
     </row>
     <row r="27" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A27" s="150"/>
       <c r="B27" s="92" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="234"/>
+      <c r="D27" s="294" t="s">
         <v>158</v>
       </c>
-      <c r="C27" s="234"/>
-      <c r="D27" s="293" t="s">
+      <c r="E27" s="280"/>
+      <c r="F27" s="280" t="s">
         <v>159</v>
       </c>
-      <c r="E27" s="279"/>
-      <c r="F27" s="279" t="s">
+      <c r="G27" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" s="52" t="s">
         <v>160</v>
-      </c>
-      <c r="G27" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" s="52" t="s">
-        <v>161</v>
       </c>
       <c r="I27" s="77"/>
       <c r="J27" s="59"/>
       <c r="K27" s="52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L27" s="58">
         <v>1</v>
       </c>
       <c r="M27" s="52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N27" s="52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O27" s="52" t="s">
         <v>0</v>
       </c>
       <c r="P27" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A28" s="152"/>
       <c r="B28" s="93" t="s">
-        <v>165</v>
-      </c>
-      <c r="C28" s="281"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="280"/>
-      <c r="F28" s="280"/>
+        <v>164</v>
+      </c>
+      <c r="C28" s="282"/>
+      <c r="D28" s="295"/>
+      <c r="E28" s="281"/>
+      <c r="F28" s="281"/>
       <c r="G28" s="62" t="s">
         <v>0</v>
       </c>
       <c r="H28" s="62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I28" s="78"/>
       <c r="J28" s="64"/>
       <c r="K28" s="62" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L28" s="63"/>
       <c r="M28" s="62" t="s">
         <v>0</v>
       </c>
       <c r="N28" s="62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O28" s="64"/>
       <c r="P28" s="67"/>
@@ -24898,93 +24927,93 @@
     <row r="29" spans="1:16" s="147" customFormat="1" ht="23.25" customHeight="1">
       <c r="A29" s="151"/>
       <c r="B29" s="94" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" s="307" t="s">
-        <v>225</v>
-      </c>
-      <c r="D29" s="308"/>
-      <c r="E29" s="309"/>
-      <c r="F29" s="309"/>
-      <c r="G29" s="309"/>
-      <c r="H29" s="310"/>
-      <c r="I29" s="311"/>
+        <v>168</v>
+      </c>
+      <c r="C29" s="308" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" s="309"/>
+      <c r="E29" s="310"/>
+      <c r="F29" s="310"/>
+      <c r="G29" s="310"/>
+      <c r="H29" s="311"/>
+      <c r="I29" s="312"/>
       <c r="J29" s="95"/>
       <c r="K29" s="96" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="322">
+        <v>169</v>
+      </c>
+      <c r="L29" s="323">
         <v>0.2</v>
       </c>
-      <c r="M29" s="323"/>
-      <c r="N29" s="323"/>
-      <c r="O29" s="323"/>
-      <c r="P29" s="324"/>
+      <c r="M29" s="324"/>
+      <c r="N29" s="324"/>
+      <c r="O29" s="324"/>
+      <c r="P29" s="325"/>
     </row>
     <row r="30" spans="1:16" s="147" customFormat="1" ht="19.5" customHeight="1">
       <c r="A30" s="150"/>
       <c r="B30" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="298" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="299"/>
+      <c r="E30" s="299"/>
+      <c r="F30" s="299"/>
+      <c r="G30" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="79" t="s">
         <v>171</v>
-      </c>
-      <c r="C30" s="297" t="s">
-        <v>226</v>
-      </c>
-      <c r="D30" s="298"/>
-      <c r="E30" s="298"/>
-      <c r="F30" s="298"/>
-      <c r="G30" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="H30" s="79" t="s">
-        <v>172</v>
       </c>
       <c r="I30" s="77"/>
       <c r="J30" s="59"/>
       <c r="K30" s="52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L30" s="230" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M30" s="231"/>
       <c r="N30" s="231"/>
       <c r="O30" s="231"/>
       <c r="P30" s="97" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="147" customFormat="1" ht="20.25" customHeight="1">
       <c r="A31" s="149"/>
       <c r="B31" s="98" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="300"/>
+      <c r="D31" s="301"/>
+      <c r="E31" s="301"/>
+      <c r="F31" s="301"/>
+      <c r="G31" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" s="100" t="s">
         <v>174</v>
-      </c>
-      <c r="C31" s="299"/>
-      <c r="D31" s="300"/>
-      <c r="E31" s="300"/>
-      <c r="F31" s="300"/>
-      <c r="G31" s="117" t="s">
-        <v>193</v>
-      </c>
-      <c r="H31" s="100" t="s">
-        <v>175</v>
       </c>
       <c r="I31" s="101"/>
       <c r="J31" s="99"/>
       <c r="K31" s="98" t="s">
-        <v>176</v>
-      </c>
-      <c r="L31" s="284" t="s">
-        <v>202</v>
-      </c>
-      <c r="M31" s="285"/>
-      <c r="N31" s="285"/>
-      <c r="O31" s="285"/>
-      <c r="P31" s="286"/>
+        <v>175</v>
+      </c>
+      <c r="L31" s="285" t="s">
+        <v>199</v>
+      </c>
+      <c r="M31" s="286"/>
+      <c r="N31" s="286"/>
+      <c r="O31" s="286"/>
+      <c r="P31" s="287"/>
     </row>
     <row r="32" spans="1:16" s="147" customFormat="1" ht="6.75" customHeight="1">
       <c r="A32" s="148"/>
-      <c r="B32" s="272" t="s">
-        <v>177</v>
+      <c r="B32" s="273" t="s">
+        <v>176</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="102"/>
@@ -25003,7 +25032,7 @@
     </row>
     <row r="33" spans="1:16" s="147" customFormat="1" ht="13.5" customHeight="1">
       <c r="A33" s="148"/>
-      <c r="B33" s="273"/>
+      <c r="B33" s="274"/>
       <c r="C33" s="55" t="s">
         <v>0</v>
       </c>
@@ -25011,7 +25040,7 @@
       <c r="E33" s="55"/>
       <c r="F33" s="69"/>
       <c r="G33" s="55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -25060,7 +25089,7 @@
       <c r="N35" s="69"/>
       <c r="O35" s="55"/>
       <c r="P35" s="87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="147" customFormat="1" ht="18.75" customHeight="1">
@@ -25103,13 +25132,13 @@
       <c r="A38" s="146"/>
       <c r="B38" s="55"/>
       <c r="C38" s="55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D38" s="56"/>
       <c r="E38" s="103"/>
       <c r="F38" s="56"/>
       <c r="G38" s="55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H38" s="56"/>
       <c r="I38" s="56"/>
@@ -25207,7 +25236,7 @@
       <c r="I43" s="141"/>
       <c r="J43" s="140"/>
       <c r="K43" s="209" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L43" s="210"/>
       <c r="M43" s="210"/>
@@ -25218,13 +25247,13 @@
     <row r="44" spans="1:16" ht="15.75" customHeight="1">
       <c r="A44" s="136"/>
       <c r="B44" s="122" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C44" s="207"/>
       <c r="D44" s="207"/>
       <c r="E44" s="207"/>
       <c r="F44" s="226" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G44" s="227"/>
       <c r="H44" s="135"/>
@@ -25240,24 +25269,24 @@
     <row r="45" spans="1:16" ht="12.75" customHeight="1">
       <c r="A45" s="136"/>
       <c r="B45" s="122" t="s">
-        <v>208</v>
-      </c>
-      <c r="C45" s="236" t="s">
-        <v>203</v>
-      </c>
-      <c r="D45" s="236"/>
-      <c r="E45" s="236"/>
+        <v>205</v>
+      </c>
+      <c r="C45" s="243" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="243"/>
+      <c r="E45" s="243"/>
       <c r="F45" s="226" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G45" s="227"/>
       <c r="H45" s="135" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I45" s="138"/>
       <c r="J45" s="139"/>
       <c r="K45" s="240" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L45" s="241"/>
       <c r="M45" s="241"/>
@@ -25286,56 +25315,56 @@
     <row r="47" spans="1:16" ht="13.5" customHeight="1">
       <c r="A47" s="136"/>
       <c r="B47" s="122" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C47" s="207"/>
       <c r="D47" s="207"/>
       <c r="E47" s="207"/>
       <c r="F47" s="226" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G47" s="227"/>
       <c r="H47" s="135"/>
       <c r="K47" s="134" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L47" s="133"/>
       <c r="M47" s="132" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N47" s="132" t="s">
+        <v>184</v>
+      </c>
+      <c r="O47" s="132" t="s">
         <v>185</v>
-      </c>
-      <c r="O47" s="132" t="s">
-        <v>186</v>
       </c>
       <c r="P47" s="131"/>
     </row>
     <row r="48" spans="1:16" ht="16.5" customHeight="1">
       <c r="A48" s="130"/>
       <c r="B48" s="129" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C48" s="236" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D48" s="236"/>
       <c r="E48" s="236"/>
-      <c r="F48" s="245" t="s">
-        <v>181</v>
-      </c>
-      <c r="G48" s="246"/>
+      <c r="F48" s="246" t="s">
+        <v>180</v>
+      </c>
+      <c r="G48" s="247"/>
       <c r="H48" s="128" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I48" s="127"/>
       <c r="J48" s="126"/>
-      <c r="K48" s="243"/>
+      <c r="K48" s="244"/>
       <c r="L48" s="216"/>
       <c r="M48" s="216"/>
       <c r="N48" s="216"/>
       <c r="O48" s="216"/>
-      <c r="P48" s="244"/>
+      <c r="P48" s="245"/>
     </row>
     <row r="49" spans="2:12" ht="27.75" customHeight="1">
       <c r="B49" s="196"/>
@@ -26953,96 +26982,96 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AL59"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="10.8"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="12.796875" style="164" customWidth="1"/>
-    <col min="2" max="2" width="5.296875" style="164" customWidth="1"/>
-    <col min="3" max="20" width="2.8984375" style="164" customWidth="1"/>
-    <col min="21" max="21" width="1.09765625" style="164" customWidth="1"/>
-    <col min="22" max="22" width="2.8984375" style="164" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="164" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="164" customWidth="1"/>
+    <col min="3" max="20" width="2.88671875" style="164" customWidth="1"/>
+    <col min="21" max="21" width="1.109375" style="164" customWidth="1"/>
+    <col min="22" max="22" width="2.88671875" style="164" customWidth="1"/>
     <col min="23" max="23" width="1" style="164" customWidth="1"/>
-    <col min="24" max="24" width="7.3984375" style="164" customWidth="1"/>
-    <col min="25" max="16384" width="8.8984375" style="164"/>
+    <col min="24" max="24" width="7.44140625" style="164" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="164"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="39" customHeight="1">
-      <c r="A1" s="335" t="s">
+      <c r="A1" s="336" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="335"/>
-      <c r="C1" s="335"/>
-      <c r="D1" s="335"/>
-      <c r="E1" s="335"/>
-      <c r="F1" s="335"/>
-      <c r="G1" s="335"/>
-      <c r="H1" s="335"/>
-      <c r="I1" s="335"/>
-      <c r="J1" s="335"/>
-      <c r="K1" s="335"/>
-      <c r="L1" s="335"/>
-      <c r="M1" s="335"/>
-      <c r="N1" s="335"/>
-      <c r="O1" s="335"/>
-      <c r="P1" s="335"/>
-      <c r="Q1" s="335"/>
-      <c r="R1" s="335"/>
-      <c r="S1" s="335"/>
-      <c r="T1" s="335"/>
-      <c r="U1" s="335"/>
-      <c r="V1" s="335"/>
-      <c r="W1" s="335"/>
-      <c r="X1" s="335"/>
+      <c r="B1" s="336"/>
+      <c r="C1" s="336"/>
+      <c r="D1" s="336"/>
+      <c r="E1" s="336"/>
+      <c r="F1" s="336"/>
+      <c r="G1" s="336"/>
+      <c r="H1" s="336"/>
+      <c r="I1" s="336"/>
+      <c r="J1" s="336"/>
+      <c r="K1" s="336"/>
+      <c r="L1" s="336"/>
+      <c r="M1" s="336"/>
+      <c r="N1" s="336"/>
+      <c r="O1" s="336"/>
+      <c r="P1" s="336"/>
+      <c r="Q1" s="336"/>
+      <c r="R1" s="336"/>
+      <c r="S1" s="336"/>
+      <c r="T1" s="336"/>
+      <c r="U1" s="336"/>
+      <c r="V1" s="336"/>
+      <c r="W1" s="336"/>
+      <c r="X1" s="336"/>
     </row>
     <row r="2" spans="1:38" ht="14.25" customHeight="1">
-      <c r="S2" s="356" t="s">
-        <v>235</v>
-      </c>
-      <c r="T2" s="356"/>
-      <c r="U2" s="356"/>
-      <c r="V2" s="356"/>
-      <c r="W2" s="356"/>
-      <c r="X2" s="356"/>
+      <c r="S2" s="357" t="s">
+        <v>228</v>
+      </c>
+      <c r="T2" s="357"/>
+      <c r="U2" s="357"/>
+      <c r="V2" s="357"/>
+      <c r="W2" s="357"/>
+      <c r="X2" s="357"/>
     </row>
     <row r="3" spans="1:38" ht="18" customHeight="1">
       <c r="A3" s="165"/>
-      <c r="B3" s="357" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="357"/>
-      <c r="D3" s="357"/>
-      <c r="E3" s="357"/>
-      <c r="F3" s="357"/>
-      <c r="G3" s="357"/>
-      <c r="H3" s="357"/>
-      <c r="I3" s="357"/>
-      <c r="J3" s="357"/>
-      <c r="K3" s="357"/>
-      <c r="L3" s="357"/>
-      <c r="M3" s="357"/>
-      <c r="N3" s="358"/>
+      <c r="B3" s="358" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="358"/>
+      <c r="K3" s="358"/>
+      <c r="L3" s="358"/>
+      <c r="M3" s="358"/>
+      <c r="N3" s="359"/>
       <c r="O3" s="166" t="s">
         <v>2</v>
       </c>
       <c r="P3" s="166"/>
       <c r="Q3" s="167"/>
-      <c r="R3" s="336" t="str">
+      <c r="R3" s="337" t="str">
         <f>갑100A!N4</f>
         <v>서울에너지공사</v>
       </c>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
-      <c r="V3" s="337"/>
-      <c r="W3" s="337"/>
-      <c r="X3" s="338"/>
+      <c r="S3" s="338"/>
+      <c r="T3" s="338"/>
+      <c r="U3" s="338"/>
+      <c r="V3" s="338"/>
+      <c r="W3" s="338"/>
+      <c r="X3" s="339"/>
     </row>
     <row r="4" spans="1:38" ht="12.75" customHeight="1">
       <c r="A4" s="168"/>
       <c r="B4" s="169" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M4" s="170"/>
       <c r="O4" s="171" t="s">
@@ -27050,51 +27079,51 @@
       </c>
       <c r="P4" s="171"/>
       <c r="Q4" s="172"/>
-      <c r="R4" s="339"/>
-      <c r="S4" s="340"/>
-      <c r="T4" s="340"/>
-      <c r="U4" s="340"/>
-      <c r="V4" s="340"/>
-      <c r="W4" s="340"/>
-      <c r="X4" s="341"/>
+      <c r="R4" s="340"/>
+      <c r="S4" s="341"/>
+      <c r="T4" s="341"/>
+      <c r="U4" s="341"/>
+      <c r="V4" s="341"/>
+      <c r="W4" s="341"/>
+      <c r="X4" s="342"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
       <c r="A5" s="168"/>
-      <c r="B5" s="342" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="342"/>
-      <c r="D5" s="342"/>
-      <c r="E5" s="342"/>
-      <c r="F5" s="342"/>
-      <c r="G5" s="342"/>
-      <c r="H5" s="342"/>
-      <c r="I5" s="342"/>
-      <c r="J5" s="342"/>
-      <c r="K5" s="342"/>
-      <c r="L5" s="342"/>
-      <c r="M5" s="342"/>
-      <c r="N5" s="343"/>
+      <c r="B5" s="343" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="343"/>
+      <c r="D5" s="343"/>
+      <c r="E5" s="343"/>
+      <c r="F5" s="343"/>
+      <c r="G5" s="343"/>
+      <c r="H5" s="343"/>
+      <c r="I5" s="343"/>
+      <c r="J5" s="343"/>
+      <c r="K5" s="343"/>
+      <c r="L5" s="343"/>
+      <c r="M5" s="343"/>
+      <c r="N5" s="344"/>
       <c r="O5" s="173" t="s">
         <v>4</v>
       </c>
       <c r="P5" s="173"/>
       <c r="Q5" s="174"/>
-      <c r="R5" s="344" t="str">
+      <c r="R5" s="345" t="str">
         <f>갑100A!N6</f>
         <v>SIS/GI-SE-RT-TNTFLYSH001</v>
       </c>
-      <c r="S5" s="345"/>
-      <c r="T5" s="345"/>
-      <c r="U5" s="345"/>
-      <c r="V5" s="345"/>
-      <c r="W5" s="345"/>
-      <c r="X5" s="346"/>
+      <c r="S5" s="346"/>
+      <c r="T5" s="346"/>
+      <c r="U5" s="346"/>
+      <c r="V5" s="346"/>
+      <c r="W5" s="346"/>
+      <c r="X5" s="347"/>
     </row>
     <row r="6" spans="1:38" ht="12.75" customHeight="1">
       <c r="A6" s="175"/>
       <c r="B6" s="176" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" s="177"/>
       <c r="D6" s="177"/>
@@ -27113,13 +27142,13 @@
       </c>
       <c r="P6" s="178"/>
       <c r="Q6" s="179"/>
-      <c r="R6" s="347"/>
-      <c r="S6" s="348"/>
-      <c r="T6" s="348"/>
-      <c r="U6" s="348"/>
-      <c r="V6" s="348"/>
-      <c r="W6" s="348"/>
-      <c r="X6" s="349"/>
+      <c r="R6" s="348"/>
+      <c r="S6" s="349"/>
+      <c r="T6" s="349"/>
+      <c r="U6" s="349"/>
+      <c r="V6" s="349"/>
+      <c r="W6" s="349"/>
+      <c r="X6" s="350"/>
     </row>
     <row r="7" spans="1:38" s="9" customFormat="1" ht="10.5" customHeight="1">
       <c r="A7" s="3"/>
@@ -27217,7 +27246,7 @@
       </c>
       <c r="U8" s="19"/>
       <c r="V8" s="118" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W8" s="20"/>
       <c r="X8" s="21" t="s">
@@ -27287,7 +27316,7 @@
       </c>
       <c r="U9" s="30"/>
       <c r="V9" s="119" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="W9" s="8"/>
       <c r="X9" s="31" t="s">
@@ -27295,9 +27324,7 @@
       </c>
     </row>
     <row r="10" spans="1:38" s="22" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="115" t="s">
-        <v>233</v>
-      </c>
+      <c r="A10" s="115"/>
       <c r="B10" s="47"/>
       <c r="C10" s="32"/>
       <c r="D10" s="34"/>
@@ -27347,11 +27374,11 @@
       <c r="T10" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U10" s="350"/>
-      <c r="V10" s="351"/>
-      <c r="W10" s="352"/>
+      <c r="U10" s="351"/>
+      <c r="V10" s="352"/>
+      <c r="W10" s="353"/>
       <c r="X10" s="120" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27375,9 +27402,9 @@
       <c r="R11" s="187"/>
       <c r="S11" s="187"/>
       <c r="T11" s="188"/>
-      <c r="U11" s="353"/>
-      <c r="V11" s="354"/>
-      <c r="W11" s="355"/>
+      <c r="U11" s="354"/>
+      <c r="V11" s="355"/>
+      <c r="W11" s="356"/>
       <c r="X11" s="184"/>
     </row>
     <row r="12" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27401,9 +27428,9 @@
       <c r="R12" s="181"/>
       <c r="S12" s="181"/>
       <c r="T12" s="190"/>
-      <c r="U12" s="332"/>
-      <c r="V12" s="333"/>
-      <c r="W12" s="334"/>
+      <c r="U12" s="333"/>
+      <c r="V12" s="334"/>
+      <c r="W12" s="335"/>
       <c r="X12" s="185"/>
     </row>
     <row r="13" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27427,9 +27454,9 @@
       <c r="R13" s="181"/>
       <c r="S13" s="181"/>
       <c r="T13" s="190"/>
-      <c r="U13" s="332"/>
-      <c r="V13" s="333"/>
-      <c r="W13" s="334"/>
+      <c r="U13" s="333"/>
+      <c r="V13" s="334"/>
+      <c r="W13" s="335"/>
       <c r="X13" s="185"/>
     </row>
     <row r="14" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27453,9 +27480,9 @@
       <c r="R14" s="181"/>
       <c r="S14" s="181"/>
       <c r="T14" s="190"/>
-      <c r="U14" s="332"/>
-      <c r="V14" s="333"/>
-      <c r="W14" s="334"/>
+      <c r="U14" s="333"/>
+      <c r="V14" s="334"/>
+      <c r="W14" s="335"/>
       <c r="X14" s="185"/>
     </row>
     <row r="15" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27479,9 +27506,9 @@
       <c r="R15" s="181"/>
       <c r="S15" s="181"/>
       <c r="T15" s="190"/>
-      <c r="U15" s="332"/>
-      <c r="V15" s="333"/>
-      <c r="W15" s="334"/>
+      <c r="U15" s="333"/>
+      <c r="V15" s="334"/>
+      <c r="W15" s="335"/>
       <c r="X15" s="185"/>
     </row>
     <row r="16" spans="1:38" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27505,9 +27532,9 @@
       <c r="R16" s="181"/>
       <c r="S16" s="181"/>
       <c r="T16" s="190"/>
-      <c r="U16" s="332"/>
-      <c r="V16" s="333"/>
-      <c r="W16" s="334"/>
+      <c r="U16" s="333"/>
+      <c r="V16" s="334"/>
+      <c r="W16" s="335"/>
       <c r="X16" s="185"/>
     </row>
     <row r="17" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27531,9 +27558,9 @@
       <c r="R17" s="181"/>
       <c r="S17" s="181"/>
       <c r="T17" s="190"/>
-      <c r="U17" s="332"/>
-      <c r="V17" s="333"/>
-      <c r="W17" s="334"/>
+      <c r="U17" s="333"/>
+      <c r="V17" s="334"/>
+      <c r="W17" s="335"/>
       <c r="X17" s="185"/>
     </row>
     <row r="18" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27557,9 +27584,9 @@
       <c r="R18" s="181"/>
       <c r="S18" s="181"/>
       <c r="T18" s="190"/>
-      <c r="U18" s="332"/>
-      <c r="V18" s="333"/>
-      <c r="W18" s="334"/>
+      <c r="U18" s="333"/>
+      <c r="V18" s="334"/>
+      <c r="W18" s="335"/>
       <c r="X18" s="185"/>
     </row>
     <row r="19" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27583,9 +27610,9 @@
       <c r="R19" s="181"/>
       <c r="S19" s="181"/>
       <c r="T19" s="190"/>
-      <c r="U19" s="332"/>
-      <c r="V19" s="333"/>
-      <c r="W19" s="334"/>
+      <c r="U19" s="333"/>
+      <c r="V19" s="334"/>
+      <c r="W19" s="335"/>
       <c r="X19" s="185"/>
     </row>
     <row r="20" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27609,9 +27636,9 @@
       <c r="R20" s="181"/>
       <c r="S20" s="181"/>
       <c r="T20" s="190"/>
-      <c r="U20" s="332"/>
-      <c r="V20" s="333"/>
-      <c r="W20" s="334"/>
+      <c r="U20" s="333"/>
+      <c r="V20" s="334"/>
+      <c r="W20" s="335"/>
       <c r="X20" s="185"/>
     </row>
     <row r="21" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27635,9 +27662,9 @@
       <c r="R21" s="181"/>
       <c r="S21" s="181"/>
       <c r="T21" s="190"/>
-      <c r="U21" s="332"/>
-      <c r="V21" s="333"/>
-      <c r="W21" s="334"/>
+      <c r="U21" s="333"/>
+      <c r="V21" s="334"/>
+      <c r="W21" s="335"/>
       <c r="X21" s="185"/>
     </row>
     <row r="22" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27661,9 +27688,9 @@
       <c r="R22" s="181"/>
       <c r="S22" s="181"/>
       <c r="T22" s="190"/>
-      <c r="U22" s="332"/>
-      <c r="V22" s="333"/>
-      <c r="W22" s="334"/>
+      <c r="U22" s="333"/>
+      <c r="V22" s="334"/>
+      <c r="W22" s="335"/>
       <c r="X22" s="185"/>
     </row>
     <row r="23" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27687,9 +27714,9 @@
       <c r="R23" s="181"/>
       <c r="S23" s="181"/>
       <c r="T23" s="190"/>
-      <c r="U23" s="332"/>
-      <c r="V23" s="333"/>
-      <c r="W23" s="334"/>
+      <c r="U23" s="333"/>
+      <c r="V23" s="334"/>
+      <c r="W23" s="335"/>
       <c r="X23" s="185"/>
     </row>
     <row r="24" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27713,9 +27740,9 @@
       <c r="R24" s="181"/>
       <c r="S24" s="181"/>
       <c r="T24" s="190"/>
-      <c r="U24" s="332"/>
-      <c r="V24" s="333"/>
-      <c r="W24" s="334"/>
+      <c r="U24" s="333"/>
+      <c r="V24" s="334"/>
+      <c r="W24" s="335"/>
       <c r="X24" s="185"/>
     </row>
     <row r="25" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27739,9 +27766,9 @@
       <c r="R25" s="181"/>
       <c r="S25" s="181"/>
       <c r="T25" s="190"/>
-      <c r="U25" s="332"/>
-      <c r="V25" s="333"/>
-      <c r="W25" s="334"/>
+      <c r="U25" s="333"/>
+      <c r="V25" s="334"/>
+      <c r="W25" s="335"/>
       <c r="X25" s="185"/>
     </row>
     <row r="26" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27765,9 +27792,9 @@
       <c r="R26" s="181"/>
       <c r="S26" s="181"/>
       <c r="T26" s="190"/>
-      <c r="U26" s="332"/>
-      <c r="V26" s="333"/>
-      <c r="W26" s="334"/>
+      <c r="U26" s="333"/>
+      <c r="V26" s="334"/>
+      <c r="W26" s="335"/>
       <c r="X26" s="185"/>
     </row>
     <row r="27" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27791,9 +27818,9 @@
       <c r="R27" s="181"/>
       <c r="S27" s="181"/>
       <c r="T27" s="190"/>
-      <c r="U27" s="332"/>
-      <c r="V27" s="333"/>
-      <c r="W27" s="334"/>
+      <c r="U27" s="333"/>
+      <c r="V27" s="334"/>
+      <c r="W27" s="335"/>
       <c r="X27" s="185"/>
     </row>
     <row r="28" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27817,9 +27844,9 @@
       <c r="R28" s="181"/>
       <c r="S28" s="181"/>
       <c r="T28" s="190"/>
-      <c r="U28" s="332"/>
-      <c r="V28" s="333"/>
-      <c r="W28" s="334"/>
+      <c r="U28" s="333"/>
+      <c r="V28" s="334"/>
+      <c r="W28" s="335"/>
       <c r="X28" s="185"/>
     </row>
     <row r="29" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27843,9 +27870,9 @@
       <c r="R29" s="181"/>
       <c r="S29" s="181"/>
       <c r="T29" s="190"/>
-      <c r="U29" s="332"/>
-      <c r="V29" s="333"/>
-      <c r="W29" s="334"/>
+      <c r="U29" s="333"/>
+      <c r="V29" s="334"/>
+      <c r="W29" s="335"/>
       <c r="X29" s="185"/>
     </row>
     <row r="30" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27869,9 +27896,9 @@
       <c r="R30" s="181"/>
       <c r="S30" s="181"/>
       <c r="T30" s="190"/>
-      <c r="U30" s="332"/>
-      <c r="V30" s="333"/>
-      <c r="W30" s="334"/>
+      <c r="U30" s="333"/>
+      <c r="V30" s="334"/>
+      <c r="W30" s="335"/>
       <c r="X30" s="185"/>
     </row>
     <row r="31" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27895,9 +27922,9 @@
       <c r="R31" s="181"/>
       <c r="S31" s="181"/>
       <c r="T31" s="190"/>
-      <c r="U31" s="332"/>
-      <c r="V31" s="333"/>
-      <c r="W31" s="334"/>
+      <c r="U31" s="333"/>
+      <c r="V31" s="334"/>
+      <c r="W31" s="335"/>
       <c r="X31" s="185"/>
     </row>
     <row r="32" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
@@ -27921,23 +27948,17 @@
       <c r="R32" s="181"/>
       <c r="S32" s="181"/>
       <c r="T32" s="190"/>
-      <c r="U32" s="332"/>
-      <c r="V32" s="333"/>
-      <c r="W32" s="334"/>
+      <c r="U32" s="333"/>
+      <c r="V32" s="334"/>
+      <c r="W32" s="335"/>
       <c r="X32" s="185"/>
     </row>
     <row r="33" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
       <c r="A33" s="46"/>
-      <c r="B33" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>64</v>
-      </c>
+      <c r="B33" s="45"/>
+      <c r="C33" s="37"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="39">
-        <v>1</v>
-      </c>
+      <c r="E33" s="39"/>
       <c r="F33" s="189"/>
       <c r="G33" s="181"/>
       <c r="H33" s="181"/>
@@ -27953,27 +27974,17 @@
       <c r="R33" s="181"/>
       <c r="S33" s="181"/>
       <c r="T33" s="190"/>
-      <c r="U33" s="332" t="s">
-        <v>195</v>
-      </c>
-      <c r="V33" s="333"/>
-      <c r="W33" s="334"/>
-      <c r="X33" s="185" t="s">
-        <v>195</v>
-      </c>
+      <c r="U33" s="333"/>
+      <c r="V33" s="334"/>
+      <c r="W33" s="335"/>
+      <c r="X33" s="185"/>
     </row>
     <row r="34" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1">
       <c r="A34" s="46"/>
-      <c r="B34" s="45" t="s">
-        <v>227</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>64</v>
-      </c>
+      <c r="B34" s="45"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="195"/>
-      <c r="E34" s="39">
-        <v>1</v>
-      </c>
+      <c r="E34" s="39"/>
       <c r="F34" s="191"/>
       <c r="G34" s="192"/>
       <c r="H34" s="192"/>
@@ -27989,42 +28000,38 @@
       <c r="R34" s="192"/>
       <c r="S34" s="192"/>
       <c r="T34" s="193"/>
-      <c r="U34" s="353" t="s">
-        <v>219</v>
-      </c>
-      <c r="V34" s="354"/>
-      <c r="W34" s="355"/>
-      <c r="X34" s="184" t="s">
-        <v>218</v>
-      </c>
+      <c r="U34" s="354"/>
+      <c r="V34" s="355"/>
+      <c r="W34" s="356"/>
+      <c r="X34" s="184"/>
     </row>
     <row r="35" spans="1:24" ht="18.75" customHeight="1">
-      <c r="A35" s="359" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="360"/>
-      <c r="C35" s="360"/>
-      <c r="D35" s="360"/>
-      <c r="E35" s="360"/>
-      <c r="F35" s="360"/>
-      <c r="G35" s="360"/>
-      <c r="H35" s="360"/>
-      <c r="I35" s="360"/>
-      <c r="J35" s="360"/>
-      <c r="K35" s="360"/>
-      <c r="L35" s="360"/>
-      <c r="M35" s="360"/>
-      <c r="N35" s="360"/>
-      <c r="O35" s="360"/>
-      <c r="P35" s="360"/>
-      <c r="Q35" s="360"/>
-      <c r="R35" s="360"/>
-      <c r="S35" s="360"/>
-      <c r="T35" s="360"/>
-      <c r="U35" s="360"/>
-      <c r="V35" s="360"/>
-      <c r="W35" s="360"/>
-      <c r="X35" s="361"/>
+      <c r="A35" s="360" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="361"/>
+      <c r="C35" s="361"/>
+      <c r="D35" s="361"/>
+      <c r="E35" s="361"/>
+      <c r="F35" s="361"/>
+      <c r="G35" s="361"/>
+      <c r="H35" s="361"/>
+      <c r="I35" s="361"/>
+      <c r="J35" s="361"/>
+      <c r="K35" s="361"/>
+      <c r="L35" s="361"/>
+      <c r="M35" s="361"/>
+      <c r="N35" s="361"/>
+      <c r="O35" s="361"/>
+      <c r="P35" s="361"/>
+      <c r="Q35" s="361"/>
+      <c r="R35" s="361"/>
+      <c r="S35" s="361"/>
+      <c r="T35" s="361"/>
+      <c r="U35" s="361"/>
+      <c r="V35" s="361"/>
+      <c r="W35" s="361"/>
+      <c r="X35" s="362"/>
     </row>
     <row r="36" spans="1:24" ht="19.5" customHeight="1"/>
     <row r="37" spans="1:24" ht="19.5" customHeight="1"/>
@@ -28091,6 +28098,7 @@
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"바탕,굵게"&amp;10양식 H 101-2&amp;R&amp;G</oddFooter>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawingHF r:id="rId3"/>
 </worksheet>
 </file>